--- a/database/event/4081/event_4081_evp_summary.xlsx
+++ b/database/event/4081/event_4081_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.5642</v>
+        <v>6.6909</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0534</v>
+        <v>1.0737</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2304</v>
+        <v>2.2217</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5642</v>
+        <v>6.6909</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1736</v>
+        <v>3.3003</v>
       </c>
       <c r="G2" t="n">
         <v>3.3906</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1736</v>
+        <v>3.3003</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5723</v>
+        <v>2.675</v>
       </c>
       <c r="J2" t="n">
         <v>3.3906</v>
@@ -529,7 +529,7 @@
         <v>106</v>
       </c>
       <c r="M2" t="n">
-        <v>5.962899999999999</v>
+        <v>6.0656</v>
       </c>
       <c r="N2" t="n">
         <v>205</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.7118</v>
+        <v>5.7406</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9166</v>
+        <v>0.9212</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8861</v>
+        <v>1.8431</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7118</v>
+        <v>5.7406</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5801</v>
+        <v>3.6089</v>
       </c>
       <c r="G3" t="n">
         <v>2.1317</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5801</v>
+        <v>3.6089</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9018</v>
+        <v>2.9251</v>
       </c>
       <c r="J3" t="n">
         <v>2.1317</v>
@@ -575,7 +575,7 @@
         <v>95</v>
       </c>
       <c r="M3" t="n">
-        <v>5.0335</v>
+        <v>5.0568</v>
       </c>
       <c r="N3" t="n">
         <v>253</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.3733</v>
+        <v>5.5439</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8623</v>
+        <v>0.8897</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7493</v>
+        <v>1.7648</v>
       </c>
       <c r="E4" t="n">
-        <v>5.3733</v>
+        <v>5.5439</v>
       </c>
       <c r="F4" t="n">
-        <v>4.046</v>
+        <v>4.2166</v>
       </c>
       <c r="G4" t="n">
         <v>1.3273</v>
       </c>
       <c r="H4" t="n">
-        <v>4.046</v>
+        <v>4.4039</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2794</v>
+        <v>3.5695</v>
       </c>
       <c r="J4" t="n">
         <v>1.3273</v>
@@ -621,7 +621,7 @@
         <v>95</v>
       </c>
       <c r="M4" t="n">
-        <v>4.6067</v>
+        <v>4.8968</v>
       </c>
       <c r="N4" t="n">
         <v>253</v>
@@ -640,7 +640,7 @@
         <v>0.8278</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6625</v>
+        <v>1.6112</v>
       </c>
       <c r="E5" t="n">
         <v>5.1584</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.7539</v>
+        <v>4.9808</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7629</v>
+        <v>0.7993</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4991</v>
+        <v>1.5404</v>
       </c>
       <c r="E6" t="n">
-        <v>4.7539</v>
+        <v>4.9808</v>
       </c>
       <c r="F6" t="n">
-        <v>3.393</v>
+        <v>3.6199</v>
       </c>
       <c r="G6" t="n">
         <v>1.3609</v>
       </c>
       <c r="H6" t="n">
-        <v>3.393</v>
+        <v>3.6199</v>
       </c>
       <c r="I6" t="n">
-        <v>2.7501</v>
+        <v>2.934</v>
       </c>
       <c r="J6" t="n">
         <v>1.3609</v>
@@ -713,7 +713,7 @@
         <v>106</v>
       </c>
       <c r="M6" t="n">
-        <v>4.111000000000001</v>
+        <v>4.2949</v>
       </c>
       <c r="N6" t="n">
         <v>205</v>
@@ -732,7 +732,7 @@
         <v>0.7523</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4724</v>
+        <v>1.4237</v>
       </c>
       <c r="E7" t="n">
         <v>4.6879</v>
@@ -778,7 +778,7 @@
         <v>0.7381</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4367</v>
+        <v>1.3885</v>
       </c>
       <c r="E8" t="n">
         <v>4.5993</v>
@@ -824,7 +824,7 @@
         <v>0.699</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3384</v>
+        <v>1.2916</v>
       </c>
       <c r="E9" t="n">
         <v>4.3561</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.1812</v>
+        <v>4.2649</v>
       </c>
       <c r="C10" t="n">
-        <v>0.671</v>
+        <v>0.6844</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2677</v>
+        <v>1.2552</v>
       </c>
       <c r="E10" t="n">
-        <v>4.1812</v>
+        <v>4.2649</v>
       </c>
       <c r="F10" t="n">
-        <v>4.195</v>
+        <v>4.2787</v>
       </c>
       <c r="G10" t="n">
         <v>-0.0138</v>
       </c>
       <c r="H10" t="n">
-        <v>4.3171</v>
+        <v>4.6538</v>
       </c>
       <c r="I10" t="n">
-        <v>3.4991</v>
+        <v>3.772</v>
       </c>
       <c r="J10" t="n">
         <v>-0.0138</v>
@@ -897,7 +897,7 @@
         <v>45</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4853</v>
+        <v>3.7582</v>
       </c>
       <c r="N10" t="n">
         <v>190</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.1883</v>
+        <v>3.427</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8666</v>
+        <v>0.9214</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1883</v>
+        <v>3.427</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3717</v>
+        <v>1.6104</v>
       </c>
       <c r="G11" t="n">
         <v>1.8166</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3717</v>
+        <v>1.6104</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1118</v>
+        <v>1.3053</v>
       </c>
       <c r="J11" t="n">
         <v>1.8166</v>
@@ -943,7 +943,7 @@
         <v>106</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9284</v>
+        <v>3.1219</v>
       </c>
       <c r="N11" t="n">
         <v>205</v>
@@ -962,7 +962,7 @@
         <v>0.3985</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5818</v>
+        <v>0.5454</v>
       </c>
       <c r="E12" t="n">
         <v>2.4832</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.1627</v>
+        <v>2.3896</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3471</v>
+        <v>0.3835</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4523</v>
+        <v>0.5081</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1627</v>
+        <v>2.3896</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2705</v>
+        <v>1.4974</v>
       </c>
       <c r="G13" t="n">
         <v>0.8922</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2705</v>
+        <v>1.4974</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0298</v>
+        <v>1.2137</v>
       </c>
       <c r="J13" t="n">
         <v>0.8922</v>
@@ -1035,7 +1035,7 @@
         <v>106</v>
       </c>
       <c r="M13" t="n">
-        <v>1.922</v>
+        <v>2.1059</v>
       </c>
       <c r="N13" t="n">
         <v>205</v>
@@ -1054,7 +1054,7 @@
         <v>0.3286</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4058</v>
+        <v>0.3719</v>
       </c>
       <c r="E14" t="n">
         <v>2.0476</v>
@@ -1100,7 +1100,7 @@
         <v>0.2329</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1651</v>
+        <v>0.1344</v>
       </c>
       <c r="E15" t="n">
         <v>1.4516</v>
@@ -1146,7 +1146,7 @@
         <v>0.2269</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1499</v>
+        <v>0.1195</v>
       </c>
       <c r="E16" t="n">
         <v>1.4141</v>
@@ -1192,7 +1192,7 @@
         <v>0.1684</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0025</v>
+        <v>-0.0259</v>
       </c>
       <c r="E17" t="n">
         <v>1.0493</v>
@@ -1238,7 +1238,7 @@
         <v>0.1587</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0219</v>
+        <v>-0.05</v>
       </c>
       <c r="E18" t="n">
         <v>0.9888</v>
@@ -1284,7 +1284,7 @@
         <v>0.156</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0285</v>
+        <v>-0.0565</v>
       </c>
       <c r="E19" t="n">
         <v>0.9724</v>
@@ -1330,7 +1330,7 @@
         <v>0.0612</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2674</v>
+        <v>-0.292</v>
       </c>
       <c r="E20" t="n">
         <v>0.3812</v>
@@ -1376,7 +1376,7 @@
         <v>0.0606</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2687</v>
+        <v>-0.2934</v>
       </c>
       <c r="E21" t="n">
         <v>0.3778</v>
@@ -1422,7 +1422,7 @@
         <v>0.0331</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3379</v>
+        <v>-0.3616</v>
       </c>
       <c r="E22" t="n">
         <v>0.2065</v>
@@ -1468,7 +1468,7 @@
         <v>0.008699999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3995</v>
+        <v>-0.4224</v>
       </c>
       <c r="E23" t="n">
         <v>0.054</v>
@@ -1514,7 +1514,7 @@
         <v>0.0009</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4192</v>
+        <v>-0.4418</v>
       </c>
       <c r="E24" t="n">
         <v>0.0053</v>
@@ -1560,7 +1560,7 @@
         <v>-0.0123</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4524</v>
+        <v>-0.4745</v>
       </c>
       <c r="E25" t="n">
         <v>-0.07679999999999999</v>
@@ -1606,7 +1606,7 @@
         <v>-0.0136</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4557</v>
+        <v>-0.4777</v>
       </c>
       <c r="E26" t="n">
         <v>-0.0849</v>
@@ -1652,7 +1652,7 @@
         <v>-0.018</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4666</v>
+        <v>-0.4885</v>
       </c>
       <c r="E27" t="n">
         <v>-0.112</v>
@@ -1698,7 +1698,7 @@
         <v>-0.0905</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6491</v>
+        <v>-0.6685</v>
       </c>
       <c r="E28" t="n">
         <v>-0.5638</v>
@@ -1734,139 +1734,139 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>xccurate</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.5949</v>
+        <v>-0.5673</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0955</v>
+        <v>-0.091</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6617</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5949</v>
+        <v>-0.5673</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.5949</v>
+        <v>-0.5673</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.5949</v>
+        <v>-0.5673</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.5949</v>
+        <v>-0.5673</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.5949</v>
+        <v>-0.5673</v>
       </c>
       <c r="N29" t="n">
-        <v>85</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.7126</v>
+        <v>-0.5949</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1144</v>
+        <v>-0.0955</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7092000000000001</v>
+        <v>-0.6808999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.7126</v>
+        <v>-0.5949</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2489</v>
+        <v>-0.5949</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.9615</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.2489</v>
+        <v>-0.5949</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2018</v>
+        <v>-0.5949</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.9615</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>197</v>
+        <v>85</v>
       </c>
       <c r="L30" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.7597</v>
+        <v>-0.5949</v>
       </c>
       <c r="N30" t="n">
-        <v>253</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>xccurate</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.8119</v>
+        <v>-0.7126</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1303</v>
+        <v>-0.1144</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7494</v>
+        <v>-0.7278</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.8119</v>
+        <v>-0.7126</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.8119</v>
+        <v>0.2489</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-0.9615</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.8119</v>
+        <v>0.2489</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8119</v>
+        <v>0.2018</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-0.9615</v>
       </c>
       <c r="K31" t="n">
-        <v>113</v>
+        <v>197</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.8119</v>
+        <v>-0.7597</v>
       </c>
       <c r="N31" t="n">
-        <v>113</v>
+        <v>253</v>
       </c>
     </row>
     <row r="32">
@@ -1882,7 +1882,7 @@
         <v>-0.1328</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7557</v>
+        <v>-0.7736</v>
       </c>
       <c r="E32" t="n">
         <v>-0.8275</v>
@@ -1928,7 +1928,7 @@
         <v>-0.1428</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7808</v>
+        <v>-0.7984</v>
       </c>
       <c r="E33" t="n">
         <v>-0.8898</v>
@@ -1974,7 +1974,7 @@
         <v>-0.1465</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7901</v>
+        <v>-0.8075</v>
       </c>
       <c r="E34" t="n">
         <v>-0.9127</v>
@@ -2020,7 +2020,7 @@
         <v>-0.1818</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8789</v>
+        <v>-0.8952</v>
       </c>
       <c r="E35" t="n">
         <v>-1.1327</v>
@@ -2056,7 +2056,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>somebody</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -2066,7 +2066,7 @@
         <v>-0.1994</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9233</v>
+        <v>-0.9389</v>
       </c>
       <c r="E36" t="n">
         <v>-1.2424</v>
@@ -2102,32 +2102,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>captainMo</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2491</v>
+        <v>-1.2424</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2004</v>
+        <v>-0.1994</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.926</v>
+        <v>-0.9389</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2491</v>
+        <v>-1.2424</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.2491</v>
+        <v>-1.2424</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.2491</v>
+        <v>-1.2424</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.2491</v>
+        <v>-1.2424</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.2491</v>
+        <v>-1.2424</v>
       </c>
       <c r="N37" t="n">
         <v>113</v>
@@ -2148,32 +2148,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>somebody</t>
+          <t>captainMo</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2716</v>
+        <v>-1.2491</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2041</v>
+        <v>-0.2004</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9351</v>
+        <v>-0.9416</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2716</v>
+        <v>-1.2491</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2716</v>
+        <v>-1.2491</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2716</v>
+        <v>-1.2491</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2716</v>
+        <v>-1.2491</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2716</v>
+        <v>-1.2491</v>
       </c>
       <c r="N38" t="n">
         <v>113</v>
@@ -2204,7 +2204,7 @@
         <v>-0.2084</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9461000000000001</v>
+        <v>-0.9614</v>
       </c>
       <c r="E39" t="n">
         <v>-1.2989</v>
@@ -2250,7 +2250,7 @@
         <v>-0.2194</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.9737</v>
+        <v>-0.9886</v>
       </c>
       <c r="E40" t="n">
         <v>-1.3672</v>
@@ -2296,7 +2296,7 @@
         <v>-0.5864</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.8977</v>
+        <v>-1.8998</v>
       </c>
       <c r="E41" t="n">
         <v>-3.6544</v>

--- a/database/event/4081/event_4081_evp_summary.xlsx
+++ b/database/event/4081/event_4081_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.6909</v>
+        <v>6.2334</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0737</v>
+        <v>1.0003</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2217</v>
+        <v>2.1761</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6909</v>
+        <v>6.2334</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3003</v>
+        <v>3.0892</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3906</v>
+        <v>3.1442</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3003</v>
+        <v>5.3982</v>
       </c>
       <c r="I2" t="n">
-        <v>2.675</v>
+        <v>2.8068</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3906</v>
+        <v>3.1442</v>
       </c>
       <c r="K2" t="n">
         <v>99</v>
@@ -529,7 +529,7 @@
         <v>106</v>
       </c>
       <c r="M2" t="n">
-        <v>6.0656</v>
+        <v>5.951000000000001</v>
       </c>
       <c r="N2" t="n">
         <v>205</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.7406</v>
+        <v>5.0903</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9212</v>
+        <v>0.8169</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8431</v>
+        <v>1.66</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7406</v>
+        <v>5.0903</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6089</v>
+        <v>3.1643</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1317</v>
+        <v>1.926</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6089</v>
+        <v>5.6628</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9251</v>
+        <v>2.9444</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1317</v>
+        <v>1.926</v>
       </c>
       <c r="K3" t="n">
         <v>158</v>
@@ -575,7 +575,7 @@
         <v>95</v>
       </c>
       <c r="M3" t="n">
-        <v>5.0568</v>
+        <v>4.8704</v>
       </c>
       <c r="N3" t="n">
         <v>253</v>
@@ -584,44 +584,44 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.5439</v>
+        <v>4.8088</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8897</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7648</v>
+        <v>1.5329</v>
       </c>
       <c r="E4" t="n">
-        <v>5.5439</v>
+        <v>4.8088</v>
       </c>
       <c r="F4" t="n">
-        <v>4.2166</v>
+        <v>4.4518</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3273</v>
+        <v>0.357</v>
       </c>
       <c r="H4" t="n">
-        <v>4.4039</v>
+        <v>11.6945</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5695</v>
+        <v>6.0806</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3273</v>
+        <v>0.357</v>
       </c>
       <c r="K4" t="n">
-        <v>158</v>
+        <v>197</v>
       </c>
       <c r="L4" t="n">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="M4" t="n">
-        <v>4.8968</v>
+        <v>6.4376</v>
       </c>
       <c r="N4" t="n">
         <v>253</v>
@@ -630,93 +630,93 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.1584</v>
+        <v>4.7611</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8278</v>
+        <v>0.764</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6112</v>
+        <v>1.5114</v>
       </c>
       <c r="E5" t="n">
-        <v>5.1584</v>
+        <v>4.7611</v>
       </c>
       <c r="F5" t="n">
-        <v>4.7746</v>
+        <v>3.2034</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3838</v>
+        <v>1.5577</v>
       </c>
       <c r="H5" t="n">
-        <v>6.6489</v>
+        <v>5.8005</v>
       </c>
       <c r="I5" t="n">
-        <v>5.3891</v>
+        <v>3.016</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3838</v>
+        <v>1.5577</v>
       </c>
       <c r="K5" t="n">
-        <v>197</v>
+        <v>99</v>
       </c>
       <c r="L5" t="n">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="M5" t="n">
-        <v>5.7729</v>
+        <v>4.573700000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>253</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.9808</v>
+        <v>4.7558</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7993</v>
+        <v>0.7632</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5404</v>
+        <v>1.509</v>
       </c>
       <c r="E6" t="n">
-        <v>4.9808</v>
+        <v>4.7558</v>
       </c>
       <c r="F6" t="n">
-        <v>3.6199</v>
+        <v>3.5089</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3609</v>
+        <v>1.2469</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6199</v>
+        <v>6.877</v>
       </c>
       <c r="I6" t="n">
-        <v>2.934</v>
+        <v>3.5757</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3609</v>
+        <v>1.2469</v>
       </c>
       <c r="K6" t="n">
-        <v>99</v>
+        <v>158</v>
       </c>
       <c r="L6" t="n">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="M6" t="n">
-        <v>4.2949</v>
+        <v>4.8226</v>
       </c>
       <c r="N6" t="n">
-        <v>205</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.6879</v>
+        <v>4.6819</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7523</v>
+        <v>0.7513</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4237</v>
+        <v>1.4756</v>
       </c>
       <c r="E7" t="n">
-        <v>4.6879</v>
+        <v>4.6819</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3876</v>
+        <v>1.0072</v>
       </c>
       <c r="G7" t="n">
-        <v>4.3002</v>
+        <v>3.6747</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3876</v>
+        <v>1.0072</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3142</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>4.3002</v>
+        <v>3.6747</v>
       </c>
       <c r="K7" t="n">
         <v>99</v>
@@ -759,7 +759,7 @@
         <v>106</v>
       </c>
       <c r="M7" t="n">
-        <v>4.6144</v>
+        <v>4.1984</v>
       </c>
       <c r="N7" t="n">
         <v>205</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.5993</v>
+        <v>4.3465</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7381</v>
+        <v>0.6975</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3885</v>
+        <v>1.3242</v>
       </c>
       <c r="E8" t="n">
-        <v>4.5993</v>
+        <v>4.3465</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8225</v>
+        <v>2.903</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7769</v>
+        <v>1.4434</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8225</v>
+        <v>4.7421</v>
       </c>
       <c r="I8" t="n">
-        <v>2.2877</v>
+        <v>2.4657</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7769</v>
+        <v>1.4434</v>
       </c>
       <c r="K8" t="n">
         <v>158</v>
@@ -805,7 +805,7 @@
         <v>95</v>
       </c>
       <c r="M8" t="n">
-        <v>4.0646</v>
+        <v>3.9091</v>
       </c>
       <c r="N8" t="n">
         <v>253</v>
@@ -814,231 +814,231 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>nex</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.3561</v>
+        <v>4.2584</v>
       </c>
       <c r="C9" t="n">
-        <v>0.699</v>
+        <v>0.6834</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2916</v>
+        <v>1.2844</v>
       </c>
       <c r="E9" t="n">
-        <v>4.3561</v>
+        <v>4.2584</v>
       </c>
       <c r="F9" t="n">
-        <v>4.6662</v>
+        <v>2.4245</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3101</v>
+        <v>1.8339</v>
       </c>
       <c r="H9" t="n">
-        <v>6.2127</v>
+        <v>3.056</v>
       </c>
       <c r="I9" t="n">
-        <v>5.0355</v>
+        <v>1.589</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3101</v>
+        <v>1.8339</v>
       </c>
       <c r="K9" t="n">
-        <v>197</v>
+        <v>99</v>
       </c>
       <c r="L9" t="n">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="M9" t="n">
-        <v>4.7254</v>
+        <v>3.4229</v>
       </c>
       <c r="N9" t="n">
-        <v>253</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>nex</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.2649</v>
+        <v>4.2197</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6844</v>
+        <v>0.6772</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2552</v>
+        <v>1.267</v>
       </c>
       <c r="E10" t="n">
-        <v>4.2649</v>
+        <v>4.2197</v>
       </c>
       <c r="F10" t="n">
-        <v>4.2787</v>
+        <v>4.4518</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0138</v>
+        <v>-0.2321</v>
       </c>
       <c r="H10" t="n">
-        <v>4.6538</v>
+        <v>11.1554</v>
       </c>
       <c r="I10" t="n">
-        <v>3.772</v>
+        <v>5.8003</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0138</v>
+        <v>-0.2321</v>
       </c>
       <c r="K10" t="n">
-        <v>145</v>
+        <v>197</v>
       </c>
       <c r="L10" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7582</v>
+        <v>5.5682</v>
       </c>
       <c r="N10" t="n">
-        <v>190</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.427</v>
+        <v>3.8049</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.6106</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9214</v>
+        <v>1.0797</v>
       </c>
       <c r="E11" t="n">
-        <v>3.427</v>
+        <v>3.8049</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6104</v>
+        <v>3.6854</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8166</v>
+        <v>0.1195</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6104</v>
+        <v>7.4987</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3053</v>
+        <v>3.899</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8166</v>
+        <v>0.1195</v>
       </c>
       <c r="K11" t="n">
-        <v>99</v>
+        <v>145</v>
       </c>
       <c r="L11" t="n">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1219</v>
+        <v>4.0185</v>
       </c>
       <c r="N11" t="n">
-        <v>205</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>smooya</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4832</v>
+        <v>3.4317</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3985</v>
+        <v>0.5507</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5454</v>
+        <v>0.9112</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4832</v>
+        <v>3.4317</v>
       </c>
       <c r="F12" t="n">
-        <v>3.2539</v>
+        <v>2.3836</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7707000000000001</v>
+        <v>1.0481</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2539</v>
+        <v>2.912</v>
       </c>
       <c r="I12" t="n">
-        <v>2.6374</v>
+        <v>1.5141</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7707000000000001</v>
+        <v>1.0481</v>
       </c>
       <c r="K12" t="n">
-        <v>197</v>
+        <v>99</v>
       </c>
       <c r="L12" t="n">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="M12" t="n">
-        <v>1.8667</v>
+        <v>2.5622</v>
       </c>
       <c r="N12" t="n">
-        <v>253</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>smooya</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.3896</v>
+        <v>2.893</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3835</v>
+        <v>0.4643</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5081</v>
+        <v>0.668</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3896</v>
+        <v>2.893</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4974</v>
+        <v>3.4008</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8922</v>
+        <v>-0.5078</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4974</v>
+        <v>6.4962</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2137</v>
+        <v>3.3777</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8922</v>
+        <v>-0.5078</v>
       </c>
       <c r="K13" t="n">
-        <v>99</v>
+        <v>197</v>
       </c>
       <c r="L13" t="n">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="M13" t="n">
-        <v>2.1059</v>
+        <v>2.8699</v>
       </c>
       <c r="N13" t="n">
-        <v>205</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.0476</v>
+        <v>2.4831</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3286</v>
+        <v>0.3985</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3719</v>
+        <v>0.483</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0476</v>
+        <v>2.4831</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2248</v>
+        <v>2.6651</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1772</v>
+        <v>-0.182</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2248</v>
+        <v>3.904</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8033</v>
+        <v>2.0299</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1772</v>
+        <v>-0.182</v>
       </c>
       <c r="K14" t="n">
         <v>145</v>
@@ -1081,7 +1081,7 @@
         <v>45</v>
       </c>
       <c r="M14" t="n">
-        <v>1.6261</v>
+        <v>1.8479</v>
       </c>
       <c r="N14" t="n">
         <v>190</v>
@@ -1090,645 +1090,645 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MICHU</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.4516</v>
+        <v>2.0321</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2329</v>
+        <v>0.3261</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1344</v>
+        <v>0.2794</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4516</v>
+        <v>2.0321</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4516</v>
+        <v>2.4681</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0.436</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4516</v>
+        <v>3.2097</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4516</v>
+        <v>1.6689</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.436</v>
       </c>
       <c r="K15" t="n">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4516</v>
+        <v>1.2329</v>
       </c>
       <c r="N15" t="n">
-        <v>131</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>snatchie</t>
+          <t>ANGE1</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4141</v>
+        <v>1.9158</v>
       </c>
       <c r="C16" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="D16" t="n">
         <v>0.2269</v>
       </c>
-      <c r="D16" t="n">
-        <v>0.1195</v>
-      </c>
       <c r="E16" t="n">
-        <v>1.4141</v>
+        <v>1.9158</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4141</v>
+        <v>2.5853</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0.6695</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4141</v>
+        <v>3.6228</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4141</v>
+        <v>1.8837</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0.6695</v>
       </c>
       <c r="K16" t="n">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4141</v>
+        <v>1.2142</v>
       </c>
       <c r="N16" t="n">
-        <v>131</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>MICHU</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.0493</v>
+        <v>1.6004</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1684</v>
+        <v>0.2568</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0259</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0493</v>
+        <v>1.6004</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6569</v>
+        <v>1.6004</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6076</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6569</v>
+        <v>1.6004</v>
       </c>
       <c r="I17" t="n">
-        <v>1.343</v>
+        <v>1.6004</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6076</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="L17" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7353999999999999</v>
+        <v>1.6004</v>
       </c>
       <c r="N17" t="n">
-        <v>190</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ANGE1</t>
+          <t>snatchie</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9888</v>
+        <v>1.5395</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1587</v>
+        <v>0.247</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.05</v>
+        <v>0.057</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9888</v>
+        <v>1.5395</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9291</v>
+        <v>1.5395</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9403</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.9291</v>
+        <v>1.5395</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5636</v>
+        <v>1.5395</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9403</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="L18" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6233000000000001</v>
+        <v>1.5395</v>
       </c>
       <c r="N18" t="n">
-        <v>190</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>DeadFox</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9724</v>
+        <v>1.4381</v>
       </c>
       <c r="C19" t="n">
-        <v>0.156</v>
+        <v>0.2308</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0565</v>
+        <v>0.0112</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9724</v>
+        <v>1.4381</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9724</v>
+        <v>2.1868</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.7487</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9724</v>
+        <v>2.2188</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9724</v>
+        <v>1.1536</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.7487</v>
       </c>
       <c r="K19" t="n">
-        <v>85</v>
+        <v>145</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9724</v>
+        <v>0.4048999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>85</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>gob b</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3812</v>
+        <v>1.2111</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0612</v>
+        <v>0.1943</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.292</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3812</v>
+        <v>1.2111</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3812</v>
+        <v>1.4803</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.2692</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3812</v>
+        <v>1.4803</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3812</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.2692</v>
       </c>
       <c r="K20" t="n">
-        <v>85</v>
+        <v>197</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3812</v>
+        <v>0.5005000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>85</v>
+        <v>253</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>rallen</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.3778</v>
+        <v>1.0597</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0606</v>
+        <v>0.1701</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2934</v>
+        <v>-0.1596</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3778</v>
+        <v>1.0597</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3778</v>
+        <v>1.0597</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3778</v>
+        <v>1.0597</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3778</v>
+        <v>1.0597</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3778</v>
+        <v>1.0597</v>
       </c>
       <c r="N21" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>rallen</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2065</v>
+        <v>0.8424</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0331</v>
+        <v>0.1352</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3616</v>
+        <v>-0.2577</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2065</v>
+        <v>0.8424</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2065</v>
+        <v>0.8424</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2065</v>
+        <v>0.8424</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2065</v>
+        <v>0.8424</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>131</v>
+        <v>90</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2065</v>
+        <v>0.8424</v>
       </c>
       <c r="N22" t="n">
-        <v>131</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.054</v>
+        <v>0.7809</v>
       </c>
       <c r="C23" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.1253</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4224</v>
+        <v>-0.2855</v>
       </c>
       <c r="E23" t="n">
-        <v>0.054</v>
+        <v>0.7809</v>
       </c>
       <c r="F23" t="n">
-        <v>0.054</v>
+        <v>0.7809</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.054</v>
+        <v>0.7809</v>
       </c>
       <c r="I23" t="n">
-        <v>0.054</v>
+        <v>0.7809</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>90</v>
+        <v>131</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.054</v>
+        <v>0.7809</v>
       </c>
       <c r="N23" t="n">
-        <v>90</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0053</v>
+        <v>0.7439</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0009</v>
+        <v>0.1194</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4418</v>
+        <v>-0.3022</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0053</v>
+        <v>0.7439</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0053</v>
+        <v>1.3712</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.6273</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0053</v>
+        <v>1.3712</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0053</v>
+        <v>0.713</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.6273</v>
       </c>
       <c r="K24" t="n">
-        <v>131</v>
+        <v>197</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0053</v>
+        <v>0.0857</v>
       </c>
       <c r="N24" t="n">
-        <v>131</v>
+        <v>253</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>mouz</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.07679999999999999</v>
+        <v>0.4402</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0123</v>
+        <v>0.0706</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4745</v>
+        <v>-0.4393</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.07679999999999999</v>
+        <v>0.4402</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.07679999999999999</v>
+        <v>0.4402</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.07679999999999999</v>
+        <v>0.4402</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.07679999999999999</v>
+        <v>0.4402</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.07679999999999999</v>
+        <v>0.4402</v>
       </c>
       <c r="N25" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>gob b</t>
+          <t>mouz</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.0849</v>
+        <v>0.2631</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0136</v>
+        <v>0.0422</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4777</v>
+        <v>-0.5192</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0849</v>
+        <v>0.2631</v>
       </c>
       <c r="F26" t="n">
-        <v>0.315</v>
+        <v>0.2631</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.3999</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.315</v>
+        <v>0.2631</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2553</v>
+        <v>0.2631</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.3999</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>197</v>
+        <v>90</v>
       </c>
       <c r="L26" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1446</v>
+        <v>0.2631</v>
       </c>
       <c r="N26" t="n">
-        <v>253</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DeadFox</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.112</v>
+        <v>0.2455</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.018</v>
+        <v>0.0394</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4885</v>
+        <v>-0.5272</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.112</v>
+        <v>0.2455</v>
       </c>
       <c r="F27" t="n">
-        <v>0.888</v>
+        <v>0.2455</v>
       </c>
       <c r="G27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.888</v>
+        <v>0.2455</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7197</v>
+        <v>0.2455</v>
       </c>
       <c r="J27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>145</v>
+        <v>90</v>
       </c>
       <c r="L27" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.2803</v>
+        <v>0.2455</v>
       </c>
       <c r="N27" t="n">
-        <v>190</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>reatz</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.5638</v>
+        <v>0.2046</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0905</v>
+        <v>0.0328</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6685</v>
+        <v>-0.5456</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.5638</v>
+        <v>0.2046</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.5638</v>
+        <v>0.2046</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.5638</v>
+        <v>0.2046</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.5638</v>
+        <v>0.2046</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>90</v>
+        <v>131</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.5638</v>
+        <v>0.2046</v>
       </c>
       <c r="N28" t="n">
-        <v>90</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.5673</v>
+        <v>-0.1608</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.091</v>
+        <v>-0.0258</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6699000000000001</v>
+        <v>-0.7106</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5673</v>
+        <v>-0.1608</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.5673</v>
+        <v>-0.1608</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.5673</v>
+        <v>-0.1608</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.5673</v>
+        <v>-0.1608</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.5673</v>
+        <v>-0.1608</v>
       </c>
       <c r="N29" t="n">
         <v>113</v>
@@ -1780,93 +1780,93 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>reatz</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.5949</v>
+        <v>-0.2699</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0955</v>
+        <v>-0.0433</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6808999999999999</v>
+        <v>-0.7599</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.5949</v>
+        <v>-0.2699</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.5949</v>
+        <v>-0.2699</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.5949</v>
+        <v>-0.2699</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.5949</v>
+        <v>-0.2699</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.5949</v>
+        <v>-0.2699</v>
       </c>
       <c r="N30" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.7126</v>
+        <v>-0.3743</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1144</v>
+        <v>-0.0601</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7278</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.7126</v>
+        <v>-0.3743</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2489</v>
+        <v>-0.3743</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.9615</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2489</v>
+        <v>-0.3743</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2018</v>
+        <v>-0.3743</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.9615</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>197</v>
+        <v>85</v>
       </c>
       <c r="L31" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.7597</v>
+        <v>-0.3743</v>
       </c>
       <c r="N31" t="n">
-        <v>253</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.8275</v>
+        <v>-0.3976</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1328</v>
+        <v>-0.0638</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7736</v>
+        <v>-0.8175</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8275</v>
+        <v>-0.3976</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.8275</v>
+        <v>-0.3976</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.8275</v>
+        <v>-0.3976</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.8275</v>
+        <v>-0.3976</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.8275</v>
+        <v>-0.3976</v>
       </c>
       <c r="N32" t="n">
         <v>90</v>
@@ -1918,47 +1918,47 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>morelz</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.8898</v>
+        <v>-0.6659</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1428</v>
+        <v>-0.1069</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7984</v>
+        <v>-0.9386</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.8898</v>
+        <v>-0.6659</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.7327</v>
+        <v>-0.6659</v>
       </c>
       <c r="G33" t="n">
-        <v>0.8429</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.7327</v>
+        <v>-0.6659</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.4044</v>
+        <v>-0.6659</v>
       </c>
       <c r="J33" t="n">
-        <v>0.8429</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="L33" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5615000000000001</v>
+        <v>-0.6659</v>
       </c>
       <c r="N33" t="n">
-        <v>253</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9127</v>
+        <v>-0.6758</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1465</v>
+        <v>-0.1084</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8075</v>
+        <v>-0.9431</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9127</v>
+        <v>-0.6758</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.9127</v>
+        <v>-0.6758</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.9127</v>
+        <v>-0.6758</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.9127</v>
+        <v>-0.6758</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.9127</v>
+        <v>-0.6758</v>
       </c>
       <c r="N34" t="n">
         <v>113</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1327</v>
+        <v>-0.7349</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1818</v>
+        <v>-0.1179</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8952</v>
+        <v>-0.9698</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1327</v>
+        <v>-0.7349</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.1327</v>
+        <v>-0.7349</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.1327</v>
+        <v>-0.7349</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.1327</v>
+        <v>-0.7349</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.1327</v>
+        <v>-0.7349</v>
       </c>
       <c r="N35" t="n">
         <v>85</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.2424</v>
+        <v>-0.7961</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1994</v>
+        <v>-0.1278</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9389</v>
+        <v>-0.9974</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.2424</v>
+        <v>-0.7961</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.2424</v>
+        <v>-0.7961</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.2424</v>
+        <v>-0.7961</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.2424</v>
+        <v>-0.7961</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.2424</v>
+        <v>-0.7961</v>
       </c>
       <c r="N36" t="n">
         <v>113</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2424</v>
+        <v>-0.8804</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1994</v>
+        <v>-0.1413</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9389</v>
+        <v>-1.0355</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2424</v>
+        <v>-0.8804</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.2424</v>
+        <v>-0.8804</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.2424</v>
+        <v>-0.8804</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.2424</v>
+        <v>-0.8804</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.2424</v>
+        <v>-0.8804</v>
       </c>
       <c r="N37" t="n">
         <v>113</v>
@@ -2148,139 +2148,139 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>captainMo</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2491</v>
+        <v>-0.8855</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2004</v>
+        <v>-0.1421</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9416</v>
+        <v>-1.0378</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2491</v>
+        <v>-0.8855</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2491</v>
+        <v>-0.8855</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2491</v>
+        <v>-0.8855</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2491</v>
+        <v>-0.8855</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2491</v>
+        <v>-0.8855</v>
       </c>
       <c r="N38" t="n">
-        <v>113</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>morelz</t>
+          <t>captainMo</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2989</v>
+        <v>-0.97</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2084</v>
+        <v>-0.1557</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9614</v>
+        <v>-1.0759</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2989</v>
+        <v>-0.97</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.2989</v>
+        <v>-0.97</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.2989</v>
+        <v>-0.97</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.2989</v>
+        <v>-0.97</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.2989</v>
+        <v>-0.97</v>
       </c>
       <c r="N39" t="n">
-        <v>131</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3672</v>
+        <v>-0.9789</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2194</v>
+        <v>-0.1571</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.9886</v>
+        <v>-1.0799</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3672</v>
+        <v>-0.9789</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.3672</v>
+        <v>-1.8244</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>0.8455</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.3672</v>
+        <v>-1.8244</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.3672</v>
+        <v>-0.9486</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>0.8455</v>
       </c>
       <c r="K40" t="n">
-        <v>85</v>
+        <v>158</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.3672</v>
+        <v>-0.1031</v>
       </c>
       <c r="N40" t="n">
-        <v>85</v>
+        <v>253</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.6544</v>
+        <v>-4.2965</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5864</v>
+        <v>-0.6895</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.8998</v>
+        <v>-2.5777</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.6544</v>
+        <v>-4.2965</v>
       </c>
       <c r="F41" t="n">
-        <v>-3.2808</v>
+        <v>-4.1433</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.3736</v>
+        <v>-0.1532</v>
       </c>
       <c r="H41" t="n">
-        <v>-3.2808</v>
+        <v>-4.1433</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.6592</v>
+        <v>-2.1543</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.3736</v>
+        <v>-0.1532</v>
       </c>
       <c r="K41" t="n">
         <v>158</v>
@@ -2323,7 +2323,7 @@
         <v>95</v>
       </c>
       <c r="M41" t="n">
-        <v>-3.0328</v>
+        <v>-2.3075</v>
       </c>
       <c r="N41" t="n">
         <v>253</v>
@@ -2429,10 +2429,10 @@
         <v>1.01</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1458</v>
+        <v>0.1155</v>
       </c>
       <c r="J2" t="n">
-        <v>2.916</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.97</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0295</v>
+        <v>-0.0133</v>
       </c>
       <c r="J3" t="n">
-        <v>0.59</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.76</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3514</v>
+        <v>-0.2493</v>
       </c>
       <c r="J4" t="n">
-        <v>-7.028</v>
+        <v>-4.986</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.59</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6107</v>
+        <v>-0.4084</v>
       </c>
       <c r="J5" t="n">
-        <v>-12.214</v>
+        <v>-8.167999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.48</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7517</v>
+        <v>-0.5107</v>
       </c>
       <c r="J6" t="n">
-        <v>-15.034</v>
+        <v>-10.214</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1384</v>
+        <v>1.1079</v>
       </c>
       <c r="J7" t="n">
-        <v>22.768</v>
+        <v>22.158</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.4</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9194</v>
+        <v>0.9691</v>
       </c>
       <c r="J8" t="n">
-        <v>18.388</v>
+        <v>19.382</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.38</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8692</v>
+        <v>0.9319</v>
       </c>
       <c r="J9" t="n">
-        <v>17.384</v>
+        <v>18.638</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.33</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.8278</v>
       </c>
       <c r="J10" t="n">
-        <v>14.688</v>
+        <v>16.556</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.25</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5458</v>
+        <v>0.6465</v>
       </c>
       <c r="J11" t="n">
-        <v>10.916</v>
+        <v>12.93</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.35</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.7109</v>
       </c>
       <c r="J12" t="n">
-        <v>17.706</v>
+        <v>21.327</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1227</v>
+        <v>0.1197</v>
       </c>
       <c r="J13" t="n">
-        <v>3.681</v>
+        <v>3.591</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.92</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1862</v>
+        <v>-0.1097</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.586</v>
+        <v>-3.291</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.85</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3041</v>
+        <v>-0.1859</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.122999999999999</v>
+        <v>-5.577</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.75</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4499</v>
+        <v>-0.2862</v>
       </c>
       <c r="J16" t="n">
-        <v>-13.497</v>
+        <v>-8.586</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.64</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4745</v>
+        <v>1.3074</v>
       </c>
       <c r="J17" t="n">
-        <v>44.235</v>
+        <v>39.222</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.52</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2435</v>
+        <v>1.1578</v>
       </c>
       <c r="J18" t="n">
-        <v>37.305</v>
+        <v>34.734</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.16</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3834</v>
+        <v>0.4547</v>
       </c>
       <c r="J19" t="n">
-        <v>11.502</v>
+        <v>13.641</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.07</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1309</v>
+        <v>0.2057</v>
       </c>
       <c r="J20" t="n">
-        <v>3.927</v>
+        <v>6.171</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.8</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7388</v>
+        <v>-0.6839</v>
       </c>
       <c r="J21" t="n">
-        <v>-22.164</v>
+        <v>-20.517</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.23</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4723</v>
+        <v>0.5472</v>
       </c>
       <c r="J22" t="n">
-        <v>11.8075</v>
+        <v>13.68</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0293</v>
       </c>
       <c r="J23" t="n">
-        <v>1.6175</v>
+        <v>0.7325</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.74</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4358</v>
+        <v>-0.2821</v>
       </c>
       <c r="J24" t="n">
-        <v>-10.895</v>
+        <v>-7.0525</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.73</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4501</v>
+        <v>-0.2917</v>
       </c>
       <c r="J25" t="n">
-        <v>-11.2525</v>
+        <v>-7.2925</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.66</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5462</v>
+        <v>-0.3584</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.655</v>
+        <v>-8.960000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.78</v>
       </c>
       <c r="I27" t="n">
-        <v>1.7273</v>
+        <v>1.477</v>
       </c>
       <c r="J27" t="n">
-        <v>43.1825</v>
+        <v>36.925</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.45</v>
       </c>
       <c r="I28" t="n">
-        <v>1.0995</v>
+        <v>1.0681</v>
       </c>
       <c r="J28" t="n">
-        <v>27.4875</v>
+        <v>26.7025</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.34</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8606</v>
+        <v>0.8729</v>
       </c>
       <c r="J29" t="n">
-        <v>21.515</v>
+        <v>21.8225</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.93</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4029</v>
+        <v>-0.3243</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.0725</v>
+        <v>-8.1075</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.71</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.9419</v>
+        <v>-0.9093</v>
       </c>
       <c r="J31" t="n">
-        <v>-23.5475</v>
+        <v>-22.7325</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>2</v>
       </c>
       <c r="I32" t="n">
-        <v>1.1429</v>
+        <v>1.0379</v>
       </c>
       <c r="J32" t="n">
-        <v>22.858</v>
+        <v>20.758</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.74</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8844</v>
+        <v>0.8177</v>
       </c>
       <c r="J33" t="n">
-        <v>17.688</v>
+        <v>16.354</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.39</v>
       </c>
       <c r="I34" t="n">
-        <v>0.461</v>
+        <v>0.4688</v>
       </c>
       <c r="J34" t="n">
-        <v>9.220000000000001</v>
+        <v>9.375999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.24</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2729</v>
+        <v>0.2987</v>
       </c>
       <c r="J35" t="n">
-        <v>5.458</v>
+        <v>5.974</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.19</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2067</v>
+        <v>0.2373</v>
       </c>
       <c r="J36" t="n">
-        <v>4.134</v>
+        <v>4.746</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.07</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3545</v>
+        <v>0.3143</v>
       </c>
       <c r="J37" t="n">
-        <v>7.09</v>
+        <v>6.286</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.75</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2616</v>
+        <v>-0.2251</v>
       </c>
       <c r="J38" t="n">
-        <v>-5.232</v>
+        <v>-4.502</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.46</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.733</v>
+        <v>-0.502</v>
       </c>
       <c r="J39" t="n">
-        <v>-14.66</v>
+        <v>-10.04</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.37</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.8522</v>
+        <v>-0.588</v>
       </c>
       <c r="J40" t="n">
-        <v>-17.044</v>
+        <v>-11.76</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.33</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.9029</v>
+        <v>-0.6264999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>-18.058</v>
+        <v>-12.53</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.01</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1328</v>
+        <v>0.1007</v>
       </c>
       <c r="J42" t="n">
-        <v>3.5856</v>
+        <v>2.7189</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.87</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1697</v>
+        <v>-0.1434</v>
       </c>
       <c r="J43" t="n">
-        <v>-4.5819</v>
+        <v>-3.8718</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.78</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.3382</v>
+        <v>-0.2335</v>
       </c>
       <c r="J44" t="n">
-        <v>-9.131399999999999</v>
+        <v>-6.3045</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.72</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4369</v>
+        <v>-0.2904</v>
       </c>
       <c r="J45" t="n">
-        <v>-11.7963</v>
+        <v>-7.8408</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.58</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6318</v>
+        <v>-0.4222</v>
       </c>
       <c r="J46" t="n">
-        <v>-17.0586</v>
+        <v>-11.3994</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.66</v>
       </c>
       <c r="I47" t="n">
-        <v>1.4813</v>
+        <v>1.3154</v>
       </c>
       <c r="J47" t="n">
-        <v>39.9951</v>
+        <v>35.5158</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.51</v>
       </c>
       <c r="I48" t="n">
-        <v>1.1918</v>
+        <v>1.1317</v>
       </c>
       <c r="J48" t="n">
-        <v>32.1786</v>
+        <v>30.5559</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.28</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6551</v>
+        <v>0.7286</v>
       </c>
       <c r="J49" t="n">
-        <v>17.6877</v>
+        <v>19.6722</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.24</v>
       </c>
       <c r="I50" t="n">
-        <v>0.554</v>
+        <v>0.6368</v>
       </c>
       <c r="J50" t="n">
-        <v>14.958</v>
+        <v>17.1936</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.83</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6817</v>
+        <v>-0.6203</v>
       </c>
       <c r="J51" t="n">
-        <v>-18.4059</v>
+        <v>-16.7481</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.37</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9601</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="J52" t="n">
-        <v>28.803</v>
+        <v>21.063</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.34</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8938</v>
+        <v>0.6619</v>
       </c>
       <c r="J53" t="n">
-        <v>26.814</v>
+        <v>19.857</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.15</v>
       </c>
       <c r="I54" t="n">
-        <v>0.39</v>
+        <v>0.3969</v>
       </c>
       <c r="J54" t="n">
-        <v>11.7</v>
+        <v>11.907</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.11</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2747</v>
+        <v>0.331</v>
       </c>
       <c r="J55" t="n">
-        <v>8.241</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.354</v>
+        <v>-0.2781</v>
       </c>
       <c r="J56" t="n">
-        <v>-10.62</v>
+        <v>-8.343</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.14</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3379</v>
+        <v>0.354</v>
       </c>
       <c r="J57" t="n">
-        <v>10.137</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.98</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0012</v>
+        <v>-0.023</v>
       </c>
       <c r="J58" t="n">
-        <v>0.036</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.86</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2478</v>
+        <v>-0.164</v>
       </c>
       <c r="J59" t="n">
-        <v>-7.434</v>
+        <v>-4.92</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.71</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4804</v>
+        <v>-0.312</v>
       </c>
       <c r="J60" t="n">
-        <v>-14.412</v>
+        <v>-9.359999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.71</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4804</v>
+        <v>-0.312</v>
       </c>
       <c r="J61" t="n">
-        <v>-14.412</v>
+        <v>-9.359999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.49</v>
       </c>
       <c r="I62" t="n">
-        <v>1.1824</v>
+        <v>0.8457</v>
       </c>
       <c r="J62" t="n">
-        <v>30.7424</v>
+        <v>21.9882</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.31</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7917</v>
+        <v>0.6121</v>
       </c>
       <c r="J63" t="n">
-        <v>20.5842</v>
+        <v>15.9146</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.19</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4623</v>
+        <v>0.4492</v>
       </c>
       <c r="J64" t="n">
-        <v>12.0198</v>
+        <v>11.6792</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.11</v>
       </c>
       <c r="I65" t="n">
-        <v>0.2461</v>
+        <v>0.3198</v>
       </c>
       <c r="J65" t="n">
-        <v>6.3986</v>
+        <v>8.3148</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.1</v>
       </c>
       <c r="I66" t="n">
-        <v>0.2179</v>
+        <v>0.2931</v>
       </c>
       <c r="J66" t="n">
-        <v>5.6654</v>
+        <v>7.6206</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>0.0805</v>
+        <v>0.0428</v>
       </c>
       <c r="J67" t="n">
-        <v>2.093</v>
+        <v>1.1128</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.99</v>
       </c>
       <c r="I68" t="n">
-        <v>0.0459</v>
+        <v>0.003</v>
       </c>
       <c r="J68" t="n">
-        <v>1.1934</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3113</v>
+        <v>-0.2091</v>
       </c>
       <c r="J69" t="n">
-        <v>-8.0938</v>
+        <v>-5.4366</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.7</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4811</v>
+        <v>-0.3153</v>
       </c>
       <c r="J70" t="n">
-        <v>-12.5086</v>
+        <v>-8.197800000000001</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.67</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5229</v>
+        <v>-0.3438</v>
       </c>
       <c r="J71" t="n">
-        <v>-13.5954</v>
+        <v>-8.938800000000001</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>0.84</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.2006</v>
+        <v>-0.1685</v>
       </c>
       <c r="J72" t="n">
-        <v>-4.012</v>
+        <v>-3.37</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.84</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.2006</v>
+        <v>-0.1685</v>
       </c>
       <c r="J73" t="n">
-        <v>-4.012</v>
+        <v>-3.37</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.83</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2172</v>
+        <v>-0.1791</v>
       </c>
       <c r="J74" t="n">
-        <v>-4.344</v>
+        <v>-3.582</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.72</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4176</v>
+        <v>-0.285</v>
       </c>
       <c r="J75" t="n">
-        <v>-8.352</v>
+        <v>-5.7</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.53</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6866</v>
+        <v>-0.4629</v>
       </c>
       <c r="J76" t="n">
-        <v>-13.732</v>
+        <v>-9.257999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.67</v>
       </c>
       <c r="I77" t="n">
-        <v>1.4531</v>
+        <v>1.0315</v>
       </c>
       <c r="J77" t="n">
-        <v>29.062</v>
+        <v>20.63</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.51</v>
       </c>
       <c r="I78" t="n">
-        <v>1.1398</v>
+        <v>0.8411</v>
       </c>
       <c r="J78" t="n">
-        <v>22.796</v>
+        <v>16.822</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.4</v>
       </c>
       <c r="I79" t="n">
-        <v>0.8794999999999999</v>
+        <v>0.7089</v>
       </c>
       <c r="J79" t="n">
-        <v>17.59</v>
+        <v>14.178</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.28</v>
       </c>
       <c r="I80" t="n">
-        <v>0.5998</v>
+        <v>0.5546</v>
       </c>
       <c r="J80" t="n">
-        <v>11.996</v>
+        <v>11.092</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.19</v>
       </c>
       <c r="I81" t="n">
-        <v>0.3891</v>
+        <v>0.4277</v>
       </c>
       <c r="J81" t="n">
-        <v>7.782</v>
+        <v>8.554</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.17</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4038</v>
+        <v>0.4045</v>
       </c>
       <c r="J82" t="n">
-        <v>10.095</v>
+        <v>10.1125</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.98</v>
       </c>
       <c r="I83" t="n">
-        <v>0.0234</v>
+        <v>-0.0135</v>
       </c>
       <c r="J83" t="n">
-        <v>0.585</v>
+        <v>-0.3375</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.76</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.3904</v>
+        <v>-0.2569</v>
       </c>
       <c r="J84" t="n">
-        <v>-9.76</v>
+        <v>-6.4225</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.73</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4358</v>
+        <v>-0.2858</v>
       </c>
       <c r="J85" t="n">
-        <v>-10.895</v>
+        <v>-7.145</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.5</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.7397</v>
+        <v>-0.501</v>
       </c>
       <c r="J86" t="n">
-        <v>-18.4925</v>
+        <v>-12.525</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.53</v>
       </c>
       <c r="I87" t="n">
-        <v>1.2366</v>
+        <v>0.8847</v>
       </c>
       <c r="J87" t="n">
-        <v>30.915</v>
+        <v>22.1175</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.5</v>
       </c>
       <c r="I88" t="n">
-        <v>1.1764</v>
+        <v>0.8474</v>
       </c>
       <c r="J88" t="n">
-        <v>29.41</v>
+        <v>21.185</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.26</v>
       </c>
       <c r="I89" t="n">
-        <v>0.6105</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="J89" t="n">
-        <v>15.2625</v>
+        <v>13.52</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.2</v>
       </c>
       <c r="I90" t="n">
-        <v>0.459</v>
+        <v>0.4571</v>
       </c>
       <c r="J90" t="n">
-        <v>11.475</v>
+        <v>11.4275</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.98</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2531</v>
+        <v>-0.1675</v>
       </c>
       <c r="J91" t="n">
-        <v>-6.3275</v>
+        <v>-4.1875</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.3151</v>
+        <v>-0.267</v>
       </c>
       <c r="J92" t="n">
-        <v>-5.6718</v>
+        <v>-4.806</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.5204</v>
+        <v>-0.3987</v>
       </c>
       <c r="J93" t="n">
-        <v>-9.3672</v>
+        <v>-7.1766</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.51</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.6243</v>
+        <v>-0.4424</v>
       </c>
       <c r="J94" t="n">
-        <v>-11.2374</v>
+        <v>-7.9632</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.48</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.6742</v>
+        <v>-0.47</v>
       </c>
       <c r="J95" t="n">
-        <v>-12.1356</v>
+        <v>-8.460000000000001</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.42</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.7639</v>
+        <v>-0.527</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.7502</v>
+        <v>-9.486000000000001</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.71</v>
       </c>
       <c r="I97" t="n">
-        <v>1.4559</v>
+        <v>1.3258</v>
       </c>
       <c r="J97" t="n">
-        <v>26.2062</v>
+        <v>23.8644</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.63</v>
       </c>
       <c r="I98" t="n">
-        <v>1.2996</v>
+        <v>1.2357</v>
       </c>
       <c r="J98" t="n">
-        <v>23.3928</v>
+        <v>22.2426</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.55</v>
       </c>
       <c r="I99" t="n">
-        <v>1.1132</v>
+        <v>1.1462</v>
       </c>
       <c r="J99" t="n">
-        <v>20.0376</v>
+        <v>20.6316</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.53</v>
       </c>
       <c r="I100" t="n">
-        <v>1.0698</v>
+        <v>1.1231</v>
       </c>
       <c r="J100" t="n">
-        <v>19.2564</v>
+        <v>20.2158</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.46</v>
       </c>
       <c r="I101" t="n">
-        <v>0.9237</v>
+        <v>1.0386</v>
       </c>
       <c r="J101" t="n">
-        <v>16.6266</v>
+        <v>18.6948</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>0.73</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.2784</v>
+        <v>-0.2385</v>
       </c>
       <c r="J102" t="n">
-        <v>-4.7328</v>
+        <v>-4.0545</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.3399</v>
+        <v>-0.2809</v>
       </c>
       <c r="J103" t="n">
-        <v>-5.7783</v>
+        <v>-4.7753</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.67</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3707</v>
+        <v>-0.3015</v>
       </c>
       <c r="J104" t="n">
-        <v>-6.3019</v>
+        <v>-5.1255</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.5</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.6655</v>
+        <v>-0.4594</v>
       </c>
       <c r="J105" t="n">
-        <v>-11.3135</v>
+        <v>-7.8098</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.27</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.9725</v>
+        <v>-0.6808999999999999</v>
       </c>
       <c r="J106" t="n">
-        <v>-16.5325</v>
+        <v>-11.5753</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>2.66</v>
       </c>
       <c r="I107" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J107" t="n">
-        <v>35.0081</v>
+        <v>31.1746</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>2.2</v>
       </c>
       <c r="I108" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J108" t="n">
-        <v>35.0081</v>
+        <v>31.1746</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.48</v>
       </c>
       <c r="I109" t="n">
-        <v>0.9311</v>
+        <v>1.0541</v>
       </c>
       <c r="J109" t="n">
-        <v>15.8287</v>
+        <v>17.9197</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.13</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1811</v>
+        <v>0.2872</v>
       </c>
       <c r="J110" t="n">
-        <v>3.0787</v>
+        <v>4.8824</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.88</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6185</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.5145</v>
+        <v>-9.3653</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.47</v>
       </c>
       <c r="I112" t="n">
-        <v>1.2013</v>
+        <v>1.1233</v>
       </c>
       <c r="J112" t="n">
-        <v>32.4351</v>
+        <v>30.3291</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.28</v>
       </c>
       <c r="I113" t="n">
-        <v>0.7896</v>
+        <v>0.7712</v>
       </c>
       <c r="J113" t="n">
-        <v>21.3192</v>
+        <v>20.8224</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.23</v>
       </c>
       <c r="I114" t="n">
-        <v>0.669</v>
+        <v>0.6505</v>
       </c>
       <c r="J114" t="n">
-        <v>18.063</v>
+        <v>17.5635</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.84</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-0.5502</v>
       </c>
       <c r="J115" t="n">
-        <v>-16.4808</v>
+        <v>-14.8554</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.79</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.7331</v>
+        <v>-0.6814</v>
       </c>
       <c r="J116" t="n">
-        <v>-19.7937</v>
+        <v>-18.3978</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.08</v>
       </c>
       <c r="I117" t="n">
-        <v>0.2186</v>
+        <v>0.2228</v>
       </c>
       <c r="J117" t="n">
-        <v>5.9022</v>
+        <v>6.0156</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0382</v>
+        <v>0.0118</v>
       </c>
       <c r="J118" t="n">
-        <v>1.0314</v>
+        <v>0.3186</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.98</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0231</v>
+        <v>-0.0305</v>
       </c>
       <c r="J119" t="n">
-        <v>-0.6237</v>
+        <v>-0.8235</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1145</v>
+        <v>-0.0825</v>
       </c>
       <c r="J120" t="n">
-        <v>-3.0915</v>
+        <v>-2.2275</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.67</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5467</v>
+        <v>-0.3569</v>
       </c>
       <c r="J121" t="n">
-        <v>-14.7609</v>
+        <v>-9.6363</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.6</v>
       </c>
       <c r="I122" t="n">
-        <v>1.3563</v>
+        <v>1.2371</v>
       </c>
       <c r="J122" t="n">
-        <v>31.1949</v>
+        <v>28.4533</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.45</v>
       </c>
       <c r="I123" t="n">
-        <v>1.0551</v>
+        <v>1.0522</v>
       </c>
       <c r="J123" t="n">
-        <v>24.2673</v>
+        <v>24.2006</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.35</v>
       </c>
       <c r="I124" t="n">
-        <v>0.828</v>
+        <v>0.8761</v>
       </c>
       <c r="J124" t="n">
-        <v>19.044</v>
+        <v>20.1503</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.32</v>
       </c>
       <c r="I125" t="n">
-        <v>0.7398</v>
+        <v>0.8126</v>
       </c>
       <c r="J125" t="n">
-        <v>17.0154</v>
+        <v>18.6898</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.93</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4258</v>
+        <v>-0.3445</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.7934</v>
+        <v>-7.9235</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.17</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4299</v>
+        <v>0.4912</v>
       </c>
       <c r="J127" t="n">
-        <v>9.887700000000001</v>
+        <v>11.2976</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.98</v>
       </c>
       <c r="I128" t="n">
-        <v>0.0501</v>
+        <v>0.0016</v>
       </c>
       <c r="J128" t="n">
-        <v>1.1523</v>
+        <v>0.0368</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.76</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.3557</v>
+        <v>-0.2496</v>
       </c>
       <c r="J129" t="n">
-        <v>-8.181100000000001</v>
+        <v>-5.7408</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.54</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.6771</v>
+        <v>-0.4556</v>
       </c>
       <c r="J130" t="n">
-        <v>-15.5733</v>
+        <v>-10.4788</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.38</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.8725000000000001</v>
+        <v>-0.6032</v>
       </c>
       <c r="J131" t="n">
-        <v>-20.0675</v>
+        <v>-13.8736</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.56</v>
       </c>
       <c r="I132" t="n">
-        <v>1.3453</v>
+        <v>1.2205</v>
       </c>
       <c r="J132" t="n">
-        <v>33.6325</v>
+        <v>30.5125</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.19</v>
       </c>
       <c r="I133" t="n">
-        <v>0.5067</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="J133" t="n">
-        <v>12.6675</v>
+        <v>13.445</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.1</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2413</v>
+        <v>0.3048</v>
       </c>
       <c r="J134" t="n">
-        <v>6.0325</v>
+        <v>7.62</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.05</v>
       </c>
       <c r="I135" t="n">
-        <v>0.0877</v>
+        <v>0.1548</v>
       </c>
       <c r="J135" t="n">
-        <v>2.1925</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.05</v>
       </c>
       <c r="I136" t="n">
-        <v>0.0877</v>
+        <v>0.1548</v>
       </c>
       <c r="J136" t="n">
-        <v>2.1925</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.16</v>
       </c>
       <c r="I137" t="n">
-        <v>0.346</v>
+        <v>0.3837</v>
       </c>
       <c r="J137" t="n">
-        <v>8.65</v>
+        <v>9.592499999999999</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1213</v>
+        <v>-0.0829</v>
       </c>
       <c r="J138" t="n">
-        <v>-3.0325</v>
+        <v>-2.0725</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.91</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1866</v>
+        <v>-0.1167</v>
       </c>
       <c r="J139" t="n">
-        <v>-4.665</v>
+        <v>-2.9175</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.86</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2746</v>
+        <v>-0.1705</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.865</v>
+        <v>-4.2625</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.83</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3226</v>
+        <v>-0.2015</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.065</v>
+        <v>-5.0375</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.49</v>
       </c>
       <c r="I142" t="n">
-        <v>1.1982</v>
+        <v>1.1267</v>
       </c>
       <c r="J142" t="n">
-        <v>41.937</v>
+        <v>39.4345</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.45</v>
       </c>
       <c r="I143" t="n">
-        <v>1.1165</v>
+        <v>1.0753</v>
       </c>
       <c r="J143" t="n">
-        <v>39.0775</v>
+        <v>37.6355</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.25</v>
       </c>
       <c r="I144" t="n">
-        <v>0.6642</v>
+        <v>0.6757</v>
       </c>
       <c r="J144" t="n">
-        <v>23.247</v>
+        <v>23.6495</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.97</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2637</v>
+        <v>-0.184</v>
       </c>
       <c r="J145" t="n">
-        <v>-9.2295</v>
+        <v>-6.44</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.88</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5325</v>
+        <v>-0.4625</v>
       </c>
       <c r="J146" t="n">
-        <v>-18.6375</v>
+        <v>-16.1875</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.11</v>
       </c>
       <c r="I147" t="n">
-        <v>0.2941</v>
+        <v>0.3103</v>
       </c>
       <c r="J147" t="n">
-        <v>10.2935</v>
+        <v>10.8605</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.02</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1252</v>
+        <v>0.0994</v>
       </c>
       <c r="J148" t="n">
-        <v>4.382</v>
+        <v>3.479</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.8</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.3448</v>
+        <v>-0.2231</v>
       </c>
       <c r="J149" t="n">
-        <v>-12.068</v>
+        <v>-7.8085</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.79</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3604</v>
+        <v>-0.233</v>
       </c>
       <c r="J150" t="n">
-        <v>-12.614</v>
+        <v>-8.154999999999999</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.63</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5851</v>
+        <v>-0.3863</v>
       </c>
       <c r="J151" t="n">
-        <v>-20.4785</v>
+        <v>-13.5205</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.4</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5956</v>
+        <v>0.7309</v>
       </c>
       <c r="J152" t="n">
-        <v>20.846</v>
+        <v>25.5815</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.27</v>
       </c>
       <c r="I153" t="n">
-        <v>0.4276</v>
+        <v>0.5192</v>
       </c>
       <c r="J153" t="n">
-        <v>14.966</v>
+        <v>18.172</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.15</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2349</v>
+        <v>0.314</v>
       </c>
       <c r="J154" t="n">
-        <v>8.221500000000001</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.15</v>
       </c>
       <c r="I155" t="n">
-        <v>0.2349</v>
+        <v>0.314</v>
       </c>
       <c r="J155" t="n">
-        <v>8.221500000000001</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.83</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3717</v>
+        <v>-0.2258</v>
       </c>
       <c r="J156" t="n">
-        <v>-13.0095</v>
+        <v>-7.903</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.29</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8558</v>
+        <v>0.8262</v>
       </c>
       <c r="J157" t="n">
-        <v>29.953</v>
+        <v>28.917</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.18</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5884</v>
+        <v>0.5503</v>
       </c>
       <c r="J158" t="n">
-        <v>20.594</v>
+        <v>19.2605</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.02</v>
       </c>
       <c r="I159" t="n">
-        <v>0.0602</v>
+        <v>0.0854</v>
       </c>
       <c r="J159" t="n">
-        <v>2.107</v>
+        <v>2.989</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.87</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.5039</v>
+        <v>-0.4471</v>
       </c>
       <c r="J160" t="n">
-        <v>-17.6365</v>
+        <v>-15.6485</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.87</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5039</v>
+        <v>-0.4471</v>
       </c>
       <c r="J161" t="n">
-        <v>-17.6365</v>
+        <v>-15.6485</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>0.8</v>
       </c>
       <c r="I162" t="n">
-        <v>-0.1793</v>
+        <v>-0.1668</v>
       </c>
       <c r="J162" t="n">
-        <v>-3.586</v>
+        <v>-3.336</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.62</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.4615</v>
+        <v>-0.3542</v>
       </c>
       <c r="J163" t="n">
-        <v>-9.23</v>
+        <v>-7.084</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.55</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.5967</v>
+        <v>-0.4162</v>
       </c>
       <c r="J164" t="n">
-        <v>-11.934</v>
+        <v>-8.324</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.51</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.6584</v>
+        <v>-0.4532</v>
       </c>
       <c r="J165" t="n">
-        <v>-13.168</v>
+        <v>-9.064</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.46</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.73</v>
+        <v>-0.5004</v>
       </c>
       <c r="J166" t="n">
-        <v>-14.6</v>
+        <v>-10.008</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.73</v>
       </c>
       <c r="I167" t="n">
-        <v>1.5473</v>
+        <v>1.3683</v>
       </c>
       <c r="J167" t="n">
-        <v>30.946</v>
+        <v>27.366</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.41</v>
       </c>
       <c r="I168" t="n">
-        <v>0.8764999999999999</v>
+        <v>0.9782</v>
       </c>
       <c r="J168" t="n">
-        <v>17.53</v>
+        <v>19.564</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.4</v>
       </c>
       <c r="I169" t="n">
-        <v>0.8536</v>
+        <v>0.9604</v>
       </c>
       <c r="J169" t="n">
-        <v>17.072</v>
+        <v>19.208</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.37</v>
       </c>
       <c r="I170" t="n">
-        <v>0.7862</v>
+        <v>0.9009</v>
       </c>
       <c r="J170" t="n">
-        <v>15.724</v>
+        <v>18.018</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.33</v>
       </c>
       <c r="I171" t="n">
-        <v>0.6972</v>
+        <v>0.8137</v>
       </c>
       <c r="J171" t="n">
-        <v>13.944</v>
+        <v>16.274</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.47</v>
       </c>
       <c r="I172" t="n">
-        <v>0.6414</v>
+        <v>0.5745</v>
       </c>
       <c r="J172" t="n">
-        <v>15.3936</v>
+        <v>13.788</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.43</v>
       </c>
       <c r="I173" t="n">
-        <v>0.5931999999999999</v>
+        <v>0.5314</v>
       </c>
       <c r="J173" t="n">
-        <v>14.2368</v>
+        <v>12.7536</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.27</v>
       </c>
       <c r="I174" t="n">
-        <v>0.3666</v>
+        <v>0.3561</v>
       </c>
       <c r="J174" t="n">
-        <v>8.798400000000001</v>
+        <v>8.5464</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.15</v>
       </c>
       <c r="I175" t="n">
-        <v>0.1908</v>
+        <v>0.2096</v>
       </c>
       <c r="J175" t="n">
-        <v>4.5792</v>
+        <v>5.0304</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>1.14</v>
       </c>
       <c r="I176" t="n">
-        <v>0.1757</v>
+        <v>0.1964</v>
       </c>
       <c r="J176" t="n">
-        <v>4.2168</v>
+        <v>4.7136</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.19</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4165</v>
+        <v>0.3608</v>
       </c>
       <c r="J177" t="n">
-        <v>9.996</v>
+        <v>8.6592</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1</v>
       </c>
       <c r="I178" t="n">
-        <v>0.0655</v>
+        <v>0.0229</v>
       </c>
       <c r="J178" t="n">
-        <v>1.572</v>
+        <v>0.5496</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.85</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2604</v>
+        <v>-0.1731</v>
       </c>
       <c r="J179" t="n">
-        <v>-6.2496</v>
+        <v>-4.1544</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.76</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4059</v>
+        <v>-0.2624</v>
       </c>
       <c r="J180" t="n">
-        <v>-9.7416</v>
+        <v>-6.2976</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.55</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6861</v>
+        <v>-0.4604</v>
       </c>
       <c r="J181" t="n">
-        <v>-16.4664</v>
+        <v>-11.0496</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.24</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4503</v>
+        <v>0.5222</v>
       </c>
       <c r="J182" t="n">
-        <v>12.6084</v>
+        <v>14.6216</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.09</v>
       </c>
       <c r="I183" t="n">
-        <v>0.2222</v>
+        <v>0.2336</v>
       </c>
       <c r="J183" t="n">
-        <v>6.2216</v>
+        <v>6.5408</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.87</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2684</v>
+        <v>-0.1634</v>
       </c>
       <c r="J184" t="n">
-        <v>-7.5152</v>
+        <v>-4.5752</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.86</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2846</v>
+        <v>-0.174</v>
       </c>
       <c r="J185" t="n">
-        <v>-7.9688</v>
+        <v>-4.872</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.79</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3908</v>
+        <v>-0.2455</v>
       </c>
       <c r="J186" t="n">
-        <v>-10.9424</v>
+        <v>-6.874</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.27</v>
       </c>
       <c r="I187" t="n">
-        <v>0.7775</v>
+        <v>0.7544</v>
       </c>
       <c r="J187" t="n">
-        <v>21.77</v>
+        <v>21.1232</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.16</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4985</v>
+        <v>0.4808</v>
       </c>
       <c r="J188" t="n">
-        <v>13.958</v>
+        <v>13.4624</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.14</v>
       </c>
       <c r="I189" t="n">
-        <v>0.4415</v>
+        <v>0.4289</v>
       </c>
       <c r="J189" t="n">
-        <v>12.362</v>
+        <v>12.0092</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.01</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.0209</v>
+        <v>0.0313</v>
       </c>
       <c r="J190" t="n">
-        <v>-0.5852000000000001</v>
+        <v>0.8764</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.93</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3549</v>
+        <v>-0.2882</v>
       </c>
       <c r="J191" t="n">
-        <v>-9.937200000000001</v>
+        <v>-8.069599999999999</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1</v>
       </c>
       <c r="I192" t="n">
-        <v>0.1203</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="J192" t="n">
-        <v>2.5263</v>
+        <v>1.7955</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.98</v>
       </c>
       <c r="I193" t="n">
-        <v>0.0609</v>
+        <v>0.0138</v>
       </c>
       <c r="J193" t="n">
-        <v>1.2789</v>
+        <v>0.2898</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.86</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1624</v>
+        <v>-0.1447</v>
       </c>
       <c r="J194" t="n">
-        <v>-3.4104</v>
+        <v>-3.0387</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.57</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.6316000000000001</v>
+        <v>-0.424</v>
       </c>
       <c r="J195" t="n">
-        <v>-13.2636</v>
+        <v>-8.904</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.3</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.9618</v>
+        <v>-0.6738</v>
       </c>
       <c r="J196" t="n">
-        <v>-20.1978</v>
+        <v>-14.1498</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.64</v>
       </c>
       <c r="I197" t="n">
-        <v>1.4064</v>
+        <v>1.2738</v>
       </c>
       <c r="J197" t="n">
-        <v>29.5344</v>
+        <v>26.7498</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.54</v>
       </c>
       <c r="I198" t="n">
-        <v>1.212</v>
+        <v>1.1541</v>
       </c>
       <c r="J198" t="n">
-        <v>25.452</v>
+        <v>24.2361</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.31</v>
       </c>
       <c r="I199" t="n">
-        <v>0.6787</v>
+        <v>0.7806999999999999</v>
       </c>
       <c r="J199" t="n">
-        <v>14.2527</v>
+        <v>16.3947</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.29</v>
       </c>
       <c r="I200" t="n">
-        <v>0.6323</v>
+        <v>0.7357</v>
       </c>
       <c r="J200" t="n">
-        <v>13.2783</v>
+        <v>15.4497</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.16</v>
       </c>
       <c r="I201" t="n">
-        <v>0.3226</v>
+        <v>0.4215</v>
       </c>
       <c r="J201" t="n">
-        <v>6.7746</v>
+        <v>8.8515</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.14</v>
       </c>
       <c r="I202" t="n">
-        <v>0.2971</v>
+        <v>0.3286</v>
       </c>
       <c r="J202" t="n">
-        <v>8.021699999999999</v>
+        <v>8.872199999999999</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.97</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.0871</v>
+        <v>-0.0492</v>
       </c>
       <c r="J203" t="n">
-        <v>-2.3517</v>
+        <v>-1.3284</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.96</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1099</v>
+        <v>-0.0623</v>
       </c>
       <c r="J204" t="n">
-        <v>-2.9673</v>
+        <v>-1.6821</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.96</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1099</v>
+        <v>-0.0623</v>
       </c>
       <c r="J205" t="n">
-        <v>-2.9673</v>
+        <v>-1.6821</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.92</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.1892</v>
+        <v>-0.1106</v>
       </c>
       <c r="J206" t="n">
-        <v>-5.1084</v>
+        <v>-2.9862</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.4</v>
       </c>
       <c r="I207" t="n">
-        <v>1.0104</v>
+        <v>1.0026</v>
       </c>
       <c r="J207" t="n">
-        <v>27.2808</v>
+        <v>27.0702</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.32</v>
       </c>
       <c r="I208" t="n">
-        <v>0.8328</v>
+        <v>0.8365</v>
       </c>
       <c r="J208" t="n">
-        <v>22.4856</v>
+        <v>22.5855</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.17</v>
       </c>
       <c r="I209" t="n">
-        <v>0.4271</v>
+        <v>0.4858</v>
       </c>
       <c r="J209" t="n">
-        <v>11.5317</v>
+        <v>13.1166</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.1</v>
       </c>
       <c r="I210" t="n">
-        <v>0.2314</v>
+        <v>0.3002</v>
       </c>
       <c r="J210" t="n">
-        <v>6.2478</v>
+        <v>8.105399999999999</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1.06</v>
       </c>
       <c r="I211" t="n">
-        <v>0.1114</v>
+        <v>0.1817</v>
       </c>
       <c r="J211" t="n">
-        <v>3.0078</v>
+        <v>4.9059</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>0.83</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.1603</v>
+        <v>-0.1512</v>
       </c>
       <c r="J212" t="n">
-        <v>-3.3663</v>
+        <v>-3.1752</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.82</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.1762</v>
+        <v>-0.1624</v>
       </c>
       <c r="J213" t="n">
-        <v>-3.7002</v>
+        <v>-3.4104</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.62</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.5144</v>
+        <v>-0.3612</v>
       </c>
       <c r="J214" t="n">
-        <v>-10.8024</v>
+        <v>-7.5852</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.55</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.4256</v>
       </c>
       <c r="J215" t="n">
-        <v>-13.0935</v>
+        <v>-8.9376</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.38</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.85</v>
+        <v>-0.5859</v>
       </c>
       <c r="J216" t="n">
-        <v>-17.85</v>
+        <v>-12.3039</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.78</v>
       </c>
       <c r="I217" t="n">
-        <v>1.6315</v>
+        <v>1.4232</v>
       </c>
       <c r="J217" t="n">
-        <v>34.2615</v>
+        <v>29.8872</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.52</v>
       </c>
       <c r="I218" t="n">
-        <v>1.133</v>
+        <v>1.1205</v>
       </c>
       <c r="J218" t="n">
-        <v>23.793</v>
+        <v>23.5305</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.44</v>
       </c>
       <c r="I219" t="n">
-        <v>0.9374</v>
+        <v>1.0235</v>
       </c>
       <c r="J219" t="n">
-        <v>19.6854</v>
+        <v>21.4935</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.29</v>
       </c>
       <c r="I220" t="n">
-        <v>0.6028</v>
+        <v>0.7209</v>
       </c>
       <c r="J220" t="n">
-        <v>12.6588</v>
+        <v>15.1389</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.28</v>
       </c>
       <c r="I221" t="n">
-        <v>0.5804</v>
+        <v>0.6979</v>
       </c>
       <c r="J221" t="n">
-        <v>12.1884</v>
+        <v>14.6559</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.48</v>
       </c>
       <c r="I222" t="n">
-        <v>1.0998</v>
+        <v>1.0844</v>
       </c>
       <c r="J222" t="n">
-        <v>28.5948</v>
+        <v>28.1944</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.47</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0787</v>
+        <v>1.0722</v>
       </c>
       <c r="J223" t="n">
-        <v>28.0462</v>
+        <v>27.8772</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.47</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0787</v>
+        <v>1.0722</v>
       </c>
       <c r="J224" t="n">
-        <v>28.0462</v>
+        <v>27.8772</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.39</v>
       </c>
       <c r="I225" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.9517</v>
       </c>
       <c r="J225" t="n">
-        <v>23.3922</v>
+        <v>24.7442</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.02</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.0751</v>
+        <v>0.0083</v>
       </c>
       <c r="J226" t="n">
-        <v>-1.9526</v>
+        <v>0.2158</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.01</v>
       </c>
       <c r="I227" t="n">
-        <v>0.1467</v>
+        <v>0.1165</v>
       </c>
       <c r="J227" t="n">
-        <v>3.8142</v>
+        <v>3.029</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.96</v>
       </c>
       <c r="I228" t="n">
-        <v>0.009299999999999999</v>
+        <v>-0.0271</v>
       </c>
       <c r="J228" t="n">
-        <v>0.2418</v>
+        <v>-0.7046</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.64</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.5415</v>
+        <v>-0.3613</v>
       </c>
       <c r="J229" t="n">
-        <v>-14.079</v>
+        <v>-9.393800000000001</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.6</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.5966</v>
+        <v>-0.3988</v>
       </c>
       <c r="J230" t="n">
-        <v>-15.5116</v>
+        <v>-10.3688</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.59</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6101</v>
+        <v>-0.4081</v>
       </c>
       <c r="J231" t="n">
-        <v>-15.8626</v>
+        <v>-10.6106</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.52</v>
       </c>
       <c r="I232" t="n">
-        <v>1.2749</v>
+        <v>1.1738</v>
       </c>
       <c r="J232" t="n">
-        <v>31.8725</v>
+        <v>29.345</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.19</v>
       </c>
       <c r="I233" t="n">
-        <v>0.5271</v>
+        <v>0.54</v>
       </c>
       <c r="J233" t="n">
-        <v>13.1775</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.17</v>
       </c>
       <c r="I234" t="n">
-        <v>0.4581</v>
+        <v>0.492</v>
       </c>
       <c r="J234" t="n">
-        <v>11.4525</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.15</v>
       </c>
       <c r="I235" t="n">
-        <v>0.3961</v>
+        <v>0.4422</v>
       </c>
       <c r="J235" t="n">
-        <v>9.9025</v>
+        <v>11.055</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.84</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.6258</v>
+        <v>-0.5636</v>
       </c>
       <c r="J236" t="n">
-        <v>-15.645</v>
+        <v>-14.09</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.18</v>
       </c>
       <c r="I237" t="n">
-        <v>0.3773</v>
+        <v>0.4237</v>
       </c>
       <c r="J237" t="n">
-        <v>9.432499999999999</v>
+        <v>10.5925</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.15</v>
       </c>
       <c r="I238" t="n">
-        <v>0.3323</v>
+        <v>0.3657</v>
       </c>
       <c r="J238" t="n">
-        <v>8.307499999999999</v>
+        <v>9.1425</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.01</v>
       </c>
       <c r="I239" t="n">
-        <v>0.0725</v>
+        <v>0.0503</v>
       </c>
       <c r="J239" t="n">
-        <v>1.8125</v>
+        <v>1.2575</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.7</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.5075</v>
+        <v>-0.3287</v>
       </c>
       <c r="J240" t="n">
-        <v>-12.6875</v>
+        <v>-8.217499999999999</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.64</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5857</v>
+        <v>-0.3852</v>
       </c>
       <c r="J241" t="n">
-        <v>-14.6425</v>
+        <v>-9.630000000000001</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.5</v>
       </c>
       <c r="I242" t="n">
-        <v>1.3128</v>
+        <v>1.1948</v>
       </c>
       <c r="J242" t="n">
-        <v>45.948</v>
+        <v>41.818</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.23</v>
       </c>
       <c r="I243" t="n">
-        <v>0.7247</v>
+        <v>0.6856</v>
       </c>
       <c r="J243" t="n">
-        <v>25.3645</v>
+        <v>23.996</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.9</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.4111</v>
+        <v>-0.3569</v>
       </c>
       <c r="J244" t="n">
-        <v>-14.3885</v>
+        <v>-12.4915</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.6534</v>
+        <v>-0.6034</v>
       </c>
       <c r="J245" t="n">
-        <v>-22.869</v>
+        <v>-21.119</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.7</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.9137999999999999</v>
+        <v>-0.8818</v>
       </c>
       <c r="J246" t="n">
-        <v>-31.983</v>
+        <v>-30.863</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.31</v>
       </c>
       <c r="I247" t="n">
-        <v>0.5122</v>
+        <v>0.6119</v>
       </c>
       <c r="J247" t="n">
-        <v>17.927</v>
+        <v>21.4165</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.19</v>
       </c>
       <c r="I248" t="n">
-        <v>0.3467</v>
+        <v>0.4023</v>
       </c>
       <c r="J248" t="n">
-        <v>12.1345</v>
+        <v>14.0805</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.14</v>
       </c>
       <c r="I249" t="n">
-        <v>0.2694</v>
+        <v>0.3101</v>
       </c>
       <c r="J249" t="n">
-        <v>9.429</v>
+        <v>10.8535</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.93</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.1943</v>
+        <v>-0.1069</v>
       </c>
       <c r="J250" t="n">
-        <v>-6.8005</v>
+        <v>-3.7415</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.75</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4657</v>
+        <v>-0.2954</v>
       </c>
       <c r="J251" t="n">
-        <v>-16.2995</v>
+        <v>-10.339</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.4</v>
       </c>
       <c r="I252" t="n">
-        <v>1.0342</v>
+        <v>1.0151</v>
       </c>
       <c r="J252" t="n">
-        <v>31.026</v>
+        <v>30.453</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.26</v>
       </c>
       <c r="I253" t="n">
-        <v>0.7175</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="J253" t="n">
-        <v>21.525</v>
+        <v>21.306</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.2</v>
       </c>
       <c r="I254" t="n">
-        <v>0.5636</v>
+        <v>0.5662</v>
       </c>
       <c r="J254" t="n">
-        <v>16.908</v>
+        <v>16.986</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.02</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.008</v>
+        <v>0.0564</v>
       </c>
       <c r="J255" t="n">
-        <v>-0.24</v>
+        <v>1.692</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.3478</v>
+        <v>-0.2735</v>
       </c>
       <c r="J256" t="n">
-        <v>-10.434</v>
+        <v>-8.205</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.28</v>
       </c>
       <c r="I257" t="n">
-        <v>0.5198</v>
+        <v>0.613</v>
       </c>
       <c r="J257" t="n">
-        <v>15.594</v>
+        <v>18.39</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.02</v>
       </c>
       <c r="I258" t="n">
-        <v>0.1022</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="J258" t="n">
-        <v>3.066</v>
+        <v>2.463</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.8</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.3641</v>
+        <v>-0.2301</v>
       </c>
       <c r="J259" t="n">
-        <v>-10.923</v>
+        <v>-6.903</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.79</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.379</v>
+        <v>-0.2401</v>
       </c>
       <c r="J260" t="n">
-        <v>-11.37</v>
+        <v>-7.203</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.74</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4507</v>
+        <v>-0.2891</v>
       </c>
       <c r="J261" t="n">
-        <v>-13.521</v>
+        <v>-8.673</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4081/event_4081_evp_summary.xlsx
+++ b/database/event/4081/event_4081_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.2334</v>
+        <v>6.2715</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0003</v>
+        <v>1.0064</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1761</v>
+        <v>2.2307</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2334</v>
+        <v>6.2715</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0892</v>
+        <v>2.9863</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1442</v>
+        <v>3.2852</v>
       </c>
       <c r="H2" t="n">
-        <v>5.3982</v>
+        <v>4.9588</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8068</v>
+        <v>2.6777</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1442</v>
+        <v>3.2852</v>
       </c>
       <c r="K2" t="n">
         <v>99</v>
@@ -529,7 +529,7 @@
         <v>106</v>
       </c>
       <c r="M2" t="n">
-        <v>5.951000000000001</v>
+        <v>5.9629</v>
       </c>
       <c r="N2" t="n">
         <v>205</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.0903</v>
+        <v>5.1467</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8169</v>
+        <v>0.8259</v>
       </c>
       <c r="D3" t="n">
-        <v>1.66</v>
+        <v>1.7187</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0903</v>
+        <v>5.1467</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1643</v>
+        <v>3.0693</v>
       </c>
       <c r="G3" t="n">
-        <v>1.926</v>
+        <v>2.0774</v>
       </c>
       <c r="H3" t="n">
-        <v>5.6628</v>
+        <v>5.2325</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9444</v>
+        <v>2.8255</v>
       </c>
       <c r="J3" t="n">
-        <v>1.926</v>
+        <v>2.0774</v>
       </c>
       <c r="K3" t="n">
         <v>158</v>
@@ -575,7 +575,7 @@
         <v>95</v>
       </c>
       <c r="M3" t="n">
-        <v>4.8704</v>
+        <v>4.9029</v>
       </c>
       <c r="N3" t="n">
         <v>253</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.8088</v>
+        <v>4.9316</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.7914</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5329</v>
+        <v>1.6208</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8088</v>
+        <v>4.9316</v>
       </c>
       <c r="F4" t="n">
-        <v>4.4518</v>
+        <v>4.5807</v>
       </c>
       <c r="G4" t="n">
-        <v>0.357</v>
+        <v>0.3509</v>
       </c>
       <c r="H4" t="n">
-        <v>11.6945</v>
+        <v>11.0746</v>
       </c>
       <c r="I4" t="n">
-        <v>6.0806</v>
+        <v>5.9802</v>
       </c>
       <c r="J4" t="n">
-        <v>0.357</v>
+        <v>0.3509</v>
       </c>
       <c r="K4" t="n">
         <v>197</v>
@@ -621,7 +621,7 @@
         <v>56</v>
       </c>
       <c r="M4" t="n">
-        <v>6.4376</v>
+        <v>6.3311</v>
       </c>
       <c r="N4" t="n">
         <v>253</v>
@@ -630,35 +630,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.7611</v>
+        <v>4.7726</v>
       </c>
       <c r="C5" t="n">
-        <v>0.764</v>
+        <v>0.7659</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5114</v>
+        <v>1.5484</v>
       </c>
       <c r="E5" t="n">
-        <v>4.7611</v>
+        <v>4.7726</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2034</v>
+        <v>0.9756</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5577</v>
+        <v>3.797</v>
       </c>
       <c r="H5" t="n">
-        <v>5.8005</v>
+        <v>0.9756</v>
       </c>
       <c r="I5" t="n">
-        <v>3.016</v>
+        <v>0.5268</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5577</v>
+        <v>3.797</v>
       </c>
       <c r="K5" t="n">
         <v>99</v>
@@ -667,7 +667,7 @@
         <v>106</v>
       </c>
       <c r="M5" t="n">
-        <v>4.573700000000001</v>
+        <v>4.3238</v>
       </c>
       <c r="N5" t="n">
         <v>205</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.7558</v>
+        <v>4.7646</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7632</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>1.509</v>
+        <v>1.5447</v>
       </c>
       <c r="E6" t="n">
-        <v>4.7558</v>
+        <v>4.7646</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5089</v>
+        <v>3.4074</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2469</v>
+        <v>1.3572</v>
       </c>
       <c r="H6" t="n">
-        <v>6.877</v>
+        <v>6.3481</v>
       </c>
       <c r="I6" t="n">
-        <v>3.5757</v>
+        <v>3.4279</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2469</v>
+        <v>1.3572</v>
       </c>
       <c r="K6" t="n">
         <v>158</v>
@@ -713,7 +713,7 @@
         <v>95</v>
       </c>
       <c r="M6" t="n">
-        <v>4.8226</v>
+        <v>4.7851</v>
       </c>
       <c r="N6" t="n">
         <v>253</v>
@@ -722,35 +722,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.6819</v>
+        <v>4.6993</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7513</v>
+        <v>0.7541</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4756</v>
+        <v>1.515</v>
       </c>
       <c r="E7" t="n">
-        <v>4.6819</v>
+        <v>4.6993</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0072</v>
+        <v>3.1318</v>
       </c>
       <c r="G7" t="n">
-        <v>3.6747</v>
+        <v>1.5675</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0072</v>
+        <v>5.4388</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5237000000000001</v>
+        <v>2.9369</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6747</v>
+        <v>1.5675</v>
       </c>
       <c r="K7" t="n">
         <v>99</v>
@@ -759,7 +759,7 @@
         <v>106</v>
       </c>
       <c r="M7" t="n">
-        <v>4.1984</v>
+        <v>4.5044</v>
       </c>
       <c r="N7" t="n">
         <v>205</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.3465</v>
+        <v>4.4396</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6975</v>
+        <v>0.7124</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3242</v>
+        <v>1.3968</v>
       </c>
       <c r="E8" t="n">
-        <v>4.3465</v>
+        <v>4.4396</v>
       </c>
       <c r="F8" t="n">
-        <v>2.903</v>
+        <v>2.8316</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4434</v>
+        <v>1.608</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7421</v>
+        <v>4.4484</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4657</v>
+        <v>2.4021</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4434</v>
+        <v>1.608</v>
       </c>
       <c r="K8" t="n">
         <v>158</v>
@@ -805,7 +805,7 @@
         <v>95</v>
       </c>
       <c r="M8" t="n">
-        <v>3.9091</v>
+        <v>4.0101</v>
       </c>
       <c r="N8" t="n">
         <v>253</v>
@@ -814,93 +814,93 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>nex</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.2584</v>
+        <v>4.3209</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6834</v>
+        <v>0.6934</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2844</v>
+        <v>1.3428</v>
       </c>
       <c r="E9" t="n">
-        <v>4.2584</v>
+        <v>4.3209</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4245</v>
+        <v>4.5807</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8339</v>
+        <v>-0.2598</v>
       </c>
       <c r="H9" t="n">
-        <v>3.056</v>
+        <v>10.7442</v>
       </c>
       <c r="I9" t="n">
-        <v>1.589</v>
+        <v>5.8018</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8339</v>
+        <v>-0.2598</v>
       </c>
       <c r="K9" t="n">
-        <v>99</v>
+        <v>197</v>
       </c>
       <c r="L9" t="n">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4229</v>
+        <v>5.542</v>
       </c>
       <c r="N9" t="n">
-        <v>205</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>nex</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.2197</v>
+        <v>4.2518</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6772</v>
+        <v>0.6823</v>
       </c>
       <c r="D10" t="n">
-        <v>1.267</v>
+        <v>1.3113</v>
       </c>
       <c r="E10" t="n">
-        <v>4.2197</v>
+        <v>4.2518</v>
       </c>
       <c r="F10" t="n">
-        <v>4.4518</v>
+        <v>2.3375</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2321</v>
+        <v>1.9143</v>
       </c>
       <c r="H10" t="n">
-        <v>11.1554</v>
+        <v>2.8182</v>
       </c>
       <c r="I10" t="n">
-        <v>5.8003</v>
+        <v>1.5218</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2321</v>
+        <v>1.9143</v>
       </c>
       <c r="K10" t="n">
-        <v>197</v>
+        <v>99</v>
       </c>
       <c r="L10" t="n">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="M10" t="n">
-        <v>5.5682</v>
+        <v>3.4361</v>
       </c>
       <c r="N10" t="n">
-        <v>253</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.8049</v>
+        <v>3.742</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6106</v>
+        <v>0.6005</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0797</v>
+        <v>1.0792</v>
       </c>
       <c r="E11" t="n">
-        <v>3.8049</v>
+        <v>3.742</v>
       </c>
       <c r="F11" t="n">
-        <v>3.6854</v>
+        <v>3.6145</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1195</v>
+        <v>0.1275</v>
       </c>
       <c r="H11" t="n">
-        <v>7.4987</v>
+        <v>7.0315</v>
       </c>
       <c r="I11" t="n">
-        <v>3.899</v>
+        <v>3.797</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1195</v>
+        <v>0.1275</v>
       </c>
       <c r="K11" t="n">
         <v>145</v>
@@ -943,7 +943,7 @@
         <v>45</v>
       </c>
       <c r="M11" t="n">
-        <v>4.0185</v>
+        <v>3.9245</v>
       </c>
       <c r="N11" t="n">
         <v>190</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.4317</v>
+        <v>3.4147</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5507</v>
+        <v>0.548</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9112</v>
+        <v>0.9302</v>
       </c>
       <c r="E12" t="n">
-        <v>3.4317</v>
+        <v>3.4147</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3836</v>
+        <v>2.304</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0481</v>
+        <v>1.1107</v>
       </c>
       <c r="H12" t="n">
-        <v>2.912</v>
+        <v>2.7074</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5141</v>
+        <v>1.462</v>
       </c>
       <c r="J12" t="n">
-        <v>1.0481</v>
+        <v>1.1107</v>
       </c>
       <c r="K12" t="n">
         <v>99</v>
@@ -989,7 +989,7 @@
         <v>106</v>
       </c>
       <c r="M12" t="n">
-        <v>2.5622</v>
+        <v>2.5727</v>
       </c>
       <c r="N12" t="n">
         <v>205</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.893</v>
+        <v>2.7739</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4643</v>
+        <v>0.4451</v>
       </c>
       <c r="D13" t="n">
-        <v>0.668</v>
+        <v>0.6385</v>
       </c>
       <c r="E13" t="n">
-        <v>2.893</v>
+        <v>2.7739</v>
       </c>
       <c r="F13" t="n">
-        <v>3.4008</v>
+        <v>3.3132</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5078</v>
+        <v>-0.5393</v>
       </c>
       <c r="H13" t="n">
-        <v>6.4962</v>
+        <v>6.0373</v>
       </c>
       <c r="I13" t="n">
-        <v>3.3777</v>
+        <v>3.2601</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5078</v>
+        <v>-0.5393</v>
       </c>
       <c r="K13" t="n">
         <v>197</v>
@@ -1035,7 +1035,7 @@
         <v>56</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8699</v>
+        <v>2.7208</v>
       </c>
       <c r="N13" t="n">
         <v>253</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.4831</v>
+        <v>2.3733</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3985</v>
+        <v>0.3809</v>
       </c>
       <c r="D14" t="n">
-        <v>0.483</v>
+        <v>0.4562</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4831</v>
+        <v>2.3733</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6651</v>
+        <v>2.5877</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.182</v>
+        <v>-0.2144</v>
       </c>
       <c r="H14" t="n">
-        <v>3.904</v>
+        <v>3.6435</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0299</v>
+        <v>1.9674</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.182</v>
+        <v>-0.2144</v>
       </c>
       <c r="K14" t="n">
         <v>145</v>
@@ -1081,7 +1081,7 @@
         <v>45</v>
       </c>
       <c r="M14" t="n">
-        <v>1.8479</v>
+        <v>1.753</v>
       </c>
       <c r="N14" t="n">
         <v>190</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.0321</v>
+        <v>1.92</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3261</v>
+        <v>0.3081</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2794</v>
+        <v>0.2498</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0321</v>
+        <v>1.92</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4681</v>
+        <v>2.394</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.436</v>
+        <v>-0.474</v>
       </c>
       <c r="H15" t="n">
-        <v>3.2097</v>
+        <v>3.0044</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6689</v>
+        <v>1.6224</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.436</v>
+        <v>-0.474</v>
       </c>
       <c r="K15" t="n">
         <v>145</v>
@@ -1127,7 +1127,7 @@
         <v>45</v>
       </c>
       <c r="M15" t="n">
-        <v>1.2329</v>
+        <v>1.1484</v>
       </c>
       <c r="N15" t="n">
         <v>190</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9158</v>
+        <v>1.8097</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3074</v>
+        <v>0.2904</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2269</v>
+        <v>0.1996</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9158</v>
+        <v>1.8097</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5853</v>
+        <v>2.5071</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6695</v>
+        <v>-0.6974</v>
       </c>
       <c r="H16" t="n">
-        <v>3.6228</v>
+        <v>3.3776</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8837</v>
+        <v>1.8239</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6695</v>
+        <v>-0.6974</v>
       </c>
       <c r="K16" t="n">
         <v>145</v>
@@ -1173,7 +1173,7 @@
         <v>45</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2142</v>
+        <v>1.1265</v>
       </c>
       <c r="N16" t="n">
         <v>190</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.6004</v>
+        <v>1.4974</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2568</v>
+        <v>0.2403</v>
       </c>
       <c r="D17" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.0574</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6004</v>
+        <v>1.4974</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6004</v>
+        <v>1.4974</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6004</v>
+        <v>1.4974</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6004</v>
+        <v>1.4974</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.6004</v>
+        <v>1.4974</v>
       </c>
       <c r="N17" t="n">
         <v>131</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5395</v>
+        <v>1.4494</v>
       </c>
       <c r="C18" t="n">
-        <v>0.247</v>
+        <v>0.2326</v>
       </c>
       <c r="D18" t="n">
-        <v>0.057</v>
+        <v>0.0356</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5395</v>
+        <v>1.4494</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5395</v>
+        <v>1.4494</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5395</v>
+        <v>1.4494</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5395</v>
+        <v>1.4494</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.5395</v>
+        <v>1.4494</v>
       </c>
       <c r="N18" t="n">
         <v>131</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.4381</v>
+        <v>1.329</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2308</v>
+        <v>0.2133</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0112</v>
+        <v>-0.0192</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4381</v>
+        <v>1.329</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1868</v>
+        <v>2.1059</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7487</v>
+        <v>-0.7769</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2188</v>
+        <v>2.1059</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1536</v>
+        <v>1.1372</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7487</v>
+        <v>-0.7769</v>
       </c>
       <c r="K19" t="n">
         <v>145</v>
@@ -1311,7 +1311,7 @@
         <v>45</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4048999999999999</v>
+        <v>0.3603</v>
       </c>
       <c r="N19" t="n">
         <v>190</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.2111</v>
+        <v>1.1355</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1943</v>
+        <v>0.1822</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.1073</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2111</v>
+        <v>1.1355</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4803</v>
+        <v>1.4314</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2692</v>
+        <v>-0.2959</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4803</v>
+        <v>1.4314</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7697000000000001</v>
+        <v>0.773</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2692</v>
+        <v>-0.2959</v>
       </c>
       <c r="K20" t="n">
         <v>197</v>
@@ -1357,7 +1357,7 @@
         <v>56</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5005000000000001</v>
+        <v>0.4771</v>
       </c>
       <c r="N20" t="n">
         <v>253</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.0597</v>
+        <v>1.0436</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1701</v>
+        <v>0.1675</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1596</v>
+        <v>-0.1491</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0597</v>
+        <v>1.0436</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0597</v>
+        <v>1.0436</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0597</v>
+        <v>1.0436</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0597</v>
+        <v>1.0436</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.0597</v>
+        <v>1.0436</v>
       </c>
       <c r="N21" t="n">
         <v>85</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8424</v>
+        <v>0.7924</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1352</v>
+        <v>0.1272</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2577</v>
+        <v>-0.2635</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8424</v>
+        <v>0.7924</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8424</v>
+        <v>0.7924</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8424</v>
+        <v>0.7924</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8424</v>
+        <v>0.7924</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8424</v>
+        <v>0.7924</v>
       </c>
       <c r="N22" t="n">
         <v>90</v>
@@ -1458,93 +1458,93 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7809</v>
+        <v>0.7788</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1253</v>
+        <v>0.125</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2855</v>
+        <v>-0.2697</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7809</v>
+        <v>0.7788</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7809</v>
+        <v>1.437</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.6582</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7809</v>
+        <v>1.437</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7809</v>
+        <v>0.7759</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.6582</v>
       </c>
       <c r="K23" t="n">
-        <v>131</v>
+        <v>197</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7809</v>
+        <v>0.1177</v>
       </c>
       <c r="N23" t="n">
-        <v>131</v>
+        <v>253</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7439</v>
+        <v>0.6441</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1194</v>
+        <v>0.1034</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3022</v>
+        <v>-0.331</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7439</v>
+        <v>0.6441</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3712</v>
+        <v>0.6441</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6273</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.3712</v>
+        <v>0.6441</v>
       </c>
       <c r="I24" t="n">
-        <v>0.713</v>
+        <v>0.6441</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6273</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>197</v>
+        <v>131</v>
       </c>
       <c r="L24" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0857</v>
+        <v>0.6441</v>
       </c>
       <c r="N24" t="n">
-        <v>253</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4402</v>
+        <v>0.4179</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0706</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4393</v>
+        <v>-0.434</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4402</v>
+        <v>0.4179</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4402</v>
+        <v>0.4179</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4402</v>
+        <v>0.4179</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4402</v>
+        <v>0.4179</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4402</v>
+        <v>0.4179</v>
       </c>
       <c r="N25" t="n">
         <v>85</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2631</v>
+        <v>0.2579</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0422</v>
+        <v>0.0414</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5192</v>
+        <v>-0.5068</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2631</v>
+        <v>0.2579</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2631</v>
+        <v>0.2579</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2631</v>
+        <v>0.2579</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2631</v>
+        <v>0.2579</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2631</v>
+        <v>0.2579</v>
       </c>
       <c r="N26" t="n">
         <v>90</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2455</v>
+        <v>0.2032</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0394</v>
+        <v>0.0326</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5272</v>
+        <v>-0.5317</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2455</v>
+        <v>0.2032</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2455</v>
+        <v>0.2032</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2455</v>
+        <v>0.2032</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2455</v>
+        <v>0.2032</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2455</v>
+        <v>0.2032</v>
       </c>
       <c r="N27" t="n">
         <v>90</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2046</v>
+        <v>0.1667</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0328</v>
+        <v>0.0268</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5456</v>
+        <v>-0.5483</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2046</v>
+        <v>0.1667</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2046</v>
+        <v>0.1667</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2046</v>
+        <v>0.1667</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2046</v>
+        <v>0.1667</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2046</v>
+        <v>0.1667</v>
       </c>
       <c r="N28" t="n">
         <v>131</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1608</v>
+        <v>-0.2867</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0258</v>
+        <v>-0.046</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7106</v>
+        <v>-0.7547</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1608</v>
+        <v>-0.2867</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1608</v>
+        <v>-0.2867</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1608</v>
+        <v>-0.2867</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1608</v>
+        <v>-0.2867</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1608</v>
+        <v>-0.2867</v>
       </c>
       <c r="N29" t="n">
         <v>113</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2699</v>
+        <v>-0.2944</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0433</v>
+        <v>-0.0472</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7599</v>
+        <v>-0.7582</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2699</v>
+        <v>-0.2944</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2699</v>
+        <v>-0.2944</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2699</v>
+        <v>-0.2944</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2699</v>
+        <v>-0.2944</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2699</v>
+        <v>-0.2944</v>
       </c>
       <c r="N30" t="n">
         <v>90</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3743</v>
+        <v>-0.4045</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0601</v>
+        <v>-0.0649</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8070000000000001</v>
+        <v>-0.8083</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3743</v>
+        <v>-0.4045</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3743</v>
+        <v>-0.4045</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3743</v>
+        <v>-0.4045</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3743</v>
+        <v>-0.4045</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3743</v>
+        <v>-0.4045</v>
       </c>
       <c r="N31" t="n">
         <v>85</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3976</v>
+        <v>-0.4173</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0638</v>
+        <v>-0.067</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8175</v>
+        <v>-0.8142</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3976</v>
+        <v>-0.4173</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.3976</v>
+        <v>-0.4173</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3976</v>
+        <v>-0.4173</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3976</v>
+        <v>-0.4173</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3976</v>
+        <v>-0.4173</v>
       </c>
       <c r="N32" t="n">
         <v>90</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6659</v>
+        <v>-0.7056</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1069</v>
+        <v>-0.1132</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9386</v>
+        <v>-0.9454</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6659</v>
+        <v>-0.7056</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6659</v>
+        <v>-0.7056</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6659</v>
+        <v>-0.7056</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6659</v>
+        <v>-0.7056</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.6659</v>
+        <v>-0.7056</v>
       </c>
       <c r="N33" t="n">
         <v>131</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6758</v>
+        <v>-0.7416</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1084</v>
+        <v>-0.119</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9431</v>
+        <v>-0.9618</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6758</v>
+        <v>-0.7416</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6758</v>
+        <v>-0.7416</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6758</v>
+        <v>-0.7416</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6758</v>
+        <v>-0.7416</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6758</v>
+        <v>-0.7416</v>
       </c>
       <c r="N34" t="n">
         <v>113</v>
@@ -2010,124 +2010,124 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7349</v>
+        <v>-0.7741</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1179</v>
+        <v>-0.1242</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9698</v>
+        <v>-0.9766</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7349</v>
+        <v>-0.7741</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7349</v>
+        <v>-1.7043</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>0.9302</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7349</v>
+        <v>-1.7043</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7349</v>
+        <v>-0.9203</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>0.9302</v>
       </c>
       <c r="K35" t="n">
-        <v>85</v>
+        <v>158</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7349</v>
+        <v>0.00990000000000002</v>
       </c>
       <c r="N35" t="n">
-        <v>85</v>
+        <v>253</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>somebody</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7961</v>
+        <v>-0.7766999999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1278</v>
+        <v>-0.1246</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9974</v>
+        <v>-0.9778</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7961</v>
+        <v>-0.7766999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7961</v>
+        <v>-0.7766999999999999</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7961</v>
+        <v>-0.7766999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7961</v>
+        <v>-0.7766999999999999</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7961</v>
+        <v>-0.7766999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>113</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>somebody</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8804</v>
+        <v>-0.881</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1413</v>
+        <v>-0.1414</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0355</v>
+        <v>-1.0253</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8804</v>
+        <v>-0.881</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8804</v>
+        <v>-0.881</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8804</v>
+        <v>-0.881</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8804</v>
+        <v>-0.881</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8804</v>
+        <v>-0.881</v>
       </c>
       <c r="N37" t="n">
         <v>113</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.8855</v>
+        <v>-0.926</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1421</v>
+        <v>-0.1486</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0378</v>
+        <v>-1.0457</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.8855</v>
+        <v>-0.926</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.8855</v>
+        <v>-0.926</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.8855</v>
+        <v>-0.926</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.8855</v>
+        <v>-0.926</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.8855</v>
+        <v>-0.926</v>
       </c>
       <c r="N38" t="n">
         <v>85</v>
@@ -2194,32 +2194,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>captainMo</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.97</v>
+        <v>-0.9432</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1557</v>
+        <v>-0.1514</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0759</v>
+        <v>-1.0536</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.97</v>
+        <v>-0.9432</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.97</v>
+        <v>-0.9432</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.97</v>
+        <v>-0.9432</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.97</v>
+        <v>-0.9432</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.97</v>
+        <v>-0.9432</v>
       </c>
       <c r="N39" t="n">
         <v>113</v>
@@ -2240,47 +2240,47 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>captainMo</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.9789</v>
+        <v>-1.0154</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1571</v>
+        <v>-0.1629</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0799</v>
+        <v>-1.0864</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.9789</v>
+        <v>-1.0154</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.8244</v>
+        <v>-1.0154</v>
       </c>
       <c r="G40" t="n">
-        <v>0.8455</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.8244</v>
+        <v>-1.0154</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.9486</v>
+        <v>-1.0154</v>
       </c>
       <c r="J40" t="n">
-        <v>0.8455</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>158</v>
+        <v>113</v>
       </c>
       <c r="L40" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.1031</v>
+        <v>-1.0154</v>
       </c>
       <c r="N40" t="n">
-        <v>253</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-4.2965</v>
+        <v>-3.8509</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.6895</v>
+        <v>-0.618</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.5777</v>
+        <v>-2.3772</v>
       </c>
       <c r="E41" t="n">
-        <v>-4.2965</v>
+        <v>-3.8509</v>
       </c>
       <c r="F41" t="n">
-        <v>-4.1433</v>
+        <v>-3.7701</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.1532</v>
+        <v>-0.0808</v>
       </c>
       <c r="H41" t="n">
-        <v>-4.1433</v>
+        <v>-3.7701</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.1543</v>
+        <v>-2.0358</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.1532</v>
+        <v>-0.0808</v>
       </c>
       <c r="K41" t="n">
         <v>158</v>
@@ -2323,7 +2323,7 @@
         <v>95</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.3075</v>
+        <v>-2.1166</v>
       </c>
       <c r="N41" t="n">
         <v>253</v>
@@ -2429,10 +2429,10 @@
         <v>1.01</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1155</v>
+        <v>0.1</v>
       </c>
       <c r="J2" t="n">
-        <v>2.31</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.97</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0133</v>
+        <v>-0.0297</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.266</v>
+        <v>-0.594</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.76</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2493</v>
+        <v>-0.2687</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.986</v>
+        <v>-5.374</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.59</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4084</v>
+        <v>-0.4224</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.167999999999999</v>
+        <v>-8.448</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.48</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5107</v>
+        <v>-0.5188</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.214</v>
+        <v>-10.376</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1079</v>
+        <v>1.0998</v>
       </c>
       <c r="J7" t="n">
-        <v>22.158</v>
+        <v>21.996</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.4</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9691</v>
+        <v>0.9191</v>
       </c>
       <c r="J8" t="n">
-        <v>19.382</v>
+        <v>18.382</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.38</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9319</v>
+        <v>0.8827</v>
       </c>
       <c r="J9" t="n">
-        <v>18.638</v>
+        <v>17.654</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.33</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8278</v>
+        <v>0.7896</v>
       </c>
       <c r="J10" t="n">
-        <v>16.556</v>
+        <v>15.792</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.25</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6465</v>
+        <v>0.6293</v>
       </c>
       <c r="J11" t="n">
-        <v>12.93</v>
+        <v>12.586</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.35</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7109</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>21.327</v>
+        <v>20.427</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1197</v>
+        <v>0.1272</v>
       </c>
       <c r="J13" t="n">
-        <v>3.591</v>
+        <v>3.816</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.92</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1097</v>
+        <v>-0.1221</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.291</v>
+        <v>-3.663</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.85</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1859</v>
+        <v>-0.1999</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.577</v>
+        <v>-5.997</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.75</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2862</v>
+        <v>-0.2993</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.586</v>
+        <v>-8.978999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.64</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3074</v>
+        <v>1.3814</v>
       </c>
       <c r="J17" t="n">
-        <v>39.222</v>
+        <v>41.442</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.52</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1578</v>
+        <v>1.1657</v>
       </c>
       <c r="J18" t="n">
-        <v>34.734</v>
+        <v>34.971</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.16</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4547</v>
+        <v>0.4514</v>
       </c>
       <c r="J19" t="n">
-        <v>13.641</v>
+        <v>13.542</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.07</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2057</v>
+        <v>0.2223</v>
       </c>
       <c r="J20" t="n">
-        <v>6.171</v>
+        <v>6.669</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.8</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6839</v>
+        <v>-0.6316000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>-20.517</v>
+        <v>-18.948</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.23</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5472</v>
+        <v>0.5239</v>
       </c>
       <c r="J22" t="n">
-        <v>13.68</v>
+        <v>13.0975</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0293</v>
+        <v>0.0211</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7325</v>
+        <v>0.5275</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.74</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2821</v>
+        <v>-0.298</v>
       </c>
       <c r="J24" t="n">
-        <v>-7.0525</v>
+        <v>-7.45</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.73</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2917</v>
+        <v>-0.3074</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.2925</v>
+        <v>-7.685</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.66</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3584</v>
+        <v>-0.3719</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.960000000000001</v>
+        <v>-9.297499999999999</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.78</v>
       </c>
       <c r="I27" t="n">
-        <v>1.477</v>
+        <v>1.4624</v>
       </c>
       <c r="J27" t="n">
-        <v>36.925</v>
+        <v>36.56</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.45</v>
       </c>
       <c r="I28" t="n">
-        <v>1.0681</v>
+        <v>1.024</v>
       </c>
       <c r="J28" t="n">
-        <v>26.7025</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.34</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8729</v>
+        <v>0.8247</v>
       </c>
       <c r="J29" t="n">
-        <v>21.8225</v>
+        <v>20.6175</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.93</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3243</v>
+        <v>-0.3044</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.1075</v>
+        <v>-7.61</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.71</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.9093</v>
+        <v>-0.8300999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>-22.7325</v>
+        <v>-20.7525</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>2</v>
       </c>
       <c r="I32" t="n">
-        <v>1.0379</v>
+        <v>1.0295</v>
       </c>
       <c r="J32" t="n">
-        <v>20.758</v>
+        <v>20.59</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.74</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8177</v>
+        <v>0.8138</v>
       </c>
       <c r="J33" t="n">
-        <v>16.354</v>
+        <v>16.276</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.39</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4688</v>
+        <v>0.4861</v>
       </c>
       <c r="J34" t="n">
-        <v>9.375999999999999</v>
+        <v>9.722</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.24</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2987</v>
+        <v>0.3227</v>
       </c>
       <c r="J35" t="n">
-        <v>5.974</v>
+        <v>6.454</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.19</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2373</v>
+        <v>0.2628</v>
       </c>
       <c r="J36" t="n">
-        <v>4.746</v>
+        <v>5.256</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.07</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3143</v>
+        <v>0.2816</v>
       </c>
       <c r="J37" t="n">
-        <v>6.286</v>
+        <v>5.632</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.75</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2251</v>
+        <v>-0.2519</v>
       </c>
       <c r="J38" t="n">
-        <v>-4.502</v>
+        <v>-5.038</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.46</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.502</v>
+        <v>-0.5147</v>
       </c>
       <c r="J39" t="n">
-        <v>-10.04</v>
+        <v>-10.294</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.37</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.588</v>
+        <v>-0.5942</v>
       </c>
       <c r="J40" t="n">
-        <v>-11.76</v>
+        <v>-11.884</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.33</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6264999999999999</v>
+        <v>-0.6296</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.53</v>
+        <v>-12.592</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.01</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1007</v>
+        <v>0.0891</v>
       </c>
       <c r="J42" t="n">
-        <v>2.7189</v>
+        <v>2.4057</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.87</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1434</v>
+        <v>-0.1622</v>
       </c>
       <c r="J43" t="n">
-        <v>-3.8718</v>
+        <v>-4.3794</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.78</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.2335</v>
+        <v>-0.2524</v>
       </c>
       <c r="J44" t="n">
-        <v>-6.3045</v>
+        <v>-6.8148</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.72</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2904</v>
+        <v>-0.3082</v>
       </c>
       <c r="J45" t="n">
-        <v>-7.8408</v>
+        <v>-8.321400000000001</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.58</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4222</v>
+        <v>-0.4347</v>
       </c>
       <c r="J46" t="n">
-        <v>-11.3994</v>
+        <v>-11.7369</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.66</v>
       </c>
       <c r="I47" t="n">
-        <v>1.3154</v>
+        <v>1.2945</v>
       </c>
       <c r="J47" t="n">
-        <v>35.5158</v>
+        <v>34.9515</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.51</v>
       </c>
       <c r="I48" t="n">
-        <v>1.1317</v>
+        <v>1.0981</v>
       </c>
       <c r="J48" t="n">
-        <v>30.5559</v>
+        <v>29.6487</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.28</v>
       </c>
       <c r="I49" t="n">
-        <v>0.7286</v>
+        <v>0.6995</v>
       </c>
       <c r="J49" t="n">
-        <v>19.6722</v>
+        <v>18.8865</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.24</v>
       </c>
       <c r="I50" t="n">
-        <v>0.6368</v>
+        <v>0.6179</v>
       </c>
       <c r="J50" t="n">
-        <v>17.1936</v>
+        <v>16.6833</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.83</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6203</v>
+        <v>-0.572</v>
       </c>
       <c r="J51" t="n">
-        <v>-16.7481</v>
+        <v>-15.444</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.37</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7020999999999999</v>
+        <v>0.7771</v>
       </c>
       <c r="J52" t="n">
-        <v>21.063</v>
+        <v>23.313</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.34</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6619</v>
+        <v>0.7332</v>
       </c>
       <c r="J53" t="n">
-        <v>19.857</v>
+        <v>21.996</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.15</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3969</v>
+        <v>0.4336</v>
       </c>
       <c r="J54" t="n">
-        <v>11.907</v>
+        <v>13.008</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.11</v>
       </c>
       <c r="I55" t="n">
-        <v>0.331</v>
+        <v>0.3388</v>
       </c>
       <c r="J55" t="n">
-        <v>9.93</v>
+        <v>10.164</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2781</v>
+        <v>-0.2646</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.343</v>
+        <v>-7.938</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.14</v>
       </c>
       <c r="I57" t="n">
-        <v>0.354</v>
+        <v>0.359</v>
       </c>
       <c r="J57" t="n">
-        <v>10.62</v>
+        <v>10.77</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.98</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.023</v>
+        <v>-0.0328</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.984</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.86</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.164</v>
+        <v>-0.1805</v>
       </c>
       <c r="J59" t="n">
-        <v>-4.92</v>
+        <v>-5.415</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.71</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.312</v>
+        <v>-0.3269</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.359999999999999</v>
+        <v>-9.807</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.71</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.312</v>
+        <v>-0.3269</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.359999999999999</v>
+        <v>-9.807</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.49</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8457</v>
+        <v>0.9351</v>
       </c>
       <c r="J62" t="n">
-        <v>21.9882</v>
+        <v>24.3126</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.31</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6121</v>
+        <v>0.6806</v>
       </c>
       <c r="J63" t="n">
-        <v>15.9146</v>
+        <v>17.6956</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.19</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4492</v>
+        <v>0.498</v>
       </c>
       <c r="J64" t="n">
-        <v>11.6792</v>
+        <v>12.948</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.11</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3198</v>
+        <v>0.3295</v>
       </c>
       <c r="J65" t="n">
-        <v>8.3148</v>
+        <v>8.567</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.1</v>
       </c>
       <c r="I66" t="n">
-        <v>0.2931</v>
+        <v>0.3037</v>
       </c>
       <c r="J66" t="n">
-        <v>7.6206</v>
+        <v>7.8962</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>0.0428</v>
+        <v>0.031</v>
       </c>
       <c r="J67" t="n">
-        <v>1.1128</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.99</v>
       </c>
       <c r="I68" t="n">
-        <v>0.003</v>
+        <v>-0.0081</v>
       </c>
       <c r="J68" t="n">
-        <v>0.078</v>
+        <v>-0.2106</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2091</v>
+        <v>-0.227</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.4366</v>
+        <v>-5.902</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.7</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3153</v>
+        <v>-0.3313</v>
       </c>
       <c r="J70" t="n">
-        <v>-8.197800000000001</v>
+        <v>-8.613799999999999</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.67</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3438</v>
+        <v>-0.3588</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.938800000000001</v>
+        <v>-9.328799999999999</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>0.84</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.1685</v>
+        <v>-0.189</v>
       </c>
       <c r="J72" t="n">
-        <v>-3.37</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.84</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.1685</v>
+        <v>-0.189</v>
       </c>
       <c r="J73" t="n">
-        <v>-3.37</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.83</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1791</v>
+        <v>-0.1995</v>
       </c>
       <c r="J74" t="n">
-        <v>-3.582</v>
+        <v>-3.99</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.72</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.285</v>
+        <v>-0.3041</v>
       </c>
       <c r="J75" t="n">
-        <v>-5.7</v>
+        <v>-6.082</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.53</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4629</v>
+        <v>-0.4741</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.257999999999999</v>
+        <v>-9.481999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.67</v>
       </c>
       <c r="I77" t="n">
-        <v>1.0315</v>
+        <v>1.1404</v>
       </c>
       <c r="J77" t="n">
-        <v>20.63</v>
+        <v>22.808</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.51</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8411</v>
+        <v>0.9361</v>
       </c>
       <c r="J78" t="n">
-        <v>16.822</v>
+        <v>18.722</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.4</v>
       </c>
       <c r="I79" t="n">
-        <v>0.7089</v>
+        <v>0.7917</v>
       </c>
       <c r="J79" t="n">
-        <v>14.178</v>
+        <v>15.834</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.28</v>
       </c>
       <c r="I80" t="n">
-        <v>0.5546</v>
+        <v>0.6213</v>
       </c>
       <c r="J80" t="n">
-        <v>11.092</v>
+        <v>12.426</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.19</v>
       </c>
       <c r="I81" t="n">
-        <v>0.4277</v>
+        <v>0.4794</v>
       </c>
       <c r="J81" t="n">
-        <v>8.554</v>
+        <v>9.587999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.17</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4045</v>
+        <v>0.4316</v>
       </c>
       <c r="J82" t="n">
-        <v>10.1125</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.98</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.0135</v>
+        <v>-0.0254</v>
       </c>
       <c r="J83" t="n">
-        <v>-0.3375</v>
+        <v>-0.635</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.76</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2569</v>
+        <v>-0.2745</v>
       </c>
       <c r="J84" t="n">
-        <v>-6.4225</v>
+        <v>-6.8625</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.73</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2858</v>
+        <v>-0.3028</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.145</v>
+        <v>-7.57</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.5</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.501</v>
+        <v>-0.5084</v>
       </c>
       <c r="J86" t="n">
-        <v>-12.525</v>
+        <v>-12.71</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.53</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8847</v>
+        <v>0.9792</v>
       </c>
       <c r="J87" t="n">
-        <v>22.1175</v>
+        <v>24.48</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.5</v>
       </c>
       <c r="I88" t="n">
-        <v>0.8474</v>
+        <v>0.9391</v>
       </c>
       <c r="J88" t="n">
-        <v>21.185</v>
+        <v>23.4775</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.26</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.6026</v>
       </c>
       <c r="J89" t="n">
-        <v>13.52</v>
+        <v>15.065</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.2</v>
       </c>
       <c r="I90" t="n">
-        <v>0.4571</v>
+        <v>0.5087</v>
       </c>
       <c r="J90" t="n">
-        <v>11.4275</v>
+        <v>12.7175</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.98</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1675</v>
+        <v>-0.1508</v>
       </c>
       <c r="J91" t="n">
-        <v>-4.1875</v>
+        <v>-3.77</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.267</v>
+        <v>-0.2956</v>
       </c>
       <c r="J92" t="n">
-        <v>-4.806</v>
+        <v>-5.3208</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.3987</v>
+        <v>-0.4197</v>
       </c>
       <c r="J93" t="n">
-        <v>-7.1766</v>
+        <v>-7.5546</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.51</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.4424</v>
+        <v>-0.4612</v>
       </c>
       <c r="J94" t="n">
-        <v>-7.9632</v>
+        <v>-8.301600000000001</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.48</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.47</v>
+        <v>-0.4869</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.460000000000001</v>
+        <v>-8.764200000000001</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.42</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.527</v>
+        <v>-0.5397999999999999</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.486000000000001</v>
+        <v>-9.7164</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.71</v>
       </c>
       <c r="I97" t="n">
-        <v>1.3258</v>
+        <v>1.3146</v>
       </c>
       <c r="J97" t="n">
-        <v>23.8644</v>
+        <v>23.6628</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.63</v>
       </c>
       <c r="I98" t="n">
-        <v>1.2357</v>
+        <v>1.2179</v>
       </c>
       <c r="J98" t="n">
-        <v>22.2426</v>
+        <v>21.9222</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.55</v>
       </c>
       <c r="I99" t="n">
-        <v>1.1462</v>
+        <v>1.1209</v>
       </c>
       <c r="J99" t="n">
-        <v>20.6316</v>
+        <v>20.1762</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.53</v>
       </c>
       <c r="I100" t="n">
-        <v>1.1231</v>
+        <v>1.0959</v>
       </c>
       <c r="J100" t="n">
-        <v>20.2158</v>
+        <v>19.7262</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.46</v>
       </c>
       <c r="I101" t="n">
-        <v>1.0386</v>
+        <v>0.9994</v>
       </c>
       <c r="J101" t="n">
-        <v>18.6948</v>
+        <v>17.9892</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>0.73</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.2385</v>
+        <v>-0.2662</v>
       </c>
       <c r="J102" t="n">
-        <v>-4.0545</v>
+        <v>-4.5254</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.2809</v>
+        <v>-0.3066</v>
       </c>
       <c r="J103" t="n">
-        <v>-4.7753</v>
+        <v>-5.2122</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.67</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3015</v>
+        <v>-0.3261</v>
       </c>
       <c r="J104" t="n">
-        <v>-5.1255</v>
+        <v>-5.5437</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.5</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4594</v>
+        <v>-0.4758</v>
       </c>
       <c r="J105" t="n">
-        <v>-7.8098</v>
+        <v>-8.0886</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.27</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6808999999999999</v>
+        <v>-0.6797</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.5753</v>
+        <v>-11.5549</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>2.66</v>
       </c>
       <c r="I107" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J107" t="n">
-        <v>31.1746</v>
+        <v>32.9324</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>2.2</v>
       </c>
       <c r="I108" t="n">
-        <v>1.8338</v>
+        <v>1.8621</v>
       </c>
       <c r="J108" t="n">
-        <v>31.1746</v>
+        <v>31.6557</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.48</v>
       </c>
       <c r="I109" t="n">
-        <v>1.0541</v>
+        <v>1.02</v>
       </c>
       <c r="J109" t="n">
-        <v>17.9197</v>
+        <v>17.34</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.13</v>
       </c>
       <c r="I110" t="n">
-        <v>0.2872</v>
+        <v>0.3176</v>
       </c>
       <c r="J110" t="n">
-        <v>4.8824</v>
+        <v>5.3992</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.88</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.4961</v>
       </c>
       <c r="J111" t="n">
-        <v>-9.3653</v>
+        <v>-8.4337</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.47</v>
       </c>
       <c r="I112" t="n">
-        <v>1.1233</v>
+        <v>1.0807</v>
       </c>
       <c r="J112" t="n">
-        <v>30.3291</v>
+        <v>29.1789</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.28</v>
       </c>
       <c r="I113" t="n">
-        <v>0.7712</v>
+        <v>0.7288</v>
       </c>
       <c r="J113" t="n">
-        <v>20.8224</v>
+        <v>19.6776</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.23</v>
       </c>
       <c r="I114" t="n">
-        <v>0.6505</v>
+        <v>0.6223</v>
       </c>
       <c r="J114" t="n">
-        <v>17.5635</v>
+        <v>16.8021</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.84</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5502</v>
+        <v>-0.5175</v>
       </c>
       <c r="J115" t="n">
-        <v>-14.8554</v>
+        <v>-13.9725</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.79</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6814</v>
+        <v>-0.6345</v>
       </c>
       <c r="J116" t="n">
-        <v>-18.3978</v>
+        <v>-17.1315</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.08</v>
       </c>
       <c r="I117" t="n">
-        <v>0.2228</v>
+        <v>0.2254</v>
       </c>
       <c r="J117" t="n">
-        <v>6.0156</v>
+        <v>6.0858</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0118</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="J118" t="n">
-        <v>0.3186</v>
+        <v>0.2268</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.98</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0305</v>
+        <v>-0.0386</v>
       </c>
       <c r="J119" t="n">
-        <v>-0.8235</v>
+        <v>-1.0422</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.0825</v>
+        <v>-0.0948</v>
       </c>
       <c r="J120" t="n">
-        <v>-2.2275</v>
+        <v>-2.5596</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.67</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3569</v>
+        <v>-0.369</v>
       </c>
       <c r="J121" t="n">
-        <v>-9.6363</v>
+        <v>-9.962999999999999</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.6</v>
       </c>
       <c r="I122" t="n">
-        <v>1.2371</v>
+        <v>1.2121</v>
       </c>
       <c r="J122" t="n">
-        <v>28.4533</v>
+        <v>27.8783</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.45</v>
       </c>
       <c r="I123" t="n">
-        <v>1.0522</v>
+        <v>1.0087</v>
       </c>
       <c r="J123" t="n">
-        <v>24.2006</v>
+        <v>23.2001</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.35</v>
       </c>
       <c r="I124" t="n">
-        <v>0.8761</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="J124" t="n">
-        <v>20.1503</v>
+        <v>19.1153</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.32</v>
       </c>
       <c r="I125" t="n">
-        <v>0.8126</v>
+        <v>0.7748</v>
       </c>
       <c r="J125" t="n">
-        <v>18.6898</v>
+        <v>17.8204</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.93</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3445</v>
+        <v>-0.3186</v>
       </c>
       <c r="J126" t="n">
-        <v>-7.9235</v>
+        <v>-7.3278</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.17</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4912</v>
+        <v>0.4616</v>
       </c>
       <c r="J127" t="n">
-        <v>11.2976</v>
+        <v>10.6168</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.98</v>
       </c>
       <c r="I128" t="n">
-        <v>0.0016</v>
+        <v>-0.0141</v>
       </c>
       <c r="J128" t="n">
-        <v>0.0368</v>
+        <v>-0.3243</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.76</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2496</v>
+        <v>-0.2689</v>
       </c>
       <c r="J129" t="n">
-        <v>-5.7408</v>
+        <v>-6.1847</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.54</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4556</v>
+        <v>-0.467</v>
       </c>
       <c r="J130" t="n">
-        <v>-10.4788</v>
+        <v>-10.741</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.38</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.6032</v>
+        <v>-0.605</v>
       </c>
       <c r="J131" t="n">
-        <v>-13.8736</v>
+        <v>-13.915</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.56</v>
       </c>
       <c r="I132" t="n">
-        <v>1.2205</v>
+        <v>1.1883</v>
       </c>
       <c r="J132" t="n">
-        <v>30.5125</v>
+        <v>29.7075</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.19</v>
       </c>
       <c r="I133" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="J133" t="n">
-        <v>13.445</v>
+        <v>13.1175</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.1</v>
       </c>
       <c r="I134" t="n">
-        <v>0.3048</v>
+        <v>0.3118</v>
       </c>
       <c r="J134" t="n">
-        <v>7.62</v>
+        <v>7.795</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.05</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1548</v>
+        <v>0.1712</v>
       </c>
       <c r="J135" t="n">
-        <v>3.87</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.05</v>
       </c>
       <c r="I136" t="n">
-        <v>0.1548</v>
+        <v>0.1712</v>
       </c>
       <c r="J136" t="n">
-        <v>3.87</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.16</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3837</v>
+        <v>0.3785</v>
       </c>
       <c r="J137" t="n">
-        <v>9.592499999999999</v>
+        <v>9.4625</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.0829</v>
+        <v>-0.095</v>
       </c>
       <c r="J138" t="n">
-        <v>-2.0725</v>
+        <v>-2.375</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.91</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1167</v>
+        <v>-0.1306</v>
       </c>
       <c r="J139" t="n">
-        <v>-2.9175</v>
+        <v>-3.265</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.86</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1705</v>
+        <v>-0.1855</v>
       </c>
       <c r="J140" t="n">
-        <v>-4.2625</v>
+        <v>-4.6375</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.83</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2015</v>
+        <v>-0.2167</v>
       </c>
       <c r="J141" t="n">
-        <v>-5.0375</v>
+        <v>-5.4175</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.49</v>
       </c>
       <c r="I142" t="n">
-        <v>1.1267</v>
+        <v>1.0888</v>
       </c>
       <c r="J142" t="n">
-        <v>39.4345</v>
+        <v>38.108</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.45</v>
       </c>
       <c r="I143" t="n">
-        <v>1.0753</v>
+        <v>1.031</v>
       </c>
       <c r="J143" t="n">
-        <v>37.6355</v>
+        <v>36.085</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.25</v>
       </c>
       <c r="I144" t="n">
-        <v>0.6757</v>
+        <v>0.6492</v>
       </c>
       <c r="J144" t="n">
-        <v>23.6495</v>
+        <v>22.722</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.97</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.184</v>
+        <v>-0.1729</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.44</v>
+        <v>-6.0515</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.88</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4625</v>
+        <v>-0.4337</v>
       </c>
       <c r="J146" t="n">
-        <v>-16.1875</v>
+        <v>-15.1795</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.11</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3103</v>
+        <v>0.3038</v>
       </c>
       <c r="J147" t="n">
-        <v>10.8605</v>
+        <v>10.633</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.02</v>
       </c>
       <c r="I148" t="n">
-        <v>0.0994</v>
+        <v>0.0975</v>
       </c>
       <c r="J148" t="n">
-        <v>3.479</v>
+        <v>3.4125</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.8</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2231</v>
+        <v>-0.2401</v>
       </c>
       <c r="J149" t="n">
-        <v>-7.8085</v>
+        <v>-8.403499999999999</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.79</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.233</v>
+        <v>-0.2499</v>
       </c>
       <c r="J150" t="n">
-        <v>-8.154999999999999</v>
+        <v>-8.746499999999999</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.63</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3863</v>
+        <v>-0.3987</v>
       </c>
       <c r="J151" t="n">
-        <v>-13.5205</v>
+        <v>-13.9545</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.4</v>
       </c>
       <c r="I152" t="n">
-        <v>0.7309</v>
+        <v>0.7094</v>
       </c>
       <c r="J152" t="n">
-        <v>25.5815</v>
+        <v>24.829</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.27</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5192</v>
+        <v>0.5163</v>
       </c>
       <c r="J153" t="n">
-        <v>18.172</v>
+        <v>18.0705</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.15</v>
       </c>
       <c r="I154" t="n">
-        <v>0.314</v>
+        <v>0.3239</v>
       </c>
       <c r="J154" t="n">
-        <v>10.99</v>
+        <v>11.3365</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.15</v>
       </c>
       <c r="I155" t="n">
-        <v>0.314</v>
+        <v>0.3239</v>
       </c>
       <c r="J155" t="n">
-        <v>10.99</v>
+        <v>11.3365</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.83</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2258</v>
+        <v>-0.2356</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.903</v>
+        <v>-8.246</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.29</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8262</v>
+        <v>0.7715</v>
       </c>
       <c r="J157" t="n">
-        <v>28.917</v>
+        <v>27.0025</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.18</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5503</v>
+        <v>0.528</v>
       </c>
       <c r="J158" t="n">
-        <v>19.2605</v>
+        <v>18.48</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.02</v>
       </c>
       <c r="I159" t="n">
-        <v>0.0854</v>
+        <v>0.094</v>
       </c>
       <c r="J159" t="n">
-        <v>2.989</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.87</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4471</v>
+        <v>-0.4287</v>
       </c>
       <c r="J160" t="n">
-        <v>-15.6485</v>
+        <v>-15.0045</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.87</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4471</v>
+        <v>-0.4287</v>
       </c>
       <c r="J161" t="n">
-        <v>-15.6485</v>
+        <v>-15.0045</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>0.8</v>
       </c>
       <c r="I162" t="n">
-        <v>-0.1668</v>
+        <v>-0.1963</v>
       </c>
       <c r="J162" t="n">
-        <v>-3.336</v>
+        <v>-3.926</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.62</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.3542</v>
+        <v>-0.3755</v>
       </c>
       <c r="J163" t="n">
-        <v>-7.084</v>
+        <v>-7.51</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.55</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.4162</v>
+        <v>-0.4347</v>
       </c>
       <c r="J164" t="n">
-        <v>-8.324</v>
+        <v>-8.694000000000001</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.51</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.4532</v>
+        <v>-0.4695</v>
       </c>
       <c r="J165" t="n">
-        <v>-9.064</v>
+        <v>-9.390000000000001</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.46</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5004</v>
+        <v>-0.5135</v>
       </c>
       <c r="J166" t="n">
-        <v>-10.008</v>
+        <v>-10.27</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.73</v>
       </c>
       <c r="I167" t="n">
-        <v>1.3683</v>
+        <v>1.356</v>
       </c>
       <c r="J167" t="n">
-        <v>27.366</v>
+        <v>27.12</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.41</v>
       </c>
       <c r="I168" t="n">
-        <v>0.9782</v>
+        <v>0.9298999999999999</v>
       </c>
       <c r="J168" t="n">
-        <v>19.564</v>
+        <v>18.598</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.4</v>
       </c>
       <c r="I169" t="n">
-        <v>0.9604</v>
+        <v>0.9121</v>
       </c>
       <c r="J169" t="n">
-        <v>19.208</v>
+        <v>18.242</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.37</v>
       </c>
       <c r="I170" t="n">
-        <v>0.9009</v>
+        <v>0.8566</v>
       </c>
       <c r="J170" t="n">
-        <v>18.018</v>
+        <v>17.132</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.33</v>
       </c>
       <c r="I171" t="n">
-        <v>0.8137</v>
+        <v>0.78</v>
       </c>
       <c r="J171" t="n">
-        <v>16.274</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.47</v>
       </c>
       <c r="I172" t="n">
-        <v>0.5745</v>
+        <v>0.5821</v>
       </c>
       <c r="J172" t="n">
-        <v>13.788</v>
+        <v>13.9704</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.43</v>
       </c>
       <c r="I173" t="n">
-        <v>0.5314</v>
+        <v>0.5415</v>
       </c>
       <c r="J173" t="n">
-        <v>12.7536</v>
+        <v>12.996</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.27</v>
       </c>
       <c r="I174" t="n">
-        <v>0.3561</v>
+        <v>0.3735</v>
       </c>
       <c r="J174" t="n">
-        <v>8.5464</v>
+        <v>8.964</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.15</v>
       </c>
       <c r="I175" t="n">
-        <v>0.2096</v>
+        <v>0.2302</v>
       </c>
       <c r="J175" t="n">
-        <v>5.0304</v>
+        <v>5.5248</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>1.14</v>
       </c>
       <c r="I176" t="n">
-        <v>0.1964</v>
+        <v>0.2171</v>
       </c>
       <c r="J176" t="n">
-        <v>4.7136</v>
+        <v>5.2104</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.19</v>
       </c>
       <c r="I177" t="n">
-        <v>0.3608</v>
+        <v>0.3559</v>
       </c>
       <c r="J177" t="n">
-        <v>8.6592</v>
+        <v>8.541600000000001</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1</v>
       </c>
       <c r="I178" t="n">
-        <v>0.0229</v>
+        <v>0.0169</v>
       </c>
       <c r="J178" t="n">
-        <v>0.5496</v>
+        <v>0.4056</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.85</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1731</v>
+        <v>-0.19</v>
       </c>
       <c r="J179" t="n">
-        <v>-4.1544</v>
+        <v>-4.56</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.76</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2624</v>
+        <v>-0.2788</v>
       </c>
       <c r="J180" t="n">
-        <v>-6.2976</v>
+        <v>-6.6912</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.55</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4604</v>
+        <v>-0.4692</v>
       </c>
       <c r="J181" t="n">
-        <v>-11.0496</v>
+        <v>-11.2608</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.24</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5222</v>
+        <v>0.5087</v>
       </c>
       <c r="J182" t="n">
-        <v>14.6216</v>
+        <v>14.2436</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.09</v>
       </c>
       <c r="I183" t="n">
-        <v>0.2336</v>
+        <v>0.2383</v>
       </c>
       <c r="J183" t="n">
-        <v>6.5408</v>
+        <v>6.6724</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.87</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1634</v>
+        <v>-0.1775</v>
       </c>
       <c r="J184" t="n">
-        <v>-4.5752</v>
+        <v>-4.97</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.86</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.174</v>
+        <v>-0.1882</v>
       </c>
       <c r="J185" t="n">
-        <v>-4.872</v>
+        <v>-5.2696</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.79</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2455</v>
+        <v>-0.2595</v>
       </c>
       <c r="J186" t="n">
-        <v>-6.874</v>
+        <v>-7.266</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.27</v>
       </c>
       <c r="I187" t="n">
-        <v>0.7544</v>
+        <v>0.7128</v>
       </c>
       <c r="J187" t="n">
-        <v>21.1232</v>
+        <v>19.9584</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.16</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4808</v>
+        <v>0.4691</v>
       </c>
       <c r="J188" t="n">
-        <v>13.4624</v>
+        <v>13.1348</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.14</v>
       </c>
       <c r="I189" t="n">
-        <v>0.4289</v>
+        <v>0.422</v>
       </c>
       <c r="J189" t="n">
-        <v>12.0092</v>
+        <v>11.816</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.01</v>
       </c>
       <c r="I190" t="n">
-        <v>0.0313</v>
+        <v>0.0436</v>
       </c>
       <c r="J190" t="n">
-        <v>0.8764</v>
+        <v>1.2208</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.93</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2882</v>
+        <v>-0.2791</v>
       </c>
       <c r="J191" t="n">
-        <v>-8.069599999999999</v>
+        <v>-7.8148</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1</v>
       </c>
       <c r="I192" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.0624</v>
       </c>
       <c r="J192" t="n">
-        <v>1.7955</v>
+        <v>1.3104</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.98</v>
       </c>
       <c r="I193" t="n">
-        <v>0.0138</v>
+        <v>-0.0089</v>
       </c>
       <c r="J193" t="n">
-        <v>0.2898</v>
+        <v>-0.1869</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.86</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1447</v>
+        <v>-0.1657</v>
       </c>
       <c r="J194" t="n">
-        <v>-3.0387</v>
+        <v>-3.4797</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.57</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.424</v>
+        <v>-0.4377</v>
       </c>
       <c r="J195" t="n">
-        <v>-8.904</v>
+        <v>-9.191700000000001</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.3</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.6738</v>
+        <v>-0.6706</v>
       </c>
       <c r="J196" t="n">
-        <v>-14.1498</v>
+        <v>-14.0826</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.64</v>
       </c>
       <c r="I197" t="n">
-        <v>1.2738</v>
+        <v>1.2535</v>
       </c>
       <c r="J197" t="n">
-        <v>26.7498</v>
+        <v>26.3235</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.54</v>
       </c>
       <c r="I198" t="n">
-        <v>1.1541</v>
+        <v>1.1252</v>
       </c>
       <c r="J198" t="n">
-        <v>24.2361</v>
+        <v>23.6292</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.31</v>
       </c>
       <c r="I199" t="n">
-        <v>0.7806999999999999</v>
+        <v>0.7487</v>
       </c>
       <c r="J199" t="n">
-        <v>16.3947</v>
+        <v>15.7227</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.29</v>
       </c>
       <c r="I200" t="n">
-        <v>0.7357</v>
+        <v>0.7089</v>
       </c>
       <c r="J200" t="n">
-        <v>15.4497</v>
+        <v>14.8869</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.16</v>
       </c>
       <c r="I201" t="n">
-        <v>0.4215</v>
+        <v>0.4283</v>
       </c>
       <c r="J201" t="n">
-        <v>8.8515</v>
+        <v>8.994300000000001</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.14</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3286</v>
+        <v>0.3301</v>
       </c>
       <c r="J202" t="n">
-        <v>8.872199999999999</v>
+        <v>8.912699999999999</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.97</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.0492</v>
+        <v>-0.0575</v>
       </c>
       <c r="J203" t="n">
-        <v>-1.3284</v>
+        <v>-1.5525</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.96</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.0623</v>
+        <v>-0.0718</v>
       </c>
       <c r="J204" t="n">
-        <v>-1.6821</v>
+        <v>-1.9386</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.96</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.0623</v>
+        <v>-0.0718</v>
       </c>
       <c r="J205" t="n">
-        <v>-1.6821</v>
+        <v>-1.9386</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.92</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.1106</v>
+        <v>-0.1228</v>
       </c>
       <c r="J206" t="n">
-        <v>-2.9862</v>
+        <v>-3.3156</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.4</v>
       </c>
       <c r="I207" t="n">
-        <v>1.0026</v>
+        <v>0.9465</v>
       </c>
       <c r="J207" t="n">
-        <v>27.0702</v>
+        <v>25.5555</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.32</v>
       </c>
       <c r="I208" t="n">
-        <v>0.8365</v>
+        <v>0.7912</v>
       </c>
       <c r="J208" t="n">
-        <v>22.5855</v>
+        <v>21.3624</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.17</v>
       </c>
       <c r="I209" t="n">
-        <v>0.4858</v>
+        <v>0.4783</v>
       </c>
       <c r="J209" t="n">
-        <v>13.1166</v>
+        <v>12.9141</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.1</v>
       </c>
       <c r="I210" t="n">
-        <v>0.3002</v>
+        <v>0.3086</v>
       </c>
       <c r="J210" t="n">
-        <v>8.105399999999999</v>
+        <v>8.3322</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1.06</v>
       </c>
       <c r="I211" t="n">
-        <v>0.1817</v>
+        <v>0.198</v>
       </c>
       <c r="J211" t="n">
-        <v>4.9059</v>
+        <v>5.346</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>0.83</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.1512</v>
+        <v>-0.1776</v>
       </c>
       <c r="J212" t="n">
-        <v>-3.1752</v>
+        <v>-3.7296</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.82</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.1624</v>
+        <v>-0.1887</v>
       </c>
       <c r="J213" t="n">
-        <v>-3.4104</v>
+        <v>-3.9627</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.62</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.3612</v>
+        <v>-0.3808</v>
       </c>
       <c r="J214" t="n">
-        <v>-7.5852</v>
+        <v>-7.9968</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.55</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4256</v>
+        <v>-0.4419</v>
       </c>
       <c r="J215" t="n">
-        <v>-8.9376</v>
+        <v>-9.2799</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.38</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5859</v>
+        <v>-0.5913</v>
       </c>
       <c r="J216" t="n">
-        <v>-12.3039</v>
+        <v>-12.4173</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.78</v>
       </c>
       <c r="I217" t="n">
-        <v>1.4232</v>
+        <v>1.4147</v>
       </c>
       <c r="J217" t="n">
-        <v>29.8872</v>
+        <v>29.7087</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.52</v>
       </c>
       <c r="I218" t="n">
-        <v>1.1205</v>
+        <v>1.0909</v>
       </c>
       <c r="J218" t="n">
-        <v>23.5305</v>
+        <v>22.9089</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.44</v>
       </c>
       <c r="I219" t="n">
-        <v>1.0235</v>
+        <v>0.9791</v>
       </c>
       <c r="J219" t="n">
-        <v>21.4935</v>
+        <v>20.5611</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.29</v>
       </c>
       <c r="I220" t="n">
-        <v>0.7209</v>
+        <v>0.6987</v>
       </c>
       <c r="J220" t="n">
-        <v>15.1389</v>
+        <v>14.6727</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.28</v>
       </c>
       <c r="I221" t="n">
-        <v>0.6979</v>
+        <v>0.6784</v>
       </c>
       <c r="J221" t="n">
-        <v>14.6559</v>
+        <v>14.2464</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.48</v>
       </c>
       <c r="I222" t="n">
-        <v>1.0844</v>
+        <v>1.0481</v>
       </c>
       <c r="J222" t="n">
-        <v>28.1944</v>
+        <v>27.2506</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.47</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0722</v>
+        <v>1.0338</v>
       </c>
       <c r="J223" t="n">
-        <v>27.8772</v>
+        <v>26.8788</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.47</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0722</v>
+        <v>1.0338</v>
       </c>
       <c r="J224" t="n">
-        <v>27.8772</v>
+        <v>26.8788</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.39</v>
       </c>
       <c r="I225" t="n">
-        <v>0.9517</v>
+        <v>0.9014</v>
       </c>
       <c r="J225" t="n">
-        <v>24.7442</v>
+        <v>23.4364</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.02</v>
       </c>
       <c r="I226" t="n">
-        <v>0.0083</v>
+        <v>0.0403</v>
       </c>
       <c r="J226" t="n">
-        <v>0.2158</v>
+        <v>1.0478</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.01</v>
       </c>
       <c r="I227" t="n">
-        <v>0.1165</v>
+        <v>0.1008</v>
       </c>
       <c r="J227" t="n">
-        <v>3.029</v>
+        <v>2.6208</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.96</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.0271</v>
+        <v>-0.0445</v>
       </c>
       <c r="J228" t="n">
-        <v>-0.7046</v>
+        <v>-1.157</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.64</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.3613</v>
+        <v>-0.3775</v>
       </c>
       <c r="J229" t="n">
-        <v>-9.393800000000001</v>
+        <v>-9.815</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.6</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3988</v>
+        <v>-0.4133</v>
       </c>
       <c r="J230" t="n">
-        <v>-10.3688</v>
+        <v>-10.7458</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.59</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4081</v>
+        <v>-0.4222</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.6106</v>
+        <v>-10.9772</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.52</v>
       </c>
       <c r="I232" t="n">
-        <v>1.1738</v>
+        <v>1.1376</v>
       </c>
       <c r="J232" t="n">
-        <v>29.345</v>
+        <v>28.44</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.19</v>
       </c>
       <c r="I233" t="n">
-        <v>0.54</v>
+        <v>0.5261</v>
       </c>
       <c r="J233" t="n">
-        <v>13.5</v>
+        <v>13.1525</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.17</v>
       </c>
       <c r="I234" t="n">
-        <v>0.492</v>
+        <v>0.4824</v>
       </c>
       <c r="J234" t="n">
-        <v>12.3</v>
+        <v>12.06</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.15</v>
       </c>
       <c r="I235" t="n">
-        <v>0.4422</v>
+        <v>0.4371</v>
       </c>
       <c r="J235" t="n">
-        <v>11.055</v>
+        <v>10.9275</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.84</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5636</v>
+        <v>-0.5269</v>
       </c>
       <c r="J236" t="n">
-        <v>-14.09</v>
+        <v>-13.1725</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.18</v>
       </c>
       <c r="I237" t="n">
-        <v>0.4237</v>
+        <v>0.4154</v>
       </c>
       <c r="J237" t="n">
-        <v>10.5925</v>
+        <v>10.385</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.15</v>
       </c>
       <c r="I238" t="n">
-        <v>0.3657</v>
+        <v>0.3613</v>
       </c>
       <c r="J238" t="n">
-        <v>9.1425</v>
+        <v>9.032500000000001</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.01</v>
       </c>
       <c r="I239" t="n">
-        <v>0.0503</v>
+        <v>0.0523</v>
       </c>
       <c r="J239" t="n">
-        <v>1.2575</v>
+        <v>1.3075</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.7</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3287</v>
+        <v>-0.3418</v>
       </c>
       <c r="J240" t="n">
-        <v>-8.217499999999999</v>
+        <v>-8.545</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.64</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3852</v>
+        <v>-0.3962</v>
       </c>
       <c r="J241" t="n">
-        <v>-9.630000000000001</v>
+        <v>-9.904999999999999</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.5</v>
       </c>
       <c r="I242" t="n">
-        <v>1.1948</v>
+        <v>1.1515</v>
       </c>
       <c r="J242" t="n">
-        <v>41.818</v>
+        <v>40.3025</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.23</v>
       </c>
       <c r="I243" t="n">
-        <v>0.6856</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="J243" t="n">
-        <v>23.996</v>
+        <v>22.6345</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.9</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.3569</v>
+        <v>-0.3476</v>
       </c>
       <c r="J244" t="n">
-        <v>-12.4915</v>
+        <v>-12.166</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.6034</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="J245" t="n">
-        <v>-21.119</v>
+        <v>-19.9535</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.7</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.8818</v>
+        <v>-0.8147</v>
       </c>
       <c r="J246" t="n">
-        <v>-30.863</v>
+        <v>-28.5145</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.31</v>
       </c>
       <c r="I247" t="n">
-        <v>0.6119</v>
+        <v>0.5965</v>
       </c>
       <c r="J247" t="n">
-        <v>21.4165</v>
+        <v>20.8775</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.19</v>
       </c>
       <c r="I248" t="n">
-        <v>0.4023</v>
+        <v>0.4035</v>
       </c>
       <c r="J248" t="n">
-        <v>14.0805</v>
+        <v>14.1225</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.14</v>
       </c>
       <c r="I249" t="n">
-        <v>0.3101</v>
+        <v>0.3167</v>
       </c>
       <c r="J249" t="n">
-        <v>10.8535</v>
+        <v>11.0845</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.93</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.1069</v>
+        <v>-0.1168</v>
       </c>
       <c r="J250" t="n">
-        <v>-3.7415</v>
+        <v>-4.088</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.75</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2954</v>
+        <v>-0.3065</v>
       </c>
       <c r="J251" t="n">
-        <v>-10.339</v>
+        <v>-10.7275</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.4</v>
       </c>
       <c r="I252" t="n">
-        <v>1.0151</v>
+        <v>0.9576</v>
       </c>
       <c r="J252" t="n">
-        <v>30.453</v>
+        <v>28.728</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.26</v>
       </c>
       <c r="I253" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.6776</v>
       </c>
       <c r="J253" t="n">
-        <v>21.306</v>
+        <v>20.328</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.2</v>
       </c>
       <c r="I254" t="n">
-        <v>0.5662</v>
+        <v>0.5493</v>
       </c>
       <c r="J254" t="n">
-        <v>16.986</v>
+        <v>16.479</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.02</v>
       </c>
       <c r="I255" t="n">
-        <v>0.0564</v>
+        <v>0.074</v>
       </c>
       <c r="J255" t="n">
-        <v>1.692</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.2735</v>
+        <v>-0.2613</v>
       </c>
       <c r="J256" t="n">
-        <v>-8.205</v>
+        <v>-7.839</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.28</v>
       </c>
       <c r="I257" t="n">
-        <v>0.613</v>
+        <v>0.5883</v>
       </c>
       <c r="J257" t="n">
-        <v>18.39</v>
+        <v>17.649</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.02</v>
       </c>
       <c r="I258" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0849</v>
       </c>
       <c r="J258" t="n">
-        <v>2.463</v>
+        <v>2.547</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.8</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.2301</v>
+        <v>-0.2455</v>
       </c>
       <c r="J259" t="n">
-        <v>-6.903</v>
+        <v>-7.365</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.79</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2401</v>
+        <v>-0.2553</v>
       </c>
       <c r="J260" t="n">
-        <v>-7.203</v>
+        <v>-7.659</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.74</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.2891</v>
+        <v>-0.3034</v>
       </c>
       <c r="J261" t="n">
-        <v>-8.673</v>
+        <v>-9.102</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4081/event_4081_evp_summary.xlsx
+++ b/database/event/4081/event_4081_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.2715</v>
+        <v>6.2422</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0064</v>
+        <v>1.0017</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2307</v>
+        <v>2.2378</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2715</v>
+        <v>6.2422</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9863</v>
+        <v>2.9835</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2852</v>
+        <v>3.2587</v>
       </c>
       <c r="H2" t="n">
-        <v>4.9588</v>
+        <v>4.7588</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6777</v>
+        <v>2.6719</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2852</v>
+        <v>3.2587</v>
       </c>
       <c r="K2" t="n">
         <v>99</v>
@@ -529,7 +529,7 @@
         <v>106</v>
       </c>
       <c r="M2" t="n">
-        <v>5.9629</v>
+        <v>5.9306</v>
       </c>
       <c r="N2" t="n">
         <v>205</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.1467</v>
+        <v>5.0075</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8259</v>
+        <v>0.8036</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7187</v>
+        <v>1.6754</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1467</v>
+        <v>5.0075</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0693</v>
+        <v>3.0109</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0774</v>
+        <v>1.9966</v>
       </c>
       <c r="H3" t="n">
-        <v>5.2325</v>
+        <v>4.8615</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8255</v>
+        <v>2.7296</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0774</v>
+        <v>1.9966</v>
       </c>
       <c r="K3" t="n">
         <v>158</v>
@@ -575,7 +575,7 @@
         <v>95</v>
       </c>
       <c r="M3" t="n">
-        <v>4.9029</v>
+        <v>4.7262</v>
       </c>
       <c r="N3" t="n">
         <v>253</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.9316</v>
+        <v>4.866</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7914</v>
+        <v>0.7809</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6208</v>
+        <v>1.6109</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9316</v>
+        <v>4.866</v>
       </c>
       <c r="F4" t="n">
-        <v>4.5807</v>
+        <v>4.5631</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3509</v>
+        <v>0.3029</v>
       </c>
       <c r="H4" t="n">
-        <v>11.0746</v>
+        <v>10.6891</v>
       </c>
       <c r="I4" t="n">
-        <v>5.9802</v>
+        <v>6.0016</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3509</v>
+        <v>0.3029</v>
       </c>
       <c r="K4" t="n">
         <v>197</v>
@@ -621,7 +621,7 @@
         <v>56</v>
       </c>
       <c r="M4" t="n">
-        <v>6.3311</v>
+        <v>6.3045</v>
       </c>
       <c r="N4" t="n">
         <v>253</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.7726</v>
+        <v>4.7106</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7659</v>
+        <v>0.7559</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5484</v>
+        <v>1.5401</v>
       </c>
       <c r="E5" t="n">
-        <v>4.7726</v>
+        <v>4.7106</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9756</v>
+        <v>0.9411</v>
       </c>
       <c r="G5" t="n">
-        <v>3.797</v>
+        <v>3.7695</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9756</v>
+        <v>0.9411</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5268</v>
+        <v>0.5284</v>
       </c>
       <c r="J5" t="n">
-        <v>3.797</v>
+        <v>3.7695</v>
       </c>
       <c r="K5" t="n">
         <v>99</v>
@@ -667,7 +667,7 @@
         <v>106</v>
       </c>
       <c r="M5" t="n">
-        <v>4.3238</v>
+        <v>4.2979</v>
       </c>
       <c r="N5" t="n">
         <v>205</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.7646</v>
+        <v>4.6483</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7645999999999999</v>
+        <v>0.7459</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5447</v>
+        <v>1.5117</v>
       </c>
       <c r="E6" t="n">
-        <v>4.7646</v>
+        <v>4.6483</v>
       </c>
       <c r="F6" t="n">
-        <v>3.4074</v>
+        <v>3.0987</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3572</v>
+        <v>1.5496</v>
       </c>
       <c r="H6" t="n">
-        <v>6.3481</v>
+        <v>5.1914</v>
       </c>
       <c r="I6" t="n">
-        <v>3.4279</v>
+        <v>2.9148</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3572</v>
+        <v>1.5496</v>
       </c>
       <c r="K6" t="n">
-        <v>158</v>
+        <v>99</v>
       </c>
       <c r="L6" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="M6" t="n">
-        <v>4.7851</v>
+        <v>4.4644</v>
       </c>
       <c r="N6" t="n">
-        <v>253</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.6993</v>
+        <v>4.5767</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7541</v>
+        <v>0.7344000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>1.515</v>
+        <v>1.4791</v>
       </c>
       <c r="E7" t="n">
-        <v>4.6993</v>
+        <v>4.5767</v>
       </c>
       <c r="F7" t="n">
-        <v>3.1318</v>
+        <v>3.2807</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5675</v>
+        <v>1.296</v>
       </c>
       <c r="H7" t="n">
-        <v>5.4388</v>
+        <v>5.8744</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9369</v>
+        <v>3.2983</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5675</v>
+        <v>1.296</v>
       </c>
       <c r="K7" t="n">
-        <v>99</v>
+        <v>158</v>
       </c>
       <c r="L7" t="n">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="M7" t="n">
-        <v>4.5044</v>
+        <v>4.5943</v>
       </c>
       <c r="N7" t="n">
-        <v>205</v>
+        <v>253</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.4396</v>
+        <v>4.4516</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7124</v>
+        <v>0.7144</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3968</v>
+        <v>1.4221</v>
       </c>
       <c r="E8" t="n">
-        <v>4.4396</v>
+        <v>4.4516</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8316</v>
+        <v>2.8236</v>
       </c>
       <c r="G8" t="n">
-        <v>1.608</v>
+        <v>1.628</v>
       </c>
       <c r="H8" t="n">
-        <v>4.4484</v>
+        <v>4.1584</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4021</v>
+        <v>2.3348</v>
       </c>
       <c r="J8" t="n">
-        <v>1.608</v>
+        <v>1.628</v>
       </c>
       <c r="K8" t="n">
         <v>158</v>
@@ -805,7 +805,7 @@
         <v>95</v>
       </c>
       <c r="M8" t="n">
-        <v>4.0101</v>
+        <v>3.9628</v>
       </c>
       <c r="N8" t="n">
         <v>253</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.3209</v>
+        <v>4.3067</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6934</v>
+        <v>0.6911</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3428</v>
+        <v>1.3561</v>
       </c>
       <c r="E9" t="n">
-        <v>4.3209</v>
+        <v>4.3067</v>
       </c>
       <c r="F9" t="n">
-        <v>4.5807</v>
+        <v>4.5406</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2598</v>
+        <v>-0.2339</v>
       </c>
       <c r="H9" t="n">
-        <v>10.7442</v>
+        <v>10.6049</v>
       </c>
       <c r="I9" t="n">
-        <v>5.8018</v>
+        <v>5.9543</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2598</v>
+        <v>-0.2339</v>
       </c>
       <c r="K9" t="n">
         <v>197</v>
@@ -851,7 +851,7 @@
         <v>56</v>
       </c>
       <c r="M9" t="n">
-        <v>5.542</v>
+        <v>5.7204</v>
       </c>
       <c r="N9" t="n">
         <v>253</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.2518</v>
+        <v>4.2489</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6823</v>
+        <v>0.6818</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3113</v>
+        <v>1.3298</v>
       </c>
       <c r="E10" t="n">
-        <v>4.2518</v>
+        <v>4.2489</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3375</v>
+        <v>2.436</v>
       </c>
       <c r="G10" t="n">
-        <v>1.9143</v>
+        <v>1.8129</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8182</v>
+        <v>2.7033</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5218</v>
+        <v>1.5178</v>
       </c>
       <c r="J10" t="n">
-        <v>1.9143</v>
+        <v>1.8129</v>
       </c>
       <c r="K10" t="n">
         <v>99</v>
@@ -897,7 +897,7 @@
         <v>106</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4361</v>
+        <v>3.3307</v>
       </c>
       <c r="N10" t="n">
         <v>205</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.742</v>
+        <v>3.6048</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6005</v>
+        <v>0.5785</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0792</v>
+        <v>1.0364</v>
       </c>
       <c r="E11" t="n">
-        <v>3.742</v>
+        <v>3.6048</v>
       </c>
       <c r="F11" t="n">
-        <v>3.6145</v>
+        <v>3.5102</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1275</v>
+        <v>0.0946</v>
       </c>
       <c r="H11" t="n">
-        <v>7.0315</v>
+        <v>6.7361</v>
       </c>
       <c r="I11" t="n">
-        <v>3.797</v>
+        <v>3.7821</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1275</v>
+        <v>0.0946</v>
       </c>
       <c r="K11" t="n">
         <v>145</v>
@@ -943,7 +943,7 @@
         <v>45</v>
       </c>
       <c r="M11" t="n">
-        <v>3.9245</v>
+        <v>3.8767</v>
       </c>
       <c r="N11" t="n">
         <v>190</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.4147</v>
+        <v>3.465</v>
       </c>
       <c r="C12" t="n">
-        <v>0.548</v>
+        <v>0.556</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9302</v>
+        <v>0.9727</v>
       </c>
       <c r="E12" t="n">
-        <v>3.4147</v>
+        <v>3.465</v>
       </c>
       <c r="F12" t="n">
-        <v>2.304</v>
+        <v>2.381</v>
       </c>
       <c r="G12" t="n">
-        <v>1.1107</v>
+        <v>1.084</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7074</v>
+        <v>2.4968</v>
       </c>
       <c r="I12" t="n">
-        <v>1.462</v>
+        <v>1.4019</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1107</v>
+        <v>1.084</v>
       </c>
       <c r="K12" t="n">
         <v>99</v>
@@ -989,7 +989,7 @@
         <v>106</v>
       </c>
       <c r="M12" t="n">
-        <v>2.5727</v>
+        <v>2.4859</v>
       </c>
       <c r="N12" t="n">
         <v>205</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7739</v>
+        <v>2.7419</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4451</v>
+        <v>0.44</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6385</v>
+        <v>0.6433</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7739</v>
+        <v>2.7419</v>
       </c>
       <c r="F13" t="n">
-        <v>3.3132</v>
+        <v>3.2478</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5393</v>
+        <v>-0.5059</v>
       </c>
       <c r="H13" t="n">
-        <v>6.0373</v>
+        <v>5.751</v>
       </c>
       <c r="I13" t="n">
-        <v>3.2601</v>
+        <v>3.229</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5393</v>
+        <v>-0.5059</v>
       </c>
       <c r="K13" t="n">
         <v>197</v>
@@ -1035,7 +1035,7 @@
         <v>56</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7208</v>
+        <v>2.7231</v>
       </c>
       <c r="N13" t="n">
         <v>253</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3733</v>
+        <v>2.4107</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3809</v>
+        <v>0.3869</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4562</v>
+        <v>0.4924</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3733</v>
+        <v>2.4107</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5877</v>
+        <v>2.6021</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2144</v>
+        <v>-0.1914</v>
       </c>
       <c r="H14" t="n">
-        <v>3.6435</v>
+        <v>3.3266</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9674</v>
+        <v>1.8678</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2144</v>
+        <v>-0.1914</v>
       </c>
       <c r="K14" t="n">
         <v>145</v>
@@ -1081,7 +1081,7 @@
         <v>45</v>
       </c>
       <c r="M14" t="n">
-        <v>1.753</v>
+        <v>1.6764</v>
       </c>
       <c r="N14" t="n">
         <v>190</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.92</v>
+        <v>2.0404</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3081</v>
+        <v>0.3274</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2498</v>
+        <v>0.3237</v>
       </c>
       <c r="E15" t="n">
-        <v>1.92</v>
+        <v>2.0404</v>
       </c>
       <c r="F15" t="n">
-        <v>2.394</v>
+        <v>2.4805</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.474</v>
+        <v>-0.4401</v>
       </c>
       <c r="H15" t="n">
-        <v>3.0044</v>
+        <v>2.8704</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6224</v>
+        <v>1.6117</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.474</v>
+        <v>-0.4401</v>
       </c>
       <c r="K15" t="n">
         <v>145</v>
@@ -1127,7 +1127,7 @@
         <v>45</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1484</v>
+        <v>1.1716</v>
       </c>
       <c r="N15" t="n">
         <v>190</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8097</v>
+        <v>1.8597</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2904</v>
+        <v>0.2984</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1996</v>
+        <v>0.2414</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8097</v>
+        <v>1.8597</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5071</v>
+        <v>2.5419</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6974</v>
+        <v>-0.6822</v>
       </c>
       <c r="H16" t="n">
-        <v>3.3776</v>
+        <v>3.1007</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8239</v>
+        <v>1.741</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6974</v>
+        <v>-0.6822</v>
       </c>
       <c r="K16" t="n">
         <v>145</v>
@@ -1173,7 +1173,7 @@
         <v>45</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1265</v>
+        <v>1.0588</v>
       </c>
       <c r="N16" t="n">
         <v>190</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.4974</v>
+        <v>1.4055</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2403</v>
+        <v>0.2255</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0574</v>
+        <v>0.0345</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4974</v>
+        <v>1.4055</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4974</v>
+        <v>1.4055</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4974</v>
+        <v>1.4055</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4974</v>
+        <v>1.4055</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4974</v>
+        <v>1.4055</v>
       </c>
       <c r="N17" t="n">
         <v>131</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.4494</v>
+        <v>1.3873</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2326</v>
+        <v>0.2226</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0356</v>
+        <v>0.0262</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4494</v>
+        <v>1.3873</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4494</v>
+        <v>1.3873</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4494</v>
+        <v>1.3873</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4494</v>
+        <v>1.3873</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4494</v>
+        <v>1.3873</v>
       </c>
       <c r="N18" t="n">
         <v>131</v>
@@ -1274,93 +1274,93 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DeadFox</t>
+          <t>gob b</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.329</v>
+        <v>1.2336</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2133</v>
+        <v>0.198</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0192</v>
+        <v>-0.0438</v>
       </c>
       <c r="E19" t="n">
-        <v>1.329</v>
+        <v>1.2336</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1059</v>
+        <v>1.5186</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7769</v>
+        <v>-0.285</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1059</v>
+        <v>1.5186</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1372</v>
+        <v>0.8526</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7769</v>
+        <v>-0.285</v>
       </c>
       <c r="K19" t="n">
-        <v>145</v>
+        <v>197</v>
       </c>
       <c r="L19" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3603</v>
+        <v>0.5676000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>190</v>
+        <v>253</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>gob b</t>
+          <t>DeadFox</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.1355</v>
+        <v>1.0968</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1822</v>
+        <v>0.176</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1073</v>
+        <v>-0.1061</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1355</v>
+        <v>1.0968</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4314</v>
+        <v>1.8519</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2959</v>
+        <v>-0.7551</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4314</v>
+        <v>1.8519</v>
       </c>
       <c r="I20" t="n">
-        <v>0.773</v>
+        <v>1.0398</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2959</v>
+        <v>-0.7551</v>
       </c>
       <c r="K20" t="n">
-        <v>197</v>
+        <v>145</v>
       </c>
       <c r="L20" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4771</v>
+        <v>0.2847000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>253</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.0436</v>
+        <v>0.8796</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1675</v>
+        <v>0.1412</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1491</v>
+        <v>-0.2051</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0436</v>
+        <v>0.8796</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0436</v>
+        <v>0.8796</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0436</v>
+        <v>0.8796</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0436</v>
+        <v>0.8796</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.0436</v>
+        <v>0.8796</v>
       </c>
       <c r="N21" t="n">
         <v>85</v>
@@ -1412,93 +1412,93 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>rallen</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7924</v>
+        <v>0.6818</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1272</v>
+        <v>0.1094</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2635</v>
+        <v>-0.2952</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7924</v>
+        <v>0.6818</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7924</v>
+        <v>1.307</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.6252</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7924</v>
+        <v>1.307</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7924</v>
+        <v>0.7339</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.6252</v>
       </c>
       <c r="K22" t="n">
-        <v>90</v>
+        <v>197</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7924</v>
+        <v>0.1087</v>
       </c>
       <c r="N22" t="n">
-        <v>90</v>
+        <v>253</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>rallen</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7788</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="C23" t="n">
-        <v>0.125</v>
+        <v>0.1075</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2697</v>
+        <v>-0.3006</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7788</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>1.437</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.6582</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.437</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7759</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6582</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>197</v>
+        <v>90</v>
       </c>
       <c r="L23" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1177</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>253</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6441</v>
+        <v>0.6365</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1034</v>
+        <v>0.1021</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.331</v>
+        <v>-0.3158</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6441</v>
+        <v>0.6365</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6441</v>
+        <v>0.6365</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6441</v>
+        <v>0.6365</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6441</v>
+        <v>0.6365</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6441</v>
+        <v>0.6365</v>
       </c>
       <c r="N24" t="n">
         <v>131</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4179</v>
+        <v>0.349</v>
       </c>
       <c r="C25" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.056</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.434</v>
+        <v>-0.4468</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4179</v>
+        <v>0.349</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4179</v>
+        <v>0.349</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4179</v>
+        <v>0.349</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4179</v>
+        <v>0.349</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4179</v>
+        <v>0.349</v>
       </c>
       <c r="N25" t="n">
         <v>85</v>
@@ -1596,47 +1596,47 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>mouz</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2579</v>
+        <v>0.2675</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0414</v>
+        <v>0.0429</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5068</v>
+        <v>-0.4839</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2579</v>
+        <v>0.2675</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2579</v>
+        <v>0.2675</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2579</v>
+        <v>0.2675</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2579</v>
+        <v>0.2675</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>90</v>
+        <v>131</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2579</v>
+        <v>0.2675</v>
       </c>
       <c r="N26" t="n">
-        <v>90</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2032</v>
+        <v>0.1798</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0326</v>
+        <v>0.0289</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5317</v>
+        <v>-0.5239</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2032</v>
+        <v>0.1798</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2032</v>
+        <v>0.1798</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2032</v>
+        <v>0.1798</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2032</v>
+        <v>0.1798</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2032</v>
+        <v>0.1798</v>
       </c>
       <c r="N27" t="n">
         <v>90</v>
@@ -1688,47 +1688,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>mouz</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1667</v>
+        <v>0.1559</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0268</v>
+        <v>0.025</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5483</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1667</v>
+        <v>0.1559</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1667</v>
+        <v>0.1559</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1667</v>
+        <v>0.1559</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1667</v>
+        <v>0.1559</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>131</v>
+        <v>90</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1667</v>
+        <v>0.1559</v>
       </c>
       <c r="N28" t="n">
-        <v>131</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2867</v>
+        <v>-0.2642</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.046</v>
+        <v>-0.0424</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7547</v>
+        <v>-0.7261</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2867</v>
+        <v>-0.2642</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.2867</v>
+        <v>-0.2642</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.2867</v>
+        <v>-0.2642</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2867</v>
+        <v>-0.2642</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2867</v>
+        <v>-0.2642</v>
       </c>
       <c r="N29" t="n">
         <v>113</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2944</v>
+        <v>-0.3196</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0472</v>
+        <v>-0.0513</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7582</v>
+        <v>-0.7514</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2944</v>
+        <v>-0.3196</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2944</v>
+        <v>-0.3196</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2944</v>
+        <v>-0.3196</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2944</v>
+        <v>-0.3196</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2944</v>
+        <v>-0.3196</v>
       </c>
       <c r="N30" t="n">
         <v>90</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4045</v>
+        <v>-0.3822</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0649</v>
+        <v>-0.0613</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8083</v>
+        <v>-0.7799</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4045</v>
+        <v>-0.3822</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.4045</v>
+        <v>-0.3822</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.4045</v>
+        <v>-0.3822</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4045</v>
+        <v>-0.3822</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4045</v>
+        <v>-0.3822</v>
       </c>
       <c r="N31" t="n">
         <v>85</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4173</v>
+        <v>-0.4418</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.067</v>
+        <v>-0.0709</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8142</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4173</v>
+        <v>-0.4418</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4173</v>
+        <v>-0.4418</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4173</v>
+        <v>-0.4418</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4173</v>
+        <v>-0.4418</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4173</v>
+        <v>-0.4418</v>
       </c>
       <c r="N32" t="n">
         <v>90</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.7056</v>
+        <v>-0.6725</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1132</v>
+        <v>-0.1079</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9454</v>
+        <v>-0.9121</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7056</v>
+        <v>-0.6725</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.7056</v>
+        <v>-0.6725</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.7056</v>
+        <v>-0.6725</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7056</v>
+        <v>-0.6725</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.7056</v>
+        <v>-0.6725</v>
       </c>
       <c r="N33" t="n">
         <v>131</v>
@@ -1964,93 +1964,93 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BnTeT</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7416</v>
+        <v>-0.6855</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.119</v>
+        <v>-0.11</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9618</v>
+        <v>-0.9181</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7416</v>
+        <v>-0.6855</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.7416</v>
+        <v>-1.6224</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.9369</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7416</v>
+        <v>-1.6224</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.7416</v>
+        <v>-0.9109</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>0.9369</v>
       </c>
       <c r="K34" t="n">
-        <v>113</v>
+        <v>158</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7416</v>
+        <v>0.02599999999999991</v>
       </c>
       <c r="N34" t="n">
-        <v>113</v>
+        <v>253</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>BnTeT</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7741</v>
+        <v>-0.7184</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1242</v>
+        <v>-0.1153</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9766</v>
+        <v>-0.9331</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7741</v>
+        <v>-0.7184</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.7043</v>
+        <v>-0.7184</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9302</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.7043</v>
+        <v>-0.7184</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9203</v>
+        <v>-0.7184</v>
       </c>
       <c r="J35" t="n">
-        <v>0.9302</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>158</v>
+        <v>113</v>
       </c>
       <c r="L35" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.00990000000000002</v>
+        <v>-0.7184</v>
       </c>
       <c r="N35" t="n">
-        <v>253</v>
+        <v>113</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7766999999999999</v>
+        <v>-0.7282</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1246</v>
+        <v>-0.1169</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9778</v>
+        <v>-0.9375</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7766999999999999</v>
+        <v>-0.7282</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7766999999999999</v>
+        <v>-0.7282</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7766999999999999</v>
+        <v>-0.7282</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7766999999999999</v>
+        <v>-0.7282</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7766999999999999</v>
+        <v>-0.7282</v>
       </c>
       <c r="N36" t="n">
         <v>85</v>
@@ -2102,93 +2102,93 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>somebody</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.881</v>
+        <v>-0.8789</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1414</v>
+        <v>-0.141</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0253</v>
+        <v>-1.0062</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.881</v>
+        <v>-0.8789</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.881</v>
+        <v>-0.8789</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.881</v>
+        <v>-0.8789</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.881</v>
+        <v>-0.8789</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.881</v>
+        <v>-0.8789</v>
       </c>
       <c r="N37" t="n">
-        <v>113</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>somebody</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.926</v>
+        <v>-0.9022</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1486</v>
+        <v>-0.1448</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0457</v>
+        <v>-1.0168</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.926</v>
+        <v>-0.9022</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.926</v>
+        <v>-0.9022</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.926</v>
+        <v>-0.9022</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.926</v>
+        <v>-0.9022</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.926</v>
+        <v>-0.9022</v>
       </c>
       <c r="N38" t="n">
-        <v>85</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.9432</v>
+        <v>-0.9152</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1514</v>
+        <v>-0.1469</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0536</v>
+        <v>-1.0227</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.9432</v>
+        <v>-0.9152</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.9432</v>
+        <v>-0.9152</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9432</v>
+        <v>-0.9152</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.9432</v>
+        <v>-0.9152</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.9432</v>
+        <v>-0.9152</v>
       </c>
       <c r="N39" t="n">
         <v>113</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.0154</v>
+        <v>-1.0259</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1629</v>
+        <v>-0.1646</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0864</v>
+        <v>-1.0731</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.0154</v>
+        <v>-1.0259</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.0154</v>
+        <v>-1.0259</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.0154</v>
+        <v>-1.0259</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.0154</v>
+        <v>-1.0259</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.0154</v>
+        <v>-1.0259</v>
       </c>
       <c r="N40" t="n">
         <v>113</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.8509</v>
+        <v>-3.5103</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.618</v>
+        <v>-0.5633</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.3772</v>
+        <v>-2.2049</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.8509</v>
+        <v>-3.5103</v>
       </c>
       <c r="F41" t="n">
-        <v>-3.7701</v>
+        <v>-3.4736</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.0808</v>
+        <v>-0.0367</v>
       </c>
       <c r="H41" t="n">
-        <v>-3.7701</v>
+        <v>-3.4736</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.0358</v>
+        <v>-1.9503</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.0808</v>
+        <v>-0.0367</v>
       </c>
       <c r="K41" t="n">
         <v>158</v>
@@ -2323,7 +2323,7 @@
         <v>95</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.1166</v>
+        <v>-1.987</v>
       </c>
       <c r="N41" t="n">
         <v>253</v>
@@ -2429,10 +2429,10 @@
         <v>1.01</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1</v>
+        <v>0.0823</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>1.646</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.97</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0297</v>
+        <v>-0.0196</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.594</v>
+        <v>-0.392</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.76</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2687</v>
+        <v>-0.2524</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.374</v>
+        <v>-5.048</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.59</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4224</v>
+        <v>-0.4128</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.448</v>
+        <v>-8.256</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.48</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5188</v>
+        <v>-0.52</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.376</v>
+        <v>-10.4</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0998</v>
+        <v>1.1066</v>
       </c>
       <c r="J7" t="n">
-        <v>21.996</v>
+        <v>22.132</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.4</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9191</v>
+        <v>0.9107</v>
       </c>
       <c r="J8" t="n">
-        <v>18.382</v>
+        <v>18.214</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.38</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8827</v>
+        <v>0.8718</v>
       </c>
       <c r="J9" t="n">
-        <v>17.654</v>
+        <v>17.436</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.33</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7896</v>
+        <v>0.773</v>
       </c>
       <c r="J10" t="n">
-        <v>15.792</v>
+        <v>15.46</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.25</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6293</v>
+        <v>0.6046</v>
       </c>
       <c r="J11" t="n">
-        <v>12.586</v>
+        <v>12.092</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.35</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.6247</v>
       </c>
       <c r="J12" t="n">
-        <v>20.427</v>
+        <v>18.741</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1272</v>
+        <v>0.096</v>
       </c>
       <c r="J13" t="n">
-        <v>3.816</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.92</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1221</v>
+        <v>-0.1039</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.663</v>
+        <v>-3.117</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.85</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1999</v>
+        <v>-0.1793</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.997</v>
+        <v>-5.379</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.75</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2993</v>
+        <v>-0.2813</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.978999999999999</v>
+        <v>-8.439</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.64</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3814</v>
+        <v>1.4166</v>
       </c>
       <c r="J17" t="n">
-        <v>41.442</v>
+        <v>42.498</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.52</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1657</v>
+        <v>1.1764</v>
       </c>
       <c r="J18" t="n">
-        <v>34.971</v>
+        <v>35.292</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.16</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4514</v>
+        <v>0.4182</v>
       </c>
       <c r="J19" t="n">
-        <v>13.542</v>
+        <v>12.546</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.07</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2223</v>
+        <v>0.193</v>
       </c>
       <c r="J20" t="n">
-        <v>6.669</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.8</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6316000000000001</v>
+        <v>-0.5992</v>
       </c>
       <c r="J21" t="n">
-        <v>-18.948</v>
+        <v>-17.976</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.23</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5239</v>
+        <v>0.4699</v>
       </c>
       <c r="J22" t="n">
-        <v>13.0975</v>
+        <v>11.7475</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0211</v>
+        <v>0.0158</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5275</v>
+        <v>0.395</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.74</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.298</v>
+        <v>-0.28</v>
       </c>
       <c r="J24" t="n">
-        <v>-7.45</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.73</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3074</v>
+        <v>-0.2898</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.685</v>
+        <v>-7.245</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.66</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3719</v>
+        <v>-0.3582</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.297499999999999</v>
+        <v>-8.955</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.78</v>
       </c>
       <c r="I27" t="n">
-        <v>1.4624</v>
+        <v>1.4935</v>
       </c>
       <c r="J27" t="n">
-        <v>36.56</v>
+        <v>37.3375</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.45</v>
       </c>
       <c r="I28" t="n">
-        <v>1.024</v>
+        <v>1.0258</v>
       </c>
       <c r="J28" t="n">
-        <v>25.6</v>
+        <v>25.645</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.34</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8247</v>
+        <v>0.8036</v>
       </c>
       <c r="J29" t="n">
-        <v>20.6175</v>
+        <v>20.09</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.93</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3044</v>
+        <v>-0.2658</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.61</v>
+        <v>-6.645</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.71</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8300999999999999</v>
+        <v>-0.8139999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>-20.7525</v>
+        <v>-20.35</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>2</v>
       </c>
       <c r="I32" t="n">
-        <v>1.0295</v>
+        <v>0.9764</v>
       </c>
       <c r="J32" t="n">
-        <v>20.59</v>
+        <v>19.528</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.74</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8138</v>
+        <v>0.7437</v>
       </c>
       <c r="J33" t="n">
-        <v>16.276</v>
+        <v>14.874</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.39</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4861</v>
+        <v>0.4253</v>
       </c>
       <c r="J34" t="n">
-        <v>9.722</v>
+        <v>8.506</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.24</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3227</v>
+        <v>0.2719</v>
       </c>
       <c r="J35" t="n">
-        <v>6.454</v>
+        <v>5.438</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.19</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2628</v>
+        <v>0.2167</v>
       </c>
       <c r="J36" t="n">
-        <v>5.256</v>
+        <v>4.334</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.07</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2816</v>
+        <v>0.3112</v>
       </c>
       <c r="J37" t="n">
-        <v>5.632</v>
+        <v>6.224</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.75</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2519</v>
+        <v>-0.2379</v>
       </c>
       <c r="J38" t="n">
-        <v>-5.038</v>
+        <v>-4.758</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.46</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.5147</v>
+        <v>-0.5145</v>
       </c>
       <c r="J39" t="n">
-        <v>-10.294</v>
+        <v>-10.29</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.37</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5942</v>
+        <v>-0.6046</v>
       </c>
       <c r="J40" t="n">
-        <v>-11.884</v>
+        <v>-12.092</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.33</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6296</v>
+        <v>-0.6458</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.592</v>
+        <v>-12.916</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.01</v>
       </c>
       <c r="I42" t="n">
-        <v>0.0891</v>
+        <v>0.0703</v>
       </c>
       <c r="J42" t="n">
-        <v>2.4057</v>
+        <v>1.8981</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.87</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1622</v>
+        <v>-0.1462</v>
       </c>
       <c r="J43" t="n">
-        <v>-4.3794</v>
+        <v>-3.9474</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.78</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.2524</v>
+        <v>-0.2351</v>
       </c>
       <c r="J44" t="n">
-        <v>-6.8148</v>
+        <v>-6.3477</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.72</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3082</v>
+        <v>-0.2916</v>
       </c>
       <c r="J45" t="n">
-        <v>-8.321400000000001</v>
+        <v>-7.8732</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.58</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4347</v>
+        <v>-0.4263</v>
       </c>
       <c r="J46" t="n">
-        <v>-11.7369</v>
+        <v>-11.5101</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.66</v>
       </c>
       <c r="I47" t="n">
-        <v>1.2945</v>
+        <v>1.3135</v>
       </c>
       <c r="J47" t="n">
-        <v>34.9515</v>
+        <v>35.4645</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.51</v>
       </c>
       <c r="I48" t="n">
-        <v>1.0981</v>
+        <v>1.1101</v>
       </c>
       <c r="J48" t="n">
-        <v>29.6487</v>
+        <v>29.9727</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.28</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6995</v>
+        <v>0.6752</v>
       </c>
       <c r="J49" t="n">
-        <v>18.8865</v>
+        <v>18.2304</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.24</v>
       </c>
       <c r="I50" t="n">
-        <v>0.6179</v>
+        <v>0.5904</v>
       </c>
       <c r="J50" t="n">
-        <v>16.6833</v>
+        <v>15.9408</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.83</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.572</v>
+        <v>-0.5383</v>
       </c>
       <c r="J51" t="n">
-        <v>-15.444</v>
+        <v>-14.5341</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.37</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7771</v>
+        <v>0.7615</v>
       </c>
       <c r="J52" t="n">
-        <v>23.313</v>
+        <v>22.845</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.34</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7332</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="J53" t="n">
-        <v>21.996</v>
+        <v>21.546</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.15</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4336</v>
+        <v>0.4006</v>
       </c>
       <c r="J54" t="n">
-        <v>13.008</v>
+        <v>12.018</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.11</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3388</v>
+        <v>0.3049</v>
       </c>
       <c r="J55" t="n">
-        <v>10.164</v>
+        <v>9.147</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2646</v>
+        <v>-0.2261</v>
       </c>
       <c r="J56" t="n">
-        <v>-7.938</v>
+        <v>-6.783</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.14</v>
       </c>
       <c r="I57" t="n">
-        <v>0.359</v>
+        <v>0.3067</v>
       </c>
       <c r="J57" t="n">
-        <v>10.77</v>
+        <v>9.201000000000001</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.98</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0328</v>
+        <v>-0.0253</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.984</v>
+        <v>-0.759</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.86</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1805</v>
+        <v>-0.1618</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.415</v>
+        <v>-4.854</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.71</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3269</v>
+        <v>-0.3102</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.807</v>
+        <v>-9.305999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.71</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3269</v>
+        <v>-0.3102</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.807</v>
+        <v>-9.305999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.49</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9351</v>
+        <v>0.9209000000000001</v>
       </c>
       <c r="J62" t="n">
-        <v>24.3126</v>
+        <v>23.9434</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.31</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6806</v>
+        <v>0.6685</v>
       </c>
       <c r="J63" t="n">
-        <v>17.6956</v>
+        <v>17.381</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.19</v>
       </c>
       <c r="I64" t="n">
-        <v>0.498</v>
+        <v>0.4857</v>
       </c>
       <c r="J64" t="n">
-        <v>12.948</v>
+        <v>12.6282</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.11</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3295</v>
+        <v>0.2971</v>
       </c>
       <c r="J65" t="n">
-        <v>8.567</v>
+        <v>7.7246</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.1</v>
       </c>
       <c r="I66" t="n">
-        <v>0.3037</v>
+        <v>0.2717</v>
       </c>
       <c r="J66" t="n">
-        <v>7.8962</v>
+        <v>7.0642</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>0.031</v>
+        <v>0.0252</v>
       </c>
       <c r="J67" t="n">
-        <v>0.806</v>
+        <v>0.6552</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.99</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0081</v>
+        <v>-0.0038</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.2106</v>
+        <v>-0.0988</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.227</v>
+        <v>-0.2086</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.902</v>
+        <v>-5.4236</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.7</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3313</v>
+        <v>-0.315</v>
       </c>
       <c r="J70" t="n">
-        <v>-8.613799999999999</v>
+        <v>-8.19</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.67</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3588</v>
+        <v>-0.3441</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.328799999999999</v>
+        <v>-8.9466</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>0.84</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.189</v>
+        <v>-0.1732</v>
       </c>
       <c r="J72" t="n">
-        <v>-3.78</v>
+        <v>-3.464</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.84</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.189</v>
+        <v>-0.1732</v>
       </c>
       <c r="J73" t="n">
-        <v>-3.78</v>
+        <v>-3.464</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.83</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1995</v>
+        <v>-0.1837</v>
       </c>
       <c r="J74" t="n">
-        <v>-3.99</v>
+        <v>-3.674</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.72</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3041</v>
+        <v>-0.2884</v>
       </c>
       <c r="J75" t="n">
-        <v>-6.082</v>
+        <v>-5.768</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.53</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4741</v>
+        <v>-0.4697</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.481999999999999</v>
+        <v>-9.394</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.67</v>
       </c>
       <c r="I77" t="n">
-        <v>1.1404</v>
+        <v>1.1343</v>
       </c>
       <c r="J77" t="n">
-        <v>22.808</v>
+        <v>22.686</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.51</v>
       </c>
       <c r="I78" t="n">
-        <v>0.9361</v>
+        <v>0.9254</v>
       </c>
       <c r="J78" t="n">
-        <v>18.722</v>
+        <v>18.508</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.4</v>
       </c>
       <c r="I79" t="n">
-        <v>0.7917</v>
+        <v>0.7823</v>
       </c>
       <c r="J79" t="n">
-        <v>15.834</v>
+        <v>15.646</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.28</v>
       </c>
       <c r="I80" t="n">
-        <v>0.6213</v>
+        <v>0.6168</v>
       </c>
       <c r="J80" t="n">
-        <v>12.426</v>
+        <v>12.336</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.19</v>
       </c>
       <c r="I81" t="n">
-        <v>0.4794</v>
+        <v>0.4644</v>
       </c>
       <c r="J81" t="n">
-        <v>9.587999999999999</v>
+        <v>9.288</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.17</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4316</v>
+        <v>0.383</v>
       </c>
       <c r="J82" t="n">
-        <v>10.79</v>
+        <v>9.574999999999999</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.98</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.0254</v>
+        <v>-0.0182</v>
       </c>
       <c r="J83" t="n">
-        <v>-0.635</v>
+        <v>-0.455</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.76</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2745</v>
+        <v>-0.2564</v>
       </c>
       <c r="J84" t="n">
-        <v>-6.8625</v>
+        <v>-6.41</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.73</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3028</v>
+        <v>-0.2854</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.57</v>
+        <v>-7.135</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.5</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5084</v>
+        <v>-0.509</v>
       </c>
       <c r="J86" t="n">
-        <v>-12.71</v>
+        <v>-12.725</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.53</v>
       </c>
       <c r="I87" t="n">
-        <v>0.9792</v>
+        <v>0.9665</v>
       </c>
       <c r="J87" t="n">
-        <v>24.48</v>
+        <v>24.1625</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.5</v>
       </c>
       <c r="I88" t="n">
-        <v>0.9391</v>
+        <v>0.9256</v>
       </c>
       <c r="J88" t="n">
-        <v>23.4775</v>
+        <v>23.14</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.26</v>
       </c>
       <c r="I89" t="n">
-        <v>0.6026</v>
+        <v>0.596</v>
       </c>
       <c r="J89" t="n">
-        <v>15.065</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.2</v>
       </c>
       <c r="I90" t="n">
-        <v>0.5087</v>
+        <v>0.5009</v>
       </c>
       <c r="J90" t="n">
-        <v>12.7175</v>
+        <v>12.5225</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.98</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1508</v>
+        <v>-0.1249</v>
       </c>
       <c r="J91" t="n">
-        <v>-3.77</v>
+        <v>-3.1225</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.2956</v>
+        <v>-0.2836</v>
       </c>
       <c r="J92" t="n">
-        <v>-5.3208</v>
+        <v>-5.1048</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.4197</v>
+        <v>-0.4157</v>
       </c>
       <c r="J93" t="n">
-        <v>-7.5546</v>
+        <v>-7.4826</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.51</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.4612</v>
+        <v>-0.4583</v>
       </c>
       <c r="J94" t="n">
-        <v>-8.301600000000001</v>
+        <v>-8.2494</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.48</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.4869</v>
+        <v>-0.4853</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.764200000000001</v>
+        <v>-8.7354</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.42</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-0.5426</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.7164</v>
+        <v>-9.7668</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.71</v>
       </c>
       <c r="I97" t="n">
-        <v>1.3146</v>
+        <v>1.3385</v>
       </c>
       <c r="J97" t="n">
-        <v>23.6628</v>
+        <v>24.093</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.63</v>
       </c>
       <c r="I98" t="n">
-        <v>1.2179</v>
+        <v>1.2396</v>
       </c>
       <c r="J98" t="n">
-        <v>21.9222</v>
+        <v>22.3128</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.55</v>
       </c>
       <c r="I99" t="n">
-        <v>1.1209</v>
+        <v>1.1414</v>
       </c>
       <c r="J99" t="n">
-        <v>20.1762</v>
+        <v>20.5452</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.53</v>
       </c>
       <c r="I100" t="n">
-        <v>1.0959</v>
+        <v>1.116</v>
       </c>
       <c r="J100" t="n">
-        <v>19.7262</v>
+        <v>20.088</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.46</v>
       </c>
       <c r="I101" t="n">
-        <v>0.9994</v>
+        <v>1.01</v>
       </c>
       <c r="J101" t="n">
-        <v>17.9892</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>0.73</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.2662</v>
+        <v>-0.2527</v>
       </c>
       <c r="J102" t="n">
-        <v>-4.5254</v>
+        <v>-4.2959</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.3066</v>
+        <v>-0.2958</v>
       </c>
       <c r="J103" t="n">
-        <v>-5.2122</v>
+        <v>-5.0286</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.67</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3261</v>
+        <v>-0.3165</v>
       </c>
       <c r="J104" t="n">
-        <v>-5.5437</v>
+        <v>-5.3805</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.5</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4758</v>
+        <v>-0.4723</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.0886</v>
+        <v>-8.0291</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.27</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6797</v>
+        <v>-0.7052</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.5549</v>
+        <v>-11.9884</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>2.66</v>
       </c>
       <c r="I107" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J107" t="n">
-        <v>32.9324</v>
+        <v>33.6906</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>2.2</v>
       </c>
       <c r="I108" t="n">
-        <v>1.8621</v>
+        <v>1.925</v>
       </c>
       <c r="J108" t="n">
-        <v>31.6557</v>
+        <v>32.725</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.48</v>
       </c>
       <c r="I109" t="n">
-        <v>1.02</v>
+        <v>1.0357</v>
       </c>
       <c r="J109" t="n">
-        <v>17.34</v>
+        <v>17.6069</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.13</v>
       </c>
       <c r="I110" t="n">
-        <v>0.3176</v>
+        <v>0.2804</v>
       </c>
       <c r="J110" t="n">
-        <v>5.3992</v>
+        <v>4.7668</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.88</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4961</v>
+        <v>-0.4713</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.4337</v>
+        <v>-8.0121</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.47</v>
       </c>
       <c r="I112" t="n">
-        <v>1.0807</v>
+        <v>1.0907</v>
       </c>
       <c r="J112" t="n">
-        <v>29.1789</v>
+        <v>29.4489</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.28</v>
       </c>
       <c r="I113" t="n">
-        <v>0.7288</v>
+        <v>0.6978</v>
       </c>
       <c r="J113" t="n">
-        <v>19.6776</v>
+        <v>18.8406</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.23</v>
       </c>
       <c r="I114" t="n">
-        <v>0.6223</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="J114" t="n">
-        <v>16.8021</v>
+        <v>15.8274</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.84</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5175</v>
+        <v>-0.4769</v>
       </c>
       <c r="J115" t="n">
-        <v>-13.9725</v>
+        <v>-12.8763</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.79</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6345</v>
+        <v>-0.5994</v>
       </c>
       <c r="J116" t="n">
-        <v>-17.1315</v>
+        <v>-16.1838</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.08</v>
       </c>
       <c r="I117" t="n">
-        <v>0.2254</v>
+        <v>0.1812</v>
       </c>
       <c r="J117" t="n">
-        <v>6.0858</v>
+        <v>4.8924</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1</v>
       </c>
       <c r="I118" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0052</v>
       </c>
       <c r="J118" t="n">
-        <v>0.2268</v>
+        <v>0.1404</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.98</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0386</v>
+        <v>-0.0301</v>
       </c>
       <c r="J119" t="n">
-        <v>-1.0422</v>
+        <v>-0.8127</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.0948</v>
+        <v>-0.0796</v>
       </c>
       <c r="J120" t="n">
-        <v>-2.5596</v>
+        <v>-2.1492</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.67</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.369</v>
+        <v>-0.3554</v>
       </c>
       <c r="J121" t="n">
-        <v>-9.962999999999999</v>
+        <v>-9.595800000000001</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.6</v>
       </c>
       <c r="I122" t="n">
-        <v>1.2121</v>
+        <v>1.2277</v>
       </c>
       <c r="J122" t="n">
-        <v>27.8783</v>
+        <v>28.2371</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.45</v>
       </c>
       <c r="I123" t="n">
-        <v>1.0087</v>
+        <v>1.0105</v>
       </c>
       <c r="J123" t="n">
-        <v>23.2001</v>
+        <v>23.2415</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.35</v>
       </c>
       <c r="I124" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.8147</v>
       </c>
       <c r="J124" t="n">
-        <v>19.1153</v>
+        <v>18.7381</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.32</v>
       </c>
       <c r="I125" t="n">
-        <v>0.7748</v>
+        <v>0.7553</v>
       </c>
       <c r="J125" t="n">
-        <v>17.8204</v>
+        <v>17.3719</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.93</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3186</v>
+        <v>-0.2823</v>
       </c>
       <c r="J126" t="n">
-        <v>-7.3278</v>
+        <v>-6.4929</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.17</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4616</v>
+        <v>0.4175</v>
       </c>
       <c r="J127" t="n">
-        <v>10.6168</v>
+        <v>9.602499999999999</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.98</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.0141</v>
+        <v>-0.0059</v>
       </c>
       <c r="J128" t="n">
-        <v>-0.3243</v>
+        <v>-0.1357</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.76</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2689</v>
+        <v>-0.2525</v>
       </c>
       <c r="J129" t="n">
-        <v>-6.1847</v>
+        <v>-5.8075</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.54</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.467</v>
+        <v>-0.4618</v>
       </c>
       <c r="J130" t="n">
-        <v>-10.741</v>
+        <v>-10.6214</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.38</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.605</v>
+        <v>-0.6196</v>
       </c>
       <c r="J131" t="n">
-        <v>-13.915</v>
+        <v>-14.2508</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.56</v>
       </c>
       <c r="I132" t="n">
-        <v>1.1883</v>
+        <v>1.203</v>
       </c>
       <c r="J132" t="n">
-        <v>29.7075</v>
+        <v>30.075</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.19</v>
       </c>
       <c r="I133" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.4898</v>
       </c>
       <c r="J133" t="n">
-        <v>13.1175</v>
+        <v>12.245</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.1</v>
       </c>
       <c r="I134" t="n">
-        <v>0.3118</v>
+        <v>0.2788</v>
       </c>
       <c r="J134" t="n">
-        <v>7.795</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.05</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1712</v>
+        <v>0.1449</v>
       </c>
       <c r="J135" t="n">
-        <v>4.28</v>
+        <v>3.6225</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.05</v>
       </c>
       <c r="I136" t="n">
-        <v>0.1712</v>
+        <v>0.1449</v>
       </c>
       <c r="J136" t="n">
-        <v>4.28</v>
+        <v>3.6225</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.16</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3785</v>
+        <v>0.3236</v>
       </c>
       <c r="J137" t="n">
-        <v>9.4625</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.095</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="J138" t="n">
-        <v>-2.375</v>
+        <v>-1.9925</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.91</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1306</v>
+        <v>-0.1126</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.265</v>
+        <v>-2.815</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.86</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1855</v>
+        <v>-0.1655</v>
       </c>
       <c r="J140" t="n">
-        <v>-4.6375</v>
+        <v>-4.1375</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.83</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2167</v>
+        <v>-0.1964</v>
       </c>
       <c r="J141" t="n">
-        <v>-5.4175</v>
+        <v>-4.91</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.49</v>
       </c>
       <c r="I142" t="n">
-        <v>1.0888</v>
+        <v>1.099</v>
       </c>
       <c r="J142" t="n">
-        <v>38.108</v>
+        <v>38.465</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.45</v>
       </c>
       <c r="I143" t="n">
-        <v>1.031</v>
+        <v>1.0334</v>
       </c>
       <c r="J143" t="n">
-        <v>36.085</v>
+        <v>36.169</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.25</v>
       </c>
       <c r="I144" t="n">
-        <v>0.6492</v>
+        <v>0.6179</v>
       </c>
       <c r="J144" t="n">
-        <v>22.722</v>
+        <v>21.6265</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.97</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1729</v>
+        <v>-0.1416</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.0515</v>
+        <v>-4.956</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.88</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4337</v>
+        <v>-0.3931</v>
       </c>
       <c r="J146" t="n">
-        <v>-15.1795</v>
+        <v>-13.7585</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.11</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3038</v>
+        <v>0.2548</v>
       </c>
       <c r="J147" t="n">
-        <v>10.633</v>
+        <v>8.917999999999999</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.02</v>
       </c>
       <c r="I148" t="n">
-        <v>0.0975</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="J148" t="n">
-        <v>3.4125</v>
+        <v>2.5165</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.8</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2401</v>
+        <v>-0.2208</v>
       </c>
       <c r="J149" t="n">
-        <v>-8.403499999999999</v>
+        <v>-7.728</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.79</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2499</v>
+        <v>-0.2306</v>
       </c>
       <c r="J150" t="n">
-        <v>-8.746499999999999</v>
+        <v>-8.071</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.63</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3987</v>
+        <v>-0.3873</v>
       </c>
       <c r="J151" t="n">
-        <v>-13.9545</v>
+        <v>-13.5555</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.4</v>
       </c>
       <c r="I152" t="n">
-        <v>0.7094</v>
+        <v>0.651</v>
       </c>
       <c r="J152" t="n">
-        <v>24.829</v>
+        <v>22.785</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.27</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5163</v>
+        <v>0.4584</v>
       </c>
       <c r="J153" t="n">
-        <v>18.0705</v>
+        <v>16.044</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.15</v>
       </c>
       <c r="I154" t="n">
-        <v>0.3239</v>
+        <v>0.276</v>
       </c>
       <c r="J154" t="n">
-        <v>11.3365</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.15</v>
       </c>
       <c r="I155" t="n">
-        <v>0.3239</v>
+        <v>0.276</v>
       </c>
       <c r="J155" t="n">
-        <v>11.3365</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.83</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2356</v>
+        <v>-0.2163</v>
       </c>
       <c r="J156" t="n">
-        <v>-8.246</v>
+        <v>-7.5705</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.29</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7715</v>
+        <v>0.7429</v>
       </c>
       <c r="J157" t="n">
-        <v>27.0025</v>
+        <v>26.0015</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.18</v>
       </c>
       <c r="I158" t="n">
-        <v>0.528</v>
+        <v>0.487</v>
       </c>
       <c r="J158" t="n">
-        <v>18.48</v>
+        <v>17.045</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.02</v>
       </c>
       <c r="I159" t="n">
-        <v>0.094</v>
+        <v>0.0738</v>
       </c>
       <c r="J159" t="n">
-        <v>3.29</v>
+        <v>2.583</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.87</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4287</v>
+        <v>-0.3856</v>
       </c>
       <c r="J160" t="n">
-        <v>-15.0045</v>
+        <v>-13.496</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.87</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4287</v>
+        <v>-0.3856</v>
       </c>
       <c r="J161" t="n">
-        <v>-15.0045</v>
+        <v>-13.496</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>0.8</v>
       </c>
       <c r="I162" t="n">
-        <v>-0.1963</v>
+        <v>-0.1784</v>
       </c>
       <c r="J162" t="n">
-        <v>-3.926</v>
+        <v>-3.568</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.62</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.3755</v>
+        <v>-0.3676</v>
       </c>
       <c r="J163" t="n">
-        <v>-7.51</v>
+        <v>-7.352</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.55</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.4347</v>
+        <v>-0.4284</v>
       </c>
       <c r="J164" t="n">
-        <v>-8.694000000000001</v>
+        <v>-8.568</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.51</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.4695</v>
+        <v>-0.4653</v>
       </c>
       <c r="J165" t="n">
-        <v>-9.390000000000001</v>
+        <v>-9.305999999999999</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.46</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5135</v>
+        <v>-0.5131</v>
       </c>
       <c r="J166" t="n">
-        <v>-10.27</v>
+        <v>-10.262</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.73</v>
       </c>
       <c r="I167" t="n">
-        <v>1.356</v>
+        <v>1.3789</v>
       </c>
       <c r="J167" t="n">
-        <v>27.12</v>
+        <v>27.578</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.41</v>
       </c>
       <c r="I168" t="n">
-        <v>0.9298999999999999</v>
+        <v>0.9268</v>
       </c>
       <c r="J168" t="n">
-        <v>18.598</v>
+        <v>18.536</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.4</v>
       </c>
       <c r="I169" t="n">
-        <v>0.9121</v>
+        <v>0.9072</v>
       </c>
       <c r="J169" t="n">
-        <v>18.242</v>
+        <v>18.144</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.37</v>
       </c>
       <c r="I170" t="n">
-        <v>0.8566</v>
+        <v>0.8475</v>
       </c>
       <c r="J170" t="n">
-        <v>17.132</v>
+        <v>16.95</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.33</v>
       </c>
       <c r="I171" t="n">
-        <v>0.78</v>
+        <v>0.7657</v>
       </c>
       <c r="J171" t="n">
-        <v>15.6</v>
+        <v>15.314</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.47</v>
       </c>
       <c r="I172" t="n">
-        <v>0.5821</v>
+        <v>0.5121</v>
       </c>
       <c r="J172" t="n">
-        <v>13.9704</v>
+        <v>12.2904</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.43</v>
       </c>
       <c r="I173" t="n">
-        <v>0.5415</v>
+        <v>0.473</v>
       </c>
       <c r="J173" t="n">
-        <v>12.996</v>
+        <v>11.352</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.27</v>
       </c>
       <c r="I174" t="n">
-        <v>0.3735</v>
+        <v>0.3162</v>
       </c>
       <c r="J174" t="n">
-        <v>8.964</v>
+        <v>7.5888</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.15</v>
       </c>
       <c r="I175" t="n">
-        <v>0.2302</v>
+        <v>0.187</v>
       </c>
       <c r="J175" t="n">
-        <v>5.5248</v>
+        <v>4.488</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>1.14</v>
       </c>
       <c r="I176" t="n">
-        <v>0.2171</v>
+        <v>0.1754</v>
       </c>
       <c r="J176" t="n">
-        <v>5.2104</v>
+        <v>4.2096</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.19</v>
       </c>
       <c r="I177" t="n">
-        <v>0.3559</v>
+        <v>0.3519</v>
       </c>
       <c r="J177" t="n">
-        <v>8.541600000000001</v>
+        <v>8.445600000000001</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1</v>
       </c>
       <c r="I178" t="n">
-        <v>0.0169</v>
+        <v>0.0143</v>
       </c>
       <c r="J178" t="n">
-        <v>0.4056</v>
+        <v>0.3432</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.85</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.19</v>
+        <v>-0.1713</v>
       </c>
       <c r="J179" t="n">
-        <v>-4.56</v>
+        <v>-4.1112</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.76</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2788</v>
+        <v>-0.2602</v>
       </c>
       <c r="J180" t="n">
-        <v>-6.6912</v>
+        <v>-6.2448</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.55</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4692</v>
+        <v>-0.4653</v>
       </c>
       <c r="J181" t="n">
-        <v>-11.2608</v>
+        <v>-11.1672</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.24</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5087</v>
+        <v>0.4502</v>
       </c>
       <c r="J182" t="n">
-        <v>14.2436</v>
+        <v>12.6056</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.09</v>
       </c>
       <c r="I183" t="n">
-        <v>0.2383</v>
+        <v>0.1928</v>
       </c>
       <c r="J183" t="n">
-        <v>6.6724</v>
+        <v>5.3984</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.87</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1775</v>
+        <v>-0.1573</v>
       </c>
       <c r="J184" t="n">
-        <v>-4.97</v>
+        <v>-4.4044</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.86</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1882</v>
+        <v>-0.1678</v>
       </c>
       <c r="J185" t="n">
-        <v>-5.2696</v>
+        <v>-4.6984</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.79</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2595</v>
+        <v>-0.2398</v>
       </c>
       <c r="J186" t="n">
-        <v>-7.266</v>
+        <v>-6.7144</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.27</v>
       </c>
       <c r="I187" t="n">
-        <v>0.7128</v>
+        <v>0.6804</v>
       </c>
       <c r="J187" t="n">
-        <v>19.9584</v>
+        <v>19.0512</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.16</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4691</v>
+        <v>0.4294</v>
       </c>
       <c r="J188" t="n">
-        <v>13.1348</v>
+        <v>12.0232</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.14</v>
       </c>
       <c r="I189" t="n">
-        <v>0.422</v>
+        <v>0.3825</v>
       </c>
       <c r="J189" t="n">
-        <v>11.816</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.01</v>
       </c>
       <c r="I190" t="n">
-        <v>0.0436</v>
+        <v>0.0326</v>
       </c>
       <c r="J190" t="n">
-        <v>1.2208</v>
+        <v>0.9127999999999999</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.93</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2791</v>
+        <v>-0.2388</v>
       </c>
       <c r="J191" t="n">
-        <v>-7.8148</v>
+        <v>-6.6864</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1</v>
       </c>
       <c r="I192" t="n">
-        <v>0.0624</v>
+        <v>0.0589</v>
       </c>
       <c r="J192" t="n">
-        <v>1.3104</v>
+        <v>1.2369</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.98</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0089</v>
+        <v>0.0004</v>
       </c>
       <c r="J193" t="n">
-        <v>-0.1869</v>
+        <v>0.008399999999999999</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.86</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1657</v>
+        <v>-0.1501</v>
       </c>
       <c r="J194" t="n">
-        <v>-3.4797</v>
+        <v>-3.1521</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.57</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4377</v>
+        <v>-0.4295</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.191700000000001</v>
+        <v>-9.019500000000001</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.3</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.6706</v>
+        <v>-0.6972</v>
       </c>
       <c r="J196" t="n">
-        <v>-14.0826</v>
+        <v>-14.6412</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.64</v>
       </c>
       <c r="I197" t="n">
-        <v>1.2535</v>
+        <v>1.2713</v>
       </c>
       <c r="J197" t="n">
-        <v>26.3235</v>
+        <v>26.6973</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.54</v>
       </c>
       <c r="I198" t="n">
-        <v>1.1252</v>
+        <v>1.1398</v>
       </c>
       <c r="J198" t="n">
-        <v>23.6292</v>
+        <v>23.9358</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.31</v>
       </c>
       <c r="I199" t="n">
-        <v>0.7487</v>
+        <v>0.7305</v>
       </c>
       <c r="J199" t="n">
-        <v>15.7227</v>
+        <v>15.3405</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.29</v>
       </c>
       <c r="I200" t="n">
-        <v>0.7089</v>
+        <v>0.6886</v>
       </c>
       <c r="J200" t="n">
-        <v>14.8869</v>
+        <v>14.4606</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.16</v>
       </c>
       <c r="I201" t="n">
-        <v>0.4283</v>
+        <v>0.3972</v>
       </c>
       <c r="J201" t="n">
-        <v>8.994300000000001</v>
+        <v>8.341200000000001</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.14</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3301</v>
+        <v>0.2774</v>
       </c>
       <c r="J202" t="n">
-        <v>8.912699999999999</v>
+        <v>7.4898</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.97</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.0575</v>
+        <v>-0.0453</v>
       </c>
       <c r="J203" t="n">
-        <v>-1.5525</v>
+        <v>-1.2231</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.96</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.0718</v>
+        <v>-0.0578</v>
       </c>
       <c r="J204" t="n">
-        <v>-1.9386</v>
+        <v>-1.5606</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.96</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.0718</v>
+        <v>-0.0578</v>
       </c>
       <c r="J205" t="n">
-        <v>-1.9386</v>
+        <v>-1.5606</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.92</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.1228</v>
+        <v>-0.1044</v>
       </c>
       <c r="J206" t="n">
-        <v>-3.3156</v>
+        <v>-2.8188</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.4</v>
       </c>
       <c r="I207" t="n">
-        <v>0.9465</v>
+        <v>0.9351</v>
       </c>
       <c r="J207" t="n">
-        <v>25.5555</v>
+        <v>25.2477</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.32</v>
       </c>
       <c r="I208" t="n">
-        <v>0.7912</v>
+        <v>0.7667</v>
       </c>
       <c r="J208" t="n">
-        <v>21.3624</v>
+        <v>20.7009</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.17</v>
       </c>
       <c r="I209" t="n">
-        <v>0.4783</v>
+        <v>0.4441</v>
       </c>
       <c r="J209" t="n">
-        <v>12.9141</v>
+        <v>11.9907</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.1</v>
       </c>
       <c r="I210" t="n">
-        <v>0.3086</v>
+        <v>0.2761</v>
       </c>
       <c r="J210" t="n">
-        <v>8.3322</v>
+        <v>7.4547</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1.06</v>
       </c>
       <c r="I211" t="n">
-        <v>0.198</v>
+        <v>0.17</v>
       </c>
       <c r="J211" t="n">
-        <v>5.346</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>0.83</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.1776</v>
+        <v>-0.1608</v>
       </c>
       <c r="J212" t="n">
-        <v>-3.7296</v>
+        <v>-3.3768</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.82</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.1887</v>
+        <v>-0.1723</v>
       </c>
       <c r="J213" t="n">
-        <v>-3.9627</v>
+        <v>-3.6183</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.62</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.3808</v>
+        <v>-0.3707</v>
       </c>
       <c r="J214" t="n">
-        <v>-7.9968</v>
+        <v>-7.7847</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.55</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4419</v>
+        <v>-0.4348</v>
       </c>
       <c r="J215" t="n">
-        <v>-9.2799</v>
+        <v>-9.130800000000001</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.38</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5913</v>
+        <v>-0.6017</v>
       </c>
       <c r="J216" t="n">
-        <v>-12.4173</v>
+        <v>-12.6357</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.78</v>
       </c>
       <c r="I217" t="n">
-        <v>1.4147</v>
+        <v>1.4408</v>
       </c>
       <c r="J217" t="n">
-        <v>29.7087</v>
+        <v>30.2568</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.52</v>
       </c>
       <c r="I218" t="n">
-        <v>1.0909</v>
+        <v>1.1069</v>
       </c>
       <c r="J218" t="n">
-        <v>22.9089</v>
+        <v>23.2449</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.44</v>
       </c>
       <c r="I219" t="n">
-        <v>0.9791</v>
+        <v>0.9825</v>
       </c>
       <c r="J219" t="n">
-        <v>20.5611</v>
+        <v>20.6325</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.29</v>
       </c>
       <c r="I220" t="n">
-        <v>0.6987</v>
+        <v>0.6797</v>
       </c>
       <c r="J220" t="n">
-        <v>14.6727</v>
+        <v>14.2737</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.28</v>
       </c>
       <c r="I221" t="n">
-        <v>0.6784</v>
+        <v>0.6582</v>
       </c>
       <c r="J221" t="n">
-        <v>14.2464</v>
+        <v>13.8222</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.48</v>
       </c>
       <c r="I222" t="n">
-        <v>1.0481</v>
+        <v>1.0568</v>
       </c>
       <c r="J222" t="n">
-        <v>27.2506</v>
+        <v>27.4768</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.47</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0338</v>
+        <v>1.0406</v>
       </c>
       <c r="J223" t="n">
-        <v>26.8788</v>
+        <v>27.0556</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.47</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0338</v>
+        <v>1.0406</v>
       </c>
       <c r="J224" t="n">
-        <v>26.8788</v>
+        <v>27.0556</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.39</v>
       </c>
       <c r="I225" t="n">
-        <v>0.9014</v>
+        <v>0.8915</v>
       </c>
       <c r="J225" t="n">
-        <v>23.4364</v>
+        <v>23.179</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.02</v>
       </c>
       <c r="I226" t="n">
-        <v>0.0403</v>
+        <v>0.0224</v>
       </c>
       <c r="J226" t="n">
-        <v>1.0478</v>
+        <v>0.5824</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.01</v>
       </c>
       <c r="I227" t="n">
-        <v>0.1008</v>
+        <v>0.0832</v>
       </c>
       <c r="J227" t="n">
-        <v>2.6208</v>
+        <v>2.1632</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.96</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.0445</v>
+        <v>-0.0331</v>
       </c>
       <c r="J228" t="n">
-        <v>-1.157</v>
+        <v>-0.8606</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.64</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.3775</v>
+        <v>-0.3645</v>
       </c>
       <c r="J229" t="n">
-        <v>-9.815</v>
+        <v>-9.477</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.6</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4133</v>
+        <v>-0.4029</v>
       </c>
       <c r="J230" t="n">
-        <v>-10.7458</v>
+        <v>-10.4754</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.59</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4222</v>
+        <v>-0.4125</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.9772</v>
+        <v>-10.725</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.52</v>
       </c>
       <c r="I232" t="n">
-        <v>1.1376</v>
+        <v>1.1505</v>
       </c>
       <c r="J232" t="n">
-        <v>28.44</v>
+        <v>28.7625</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.19</v>
       </c>
       <c r="I233" t="n">
-        <v>0.5261</v>
+        <v>0.4904</v>
       </c>
       <c r="J233" t="n">
-        <v>13.1525</v>
+        <v>12.26</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.17</v>
       </c>
       <c r="I234" t="n">
-        <v>0.4824</v>
+        <v>0.4464</v>
       </c>
       <c r="J234" t="n">
-        <v>12.06</v>
+        <v>11.16</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.15</v>
       </c>
       <c r="I235" t="n">
-        <v>0.4371</v>
+        <v>0.4012</v>
       </c>
       <c r="J235" t="n">
-        <v>10.9275</v>
+        <v>10.03</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.84</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5269</v>
+        <v>-0.4877</v>
       </c>
       <c r="J236" t="n">
-        <v>-13.1725</v>
+        <v>-12.1925</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.18</v>
       </c>
       <c r="I237" t="n">
-        <v>0.4154</v>
+        <v>0.3593</v>
       </c>
       <c r="J237" t="n">
-        <v>10.385</v>
+        <v>8.9825</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.15</v>
       </c>
       <c r="I238" t="n">
-        <v>0.3613</v>
+        <v>0.3073</v>
       </c>
       <c r="J238" t="n">
-        <v>9.032500000000001</v>
+        <v>7.6825</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.01</v>
       </c>
       <c r="I239" t="n">
-        <v>0.0523</v>
+        <v>0.0352</v>
       </c>
       <c r="J239" t="n">
-        <v>1.3075</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.7</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3418</v>
+        <v>-0.3261</v>
       </c>
       <c r="J240" t="n">
-        <v>-8.545</v>
+        <v>-8.1525</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.64</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3962</v>
+        <v>-0.385</v>
       </c>
       <c r="J241" t="n">
-        <v>-9.904999999999999</v>
+        <v>-9.625</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.5</v>
       </c>
       <c r="I242" t="n">
-        <v>1.1515</v>
+        <v>1.1695</v>
       </c>
       <c r="J242" t="n">
-        <v>40.3025</v>
+        <v>40.9325</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.23</v>
       </c>
       <c r="I243" t="n">
-        <v>0.6467000000000001</v>
+        <v>0.6101</v>
       </c>
       <c r="J243" t="n">
-        <v>22.6345</v>
+        <v>21.3535</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.9</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.3476</v>
+        <v>-0.3052</v>
       </c>
       <c r="J244" t="n">
-        <v>-12.166</v>
+        <v>-10.682</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.5701000000000001</v>
+        <v>-0.5302</v>
       </c>
       <c r="J245" t="n">
-        <v>-19.9535</v>
+        <v>-18.557</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.7</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.8147</v>
+        <v>-0.7913</v>
       </c>
       <c r="J246" t="n">
-        <v>-28.5145</v>
+        <v>-27.6955</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.31</v>
       </c>
       <c r="I247" t="n">
-        <v>0.5965</v>
+        <v>0.5367</v>
       </c>
       <c r="J247" t="n">
-        <v>20.8775</v>
+        <v>18.7845</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.19</v>
       </c>
       <c r="I248" t="n">
-        <v>0.4035</v>
+        <v>0.3476</v>
       </c>
       <c r="J248" t="n">
-        <v>14.1225</v>
+        <v>12.166</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.14</v>
       </c>
       <c r="I249" t="n">
-        <v>0.3167</v>
+        <v>0.2661</v>
       </c>
       <c r="J249" t="n">
-        <v>11.0845</v>
+        <v>9.313499999999999</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.93</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.1168</v>
+        <v>-0.0983</v>
       </c>
       <c r="J250" t="n">
-        <v>-4.088</v>
+        <v>-3.4405</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.75</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3065</v>
+        <v>-0.2894</v>
       </c>
       <c r="J251" t="n">
-        <v>-10.7275</v>
+        <v>-10.129</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.4</v>
       </c>
       <c r="I252" t="n">
-        <v>0.9576</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="J252" t="n">
-        <v>28.728</v>
+        <v>28.413</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.26</v>
       </c>
       <c r="I253" t="n">
-        <v>0.6776</v>
+        <v>0.6453</v>
       </c>
       <c r="J253" t="n">
-        <v>20.328</v>
+        <v>19.359</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.2</v>
       </c>
       <c r="I254" t="n">
-        <v>0.5493</v>
+        <v>0.5133</v>
       </c>
       <c r="J254" t="n">
-        <v>16.479</v>
+        <v>15.399</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.02</v>
       </c>
       <c r="I255" t="n">
-        <v>0.074</v>
+        <v>0.0575</v>
       </c>
       <c r="J255" t="n">
-        <v>2.22</v>
+        <v>1.725</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.2613</v>
+        <v>-0.2227</v>
       </c>
       <c r="J256" t="n">
-        <v>-7.839</v>
+        <v>-6.681</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.28</v>
       </c>
       <c r="I257" t="n">
-        <v>0.5883</v>
+        <v>0.5321</v>
       </c>
       <c r="J257" t="n">
-        <v>17.649</v>
+        <v>15.963</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.02</v>
       </c>
       <c r="I258" t="n">
-        <v>0.0849</v>
+        <v>0.0607</v>
       </c>
       <c r="J258" t="n">
-        <v>2.547</v>
+        <v>1.821</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.8</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.2455</v>
+        <v>-0.2256</v>
       </c>
       <c r="J259" t="n">
-        <v>-7.365</v>
+        <v>-6.768</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.79</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2553</v>
+        <v>-0.2356</v>
       </c>
       <c r="J260" t="n">
-        <v>-7.659</v>
+        <v>-7.068</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.74</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3034</v>
+        <v>-0.2855</v>
       </c>
       <c r="J261" t="n">
-        <v>-9.102</v>
+        <v>-8.565</v>
       </c>
     </row>
   </sheetData>
